--- a/cleaned_data_p2.xlsx
+++ b/cleaned_data_p2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N150"/>
+  <dimension ref="A1:N160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -537,37 +537,37 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>3.49201994126609</v>
+        <v>0.7459619830659699</v>
       </c>
       <c r="D3" t="n">
-        <v>-2.09987360600907</v>
+        <v>6.12744724329777</v>
       </c>
       <c r="E3" t="n">
-        <v>14.89</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04317</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>9.883333333333333</v>
+        <v>3.550000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>10.81666666666667</v>
+        <v>4.366666666666667</v>
       </c>
       <c r="I3" t="n">
-        <v>9.883333333333333</v>
+        <v>-1</v>
       </c>
       <c r="J3" t="n">
-        <v>10.81666666666667</v>
+        <v>-1</v>
       </c>
       <c r="K3" t="n">
-        <v>9.883333333333333</v>
+        <v>3.550000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>10.81666666666667</v>
+        <v>4.366666666666667</v>
       </c>
       <c r="M3" t="n">
         <v>0.3333333333333333</v>
@@ -581,37 +581,37 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>-2.7926750198023</v>
+        <v>3.49201994126609</v>
       </c>
       <c r="D4" t="n">
-        <v>-7.07070496926335</v>
+        <v>-2.09987360600907</v>
       </c>
       <c r="E4" t="n">
-        <v>235.0181</v>
+        <v>14.89</v>
       </c>
       <c r="F4" t="n">
-        <v>0.70348</v>
+        <v>0.04317</v>
       </c>
       <c r="G4" t="n">
-        <v>6.550000000000001</v>
+        <v>9.883333333333333</v>
       </c>
       <c r="H4" t="n">
-        <v>7.35</v>
+        <v>10.81666666666667</v>
       </c>
       <c r="I4" t="n">
-        <v>-1</v>
+        <v>9.883333333333333</v>
       </c>
       <c r="J4" t="n">
-        <v>-1</v>
+        <v>10.81666666666667</v>
       </c>
       <c r="K4" t="n">
-        <v>6.550000000000001</v>
+        <v>9.883333333333333</v>
       </c>
       <c r="L4" t="n">
-        <v>7.35</v>
+        <v>10.81666666666667</v>
       </c>
       <c r="M4" t="n">
         <v>0.3333333333333333</v>
@@ -625,37 +625,37 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>-5.53320102964836</v>
+        <v>-2.7926750198023</v>
       </c>
       <c r="D5" t="n">
-        <v>4.96886646380205</v>
+        <v>-7.07070496926335</v>
       </c>
       <c r="E5" t="n">
-        <v>1443.5621</v>
+        <v>235.0181</v>
       </c>
       <c r="F5" t="n">
-        <v>3.40848</v>
+        <v>0.70348</v>
       </c>
       <c r="G5" t="n">
-        <v>11.48333333333333</v>
+        <v>6.550000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>12.61666666666667</v>
+        <v>7.35</v>
       </c>
       <c r="I5" t="n">
-        <v>11.48333333333333</v>
+        <v>-1</v>
       </c>
       <c r="J5" t="n">
-        <v>12.61666666666667</v>
+        <v>-1</v>
       </c>
       <c r="K5" t="n">
-        <v>11.48333333333333</v>
+        <v>6.550000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>12.61666666666667</v>
+        <v>7.35</v>
       </c>
       <c r="M5" t="n">
         <v>0.3333333333333333</v>
@@ -669,37 +669,37 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>-7.58608040355909</v>
+        <v>-5.53320102964836</v>
       </c>
       <c r="D6" t="n">
-        <v>-3.95143072486639</v>
+        <v>4.96886646380205</v>
       </c>
       <c r="E6" t="n">
-        <v>731.6005</v>
+        <v>1443.5621</v>
       </c>
       <c r="F6" t="n">
-        <v>2.31239</v>
+        <v>3.40848</v>
       </c>
       <c r="G6" t="n">
-        <v>11.46666666666667</v>
+        <v>11.48333333333333</v>
       </c>
       <c r="H6" t="n">
-        <v>12.43333333333333</v>
+        <v>12.61666666666667</v>
       </c>
       <c r="I6" t="n">
-        <v>11.46666666666667</v>
+        <v>11.48333333333333</v>
       </c>
       <c r="J6" t="n">
-        <v>12.43333333333333</v>
+        <v>12.61666666666667</v>
       </c>
       <c r="K6" t="n">
-        <v>11.46666666666667</v>
+        <v>11.48333333333333</v>
       </c>
       <c r="L6" t="n">
-        <v>12.43333333333333</v>
+        <v>12.61666666666667</v>
       </c>
       <c r="M6" t="n">
         <v>0.3333333333333333</v>
@@ -713,37 +713,37 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>-4.66159864091412</v>
+        <v>-7.58608040355909</v>
       </c>
       <c r="D7" t="n">
-        <v>-7.50935781984783</v>
+        <v>-3.95143072486639</v>
       </c>
       <c r="E7" t="n">
-        <v>3000</v>
+        <v>731.6005</v>
       </c>
       <c r="F7" t="n">
-        <v>11.9832</v>
+        <v>2.31239</v>
       </c>
       <c r="G7" t="n">
-        <v>3.766666666666667</v>
+        <v>11.46666666666667</v>
       </c>
       <c r="H7" t="n">
-        <v>4.983333333333333</v>
+        <v>12.43333333333333</v>
       </c>
       <c r="I7" t="n">
-        <v>-1</v>
+        <v>11.46666666666667</v>
       </c>
       <c r="J7" t="n">
-        <v>-1</v>
+        <v>12.43333333333333</v>
       </c>
       <c r="K7" t="n">
-        <v>3.766666666666667</v>
+        <v>11.46666666666667</v>
       </c>
       <c r="L7" t="n">
-        <v>4.983333333333333</v>
+        <v>12.43333333333333</v>
       </c>
       <c r="M7" t="n">
         <v>0.3333333333333333</v>
@@ -766,10 +766,10 @@
         <v>-7.50935781984783</v>
       </c>
       <c r="E8" t="n">
-        <v>1473.6432</v>
+        <v>2236.8216</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>5.991599999999999</v>
       </c>
       <c r="G8" t="n">
         <v>3.766666666666667</v>
@@ -801,25 +801,25 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>-8.50508883064982</v>
+        <v>-4.66159864091412</v>
       </c>
       <c r="D9" t="n">
-        <v>3.40488850459411</v>
+        <v>-7.50935781984783</v>
       </c>
       <c r="E9" t="n">
-        <v>3000</v>
+        <v>2236.8216</v>
       </c>
       <c r="F9" t="n">
-        <v>15</v>
+        <v>5.991599999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>4.683333333333334</v>
+        <v>3.766666666666667</v>
       </c>
       <c r="H9" t="n">
-        <v>6.133333333333333</v>
+        <v>4.983333333333333</v>
       </c>
       <c r="I9" t="n">
         <v>-1</v>
@@ -828,10 +828,10 @@
         <v>-1</v>
       </c>
       <c r="K9" t="n">
-        <v>4.683333333333334</v>
+        <v>3.766666666666667</v>
       </c>
       <c r="L9" t="n">
-        <v>6.133333333333333</v>
+        <v>4.983333333333333</v>
       </c>
       <c r="M9" t="n">
         <v>0.3333333333333333</v>
@@ -854,10 +854,10 @@
         <v>3.40488850459411</v>
       </c>
       <c r="E10" t="n">
-        <v>3000</v>
+        <v>2487.744266666667</v>
       </c>
       <c r="F10" t="n">
-        <v>3.23404</v>
+        <v>6.078013333333334</v>
       </c>
       <c r="G10" t="n">
         <v>4.683333333333334</v>
@@ -898,10 +898,10 @@
         <v>3.40488850459411</v>
       </c>
       <c r="E11" t="n">
-        <v>1463.2328</v>
+        <v>2487.744266666667</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>6.078013333333334</v>
       </c>
       <c r="G11" t="n">
         <v>4.683333333333334</v>
@@ -933,25 +933,25 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C12" t="n">
-        <v>2.31778195492727</v>
+        <v>-8.50508883064982</v>
       </c>
       <c r="D12" t="n">
-        <v>3.18321046881879</v>
+        <v>3.40488850459411</v>
       </c>
       <c r="E12" t="n">
-        <v>3000</v>
+        <v>2487.744266666667</v>
       </c>
       <c r="F12" t="n">
-        <v>15</v>
+        <v>6.078013333333334</v>
       </c>
       <c r="G12" t="n">
-        <v>2.816666666666666</v>
+        <v>4.683333333333334</v>
       </c>
       <c r="H12" t="n">
-        <v>3.783333333333333</v>
+        <v>6.133333333333333</v>
       </c>
       <c r="I12" t="n">
         <v>-1</v>
@@ -960,10 +960,10 @@
         <v>-1</v>
       </c>
       <c r="K12" t="n">
-        <v>2.816666666666666</v>
+        <v>4.683333333333334</v>
       </c>
       <c r="L12" t="n">
-        <v>3.783333333333333</v>
+        <v>6.133333333333333</v>
       </c>
       <c r="M12" t="n">
         <v>0.3333333333333333</v>
@@ -986,10 +986,10 @@
         <v>3.18321046881879</v>
       </c>
       <c r="E13" t="n">
-        <v>3000</v>
+        <v>2937.388405</v>
       </c>
       <c r="F13" t="n">
-        <v>15</v>
+        <v>9.006755</v>
       </c>
       <c r="G13" t="n">
         <v>2.816666666666666</v>
@@ -1030,10 +1030,10 @@
         <v>3.18321046881879</v>
       </c>
       <c r="E14" t="n">
-        <v>3000</v>
+        <v>2937.388405</v>
       </c>
       <c r="F14" t="n">
-        <v>6.02702</v>
+        <v>9.006755</v>
       </c>
       <c r="G14" t="n">
         <v>2.816666666666666</v>
@@ -1074,10 +1074,10 @@
         <v>3.18321046881879</v>
       </c>
       <c r="E15" t="n">
-        <v>2749.553620000001</v>
+        <v>2937.388405</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>9.006755</v>
       </c>
       <c r="G15" t="n">
         <v>2.816666666666666</v>
@@ -1109,25 +1109,25 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>4.21284964345134</v>
+        <v>2.31778195492727</v>
       </c>
       <c r="D16" t="n">
-        <v>7.3870741887538</v>
+        <v>3.18321046881879</v>
       </c>
       <c r="E16" t="n">
-        <v>2506.7093</v>
+        <v>2937.388405</v>
       </c>
       <c r="F16" t="n">
-        <v>6.65072</v>
+        <v>9.006755</v>
       </c>
       <c r="G16" t="n">
-        <v>2.1</v>
+        <v>2.816666666666666</v>
       </c>
       <c r="H16" t="n">
-        <v>3.533333333333333</v>
+        <v>3.783333333333333</v>
       </c>
       <c r="I16" t="n">
         <v>-1</v>
@@ -1136,10 +1136,10 @@
         <v>-1</v>
       </c>
       <c r="K16" t="n">
-        <v>2.1</v>
+        <v>2.816666666666666</v>
       </c>
       <c r="L16" t="n">
-        <v>3.533333333333333</v>
+        <v>3.783333333333333</v>
       </c>
       <c r="M16" t="n">
         <v>0.3333333333333333</v>
@@ -1153,37 +1153,37 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>-5.87115512935265</v>
+        <v>4.21284964345134</v>
       </c>
       <c r="D17" t="n">
-        <v>-5.56732049906664</v>
+        <v>7.3870741887538</v>
       </c>
       <c r="E17" t="n">
-        <v>3000</v>
+        <v>2506.7093</v>
       </c>
       <c r="F17" t="n">
-        <v>14.55749</v>
+        <v>6.65072</v>
       </c>
       <c r="G17" t="n">
-        <v>11.66666666666667</v>
+        <v>2.1</v>
       </c>
       <c r="H17" t="n">
-        <v>12.48333333333333</v>
+        <v>3.533333333333333</v>
       </c>
       <c r="I17" t="n">
-        <v>11.66666666666667</v>
+        <v>-1</v>
       </c>
       <c r="J17" t="n">
-        <v>12.48333333333333</v>
+        <v>-1</v>
       </c>
       <c r="K17" t="n">
-        <v>11.66666666666667</v>
+        <v>2.1</v>
       </c>
       <c r="L17" t="n">
-        <v>12.48333333333333</v>
+        <v>3.533333333333333</v>
       </c>
       <c r="M17" t="n">
         <v>0.3333333333333333</v>
@@ -1206,10 +1206,10 @@
         <v>-5.56732049906664</v>
       </c>
       <c r="E18" t="n">
-        <v>759.9850000000001</v>
+        <v>1879.9925</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>7.278745</v>
       </c>
       <c r="G18" t="n">
         <v>11.66666666666667</v>
@@ -1241,37 +1241,37 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>0.52184375622088</v>
+        <v>-5.87115512935265</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.3827701607119</v>
+        <v>-5.56732049906664</v>
       </c>
       <c r="E19" t="n">
-        <v>1325.5301</v>
+        <v>1879.9925</v>
       </c>
       <c r="F19" t="n">
-        <v>4.36316</v>
+        <v>7.278745</v>
       </c>
       <c r="G19" t="n">
-        <v>3.483333333333333</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="H19" t="n">
-        <v>4.833333333333334</v>
+        <v>12.48333333333333</v>
       </c>
       <c r="I19" t="n">
-        <v>-1</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="J19" t="n">
-        <v>-1</v>
+        <v>12.48333333333333</v>
       </c>
       <c r="K19" t="n">
-        <v>3.483333333333333</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="L19" t="n">
-        <v>4.833333333333334</v>
+        <v>12.48333333333333</v>
       </c>
       <c r="M19" t="n">
         <v>0.3333333333333333</v>
@@ -1285,25 +1285,25 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C20" t="n">
-        <v>1.21755848144176</v>
+        <v>0.52184375622088</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.34839674138507</v>
+        <v>-2.3827701607119</v>
       </c>
       <c r="E20" t="n">
-        <v>1726.8416</v>
+        <v>1325.5301</v>
       </c>
       <c r="F20" t="n">
-        <v>4.399550000000001</v>
+        <v>4.36316</v>
       </c>
       <c r="G20" t="n">
-        <v>6.916666666666666</v>
+        <v>3.483333333333333</v>
       </c>
       <c r="H20" t="n">
-        <v>7.833333333333334</v>
+        <v>4.833333333333334</v>
       </c>
       <c r="I20" t="n">
         <v>-1</v>
@@ -1312,10 +1312,10 @@
         <v>-1</v>
       </c>
       <c r="K20" t="n">
-        <v>6.916666666666666</v>
+        <v>3.483333333333333</v>
       </c>
       <c r="L20" t="n">
-        <v>7.833333333333334</v>
+        <v>4.833333333333334</v>
       </c>
       <c r="M20" t="n">
         <v>0.3333333333333333</v>
@@ -1329,25 +1329,25 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C21" t="n">
-        <v>1.95141807684275</v>
+        <v>1.21755848144176</v>
       </c>
       <c r="D21" t="n">
-        <v>8.96083447171654</v>
+        <v>-1.34839674138507</v>
       </c>
       <c r="E21" t="n">
-        <v>540.0867999999999</v>
+        <v>1726.8416</v>
       </c>
       <c r="F21" t="n">
-        <v>1.27918</v>
+        <v>4.399550000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>4.166666666666666</v>
+        <v>6.916666666666666</v>
       </c>
       <c r="H21" t="n">
-        <v>5.1</v>
+        <v>7.833333333333334</v>
       </c>
       <c r="I21" t="n">
         <v>-1</v>
@@ -1356,10 +1356,10 @@
         <v>-1</v>
       </c>
       <c r="K21" t="n">
-        <v>4.166666666666666</v>
+        <v>6.916666666666666</v>
       </c>
       <c r="L21" t="n">
-        <v>5.1</v>
+        <v>7.833333333333334</v>
       </c>
       <c r="M21" t="n">
         <v>0.3333333333333333</v>
@@ -1373,43 +1373,43 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C22" t="n">
-        <v>14.450550964877</v>
+        <v>1.95141807684275</v>
       </c>
       <c r="D22" t="n">
-        <v>-8.765440295958079</v>
+        <v>8.96083447171654</v>
       </c>
       <c r="E22" t="n">
-        <v>85.19999999999999</v>
+        <v>540.0867999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1931</v>
+        <v>1.27918</v>
       </c>
       <c r="G22" t="n">
-        <v>1.283333333333333</v>
+        <v>4.166666666666666</v>
       </c>
       <c r="H22" t="n">
-        <v>2.683333333333334</v>
+        <v>5.1</v>
       </c>
       <c r="I22" t="n">
-        <v>1.283333333333333</v>
+        <v>-1</v>
       </c>
       <c r="J22" t="n">
-        <v>2.683333333333334</v>
+        <v>-1</v>
       </c>
       <c r="K22" t="n">
-        <v>1.283333333333333</v>
+        <v>4.166666666666666</v>
       </c>
       <c r="L22" t="n">
-        <v>2.683333333333334</v>
+        <v>5.1</v>
       </c>
       <c r="M22" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="N22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1417,43 +1417,43 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C23" t="n">
-        <v>-24.9556659958338</v>
+        <v>-0.943660216384455</v>
       </c>
       <c r="D23" t="n">
-        <v>-20.1758424030975</v>
+        <v>-8.4695515770045</v>
       </c>
       <c r="E23" t="n">
-        <v>9.372199999999999</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0.07403</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>11.25</v>
+        <v>7.699999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>12.46666666666667</v>
+        <v>9.083333333333332</v>
       </c>
       <c r="I23" t="n">
-        <v>11.25</v>
+        <v>8</v>
       </c>
       <c r="J23" t="n">
-        <v>12.46666666666667</v>
+        <v>9.083333333333332</v>
       </c>
       <c r="K23" t="n">
-        <v>11.25</v>
+        <v>7.699999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>12.46666666666667</v>
+        <v>9.083333333333332</v>
       </c>
       <c r="M23" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="N23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1461,43 +1461,43 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C24" t="n">
-        <v>-22.8798563925078</v>
+        <v>-1.70421069554743</v>
       </c>
       <c r="D24" t="n">
-        <v>17.78788893064</v>
+        <v>-3.09774834490506</v>
       </c>
       <c r="E24" t="n">
-        <v>1262.1673</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>2.95599</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>8.850000000000001</v>
+        <v>7</v>
       </c>
       <c r="H24" t="n">
-        <v>10.26666666666667</v>
+        <v>8.399999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>8.850000000000001</v>
+        <v>8</v>
       </c>
       <c r="J24" t="n">
-        <v>10.26666666666667</v>
+        <v>8.399999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>8.850000000000001</v>
+        <v>7</v>
       </c>
       <c r="L24" t="n">
-        <v>10.26666666666667</v>
+        <v>8.399999999999999</v>
       </c>
       <c r="M24" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="N24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1505,37 +1505,37 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C25" t="n">
-        <v>7.61494129207758</v>
+        <v>14.450550964877</v>
       </c>
       <c r="D25" t="n">
-        <v>8.631907896864689</v>
+        <v>-8.765440295958079</v>
       </c>
       <c r="E25" t="n">
-        <v>2528.1351</v>
+        <v>85.19999999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>5.33839</v>
+        <v>0.1931</v>
       </c>
       <c r="G25" t="n">
-        <v>8.316666666666666</v>
+        <v>1.283333333333333</v>
       </c>
       <c r="H25" t="n">
-        <v>9.483333333333334</v>
+        <v>2.683333333333334</v>
       </c>
       <c r="I25" t="n">
-        <v>8.316666666666666</v>
+        <v>1.283333333333333</v>
       </c>
       <c r="J25" t="n">
-        <v>9.483333333333334</v>
+        <v>2.683333333333334</v>
       </c>
       <c r="K25" t="n">
-        <v>8.316666666666666</v>
+        <v>1.283333333333333</v>
       </c>
       <c r="L25" t="n">
-        <v>9.483333333333334</v>
+        <v>2.683333333333334</v>
       </c>
       <c r="M25" t="n">
         <v>0.3333333333333333</v>
@@ -1549,37 +1549,37 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C26" t="n">
-        <v>-3.82996615152896</v>
+        <v>33.3988623061578</v>
       </c>
       <c r="D26" t="n">
-        <v>-27.8021080833649</v>
+        <v>-4.21820637223678</v>
       </c>
       <c r="E26" t="n">
-        <v>45.81319999999999</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1362</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>7.833333333333334</v>
+        <v>4.866666666666667</v>
       </c>
       <c r="H26" t="n">
-        <v>9.199999999999999</v>
+        <v>6.266666666666667</v>
       </c>
       <c r="I26" t="n">
-        <v>7.833333333333334</v>
+        <v>4.866666666666667</v>
       </c>
       <c r="J26" t="n">
-        <v>9.199999999999999</v>
+        <v>6.266666666666667</v>
       </c>
       <c r="K26" t="n">
-        <v>7.833333333333334</v>
+        <v>4.866666666666667</v>
       </c>
       <c r="L26" t="n">
-        <v>9.199999999999999</v>
+        <v>6.266666666666667</v>
       </c>
       <c r="M26" t="n">
         <v>0.3333333333333333</v>
@@ -1593,37 +1593,37 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.948882982472617</v>
+        <v>-5.54863118490896</v>
       </c>
       <c r="D27" t="n">
-        <v>-27.1587227180418</v>
+        <v>12.227305144567</v>
       </c>
       <c r="E27" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>7.63971</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>9.850000000000001</v>
+        <v>7.233333333333333</v>
       </c>
       <c r="H27" t="n">
-        <v>11.11666666666667</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>9.850000000000001</v>
+        <v>7.233333333333333</v>
       </c>
       <c r="J27" t="n">
-        <v>11.11666666666667</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>9.850000000000001</v>
+        <v>7.233333333333333</v>
       </c>
       <c r="L27" t="n">
-        <v>11.11666666666667</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M27" t="n">
         <v>0.3333333333333333</v>
@@ -1637,37 +1637,37 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.948882982472617</v>
+        <v>-24.9556659958338</v>
       </c>
       <c r="D28" t="n">
-        <v>-27.1587227180418</v>
+        <v>-20.1758424030975</v>
       </c>
       <c r="E28" t="n">
-        <v>233.6041</v>
+        <v>9.372199999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>0.07403</v>
       </c>
       <c r="G28" t="n">
-        <v>9.850000000000001</v>
+        <v>11.25</v>
       </c>
       <c r="H28" t="n">
-        <v>11.11666666666667</v>
+        <v>12.46666666666667</v>
       </c>
       <c r="I28" t="n">
-        <v>9.850000000000001</v>
+        <v>11.25</v>
       </c>
       <c r="J28" t="n">
-        <v>11.11666666666667</v>
+        <v>12.46666666666667</v>
       </c>
       <c r="K28" t="n">
-        <v>9.850000000000001</v>
+        <v>11.25</v>
       </c>
       <c r="L28" t="n">
-        <v>11.11666666666667</v>
+        <v>12.46666666666667</v>
       </c>
       <c r="M28" t="n">
         <v>0.3333333333333333</v>
@@ -1681,37 +1681,37 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C29" t="n">
-        <v>22.0320436347622</v>
+        <v>14.7106222334661</v>
       </c>
       <c r="D29" t="n">
-        <v>-20.5978136037632</v>
+        <v>-12.5193153454242</v>
       </c>
       <c r="E29" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>7.9603</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>11.45</v>
+        <v>2.616666666666667</v>
       </c>
       <c r="H29" t="n">
-        <v>12.58333333333333</v>
+        <v>4.016666666666667</v>
       </c>
       <c r="I29" t="n">
-        <v>11.45</v>
+        <v>2.616666666666667</v>
       </c>
       <c r="J29" t="n">
-        <v>12.58333333333333</v>
+        <v>4.016666666666667</v>
       </c>
       <c r="K29" t="n">
-        <v>11.45</v>
+        <v>2.616666666666667</v>
       </c>
       <c r="L29" t="n">
-        <v>12.58333333333333</v>
+        <v>4.016666666666667</v>
       </c>
       <c r="M29" t="n">
         <v>0.3333333333333333</v>
@@ -1725,37 +1725,37 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C30" t="n">
-        <v>22.0320436347622</v>
+        <v>-11.7497074626045</v>
       </c>
       <c r="D30" t="n">
-        <v>-20.5978136037632</v>
+        <v>35.0960881663225</v>
       </c>
       <c r="E30" t="n">
-        <v>257.3115000000003</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>11.45</v>
+        <v>1.583333333333334</v>
       </c>
       <c r="H30" t="n">
-        <v>12.58333333333333</v>
+        <v>2.383333333333333</v>
       </c>
       <c r="I30" t="n">
-        <v>11.45</v>
+        <v>1.583333333333334</v>
       </c>
       <c r="J30" t="n">
-        <v>12.58333333333333</v>
+        <v>2.383333333333333</v>
       </c>
       <c r="K30" t="n">
-        <v>11.45</v>
+        <v>1.583333333333334</v>
       </c>
       <c r="L30" t="n">
-        <v>12.58333333333333</v>
+        <v>2.383333333333333</v>
       </c>
       <c r="M30" t="n">
         <v>0.3333333333333333</v>
@@ -1769,37 +1769,37 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C31" t="n">
-        <v>-14.3588031854593</v>
+        <v>-8.831732975604879</v>
       </c>
       <c r="D31" t="n">
-        <v>29.6057903264111</v>
+        <v>-15.519725753721</v>
       </c>
       <c r="E31" t="n">
-        <v>873.9449999999999</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>2.04764</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>9.633333333333333</v>
+        <v>5.85</v>
       </c>
       <c r="H31" t="n">
-        <v>11.05</v>
+        <v>7.283333333333333</v>
       </c>
       <c r="I31" t="n">
-        <v>9.633333333333333</v>
+        <v>5.85</v>
       </c>
       <c r="J31" t="n">
-        <v>11.05</v>
+        <v>7.283333333333333</v>
       </c>
       <c r="K31" t="n">
-        <v>9.633333333333333</v>
+        <v>5.85</v>
       </c>
       <c r="L31" t="n">
-        <v>11.05</v>
+        <v>7.283333333333333</v>
       </c>
       <c r="M31" t="n">
         <v>0.3333333333333333</v>
@@ -1813,37 +1813,37 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C32" t="n">
-        <v>16.0800764301466</v>
+        <v>-13.8099790627706</v>
       </c>
       <c r="D32" t="n">
-        <v>7.04621833529546</v>
+        <v>-22.8050691954668</v>
       </c>
       <c r="E32" t="n">
-        <v>334.852</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0.73178</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>3.533333333333333</v>
+        <v>4.166666666666666</v>
       </c>
       <c r="H32" t="n">
-        <v>5.033333333333333</v>
+        <v>5.25</v>
       </c>
       <c r="I32" t="n">
-        <v>3.533333333333333</v>
+        <v>4.166666666666666</v>
       </c>
       <c r="J32" t="n">
-        <v>5.033333333333333</v>
+        <v>5.25</v>
       </c>
       <c r="K32" t="n">
-        <v>3.533333333333333</v>
+        <v>4.166666666666666</v>
       </c>
       <c r="L32" t="n">
-        <v>5.033333333333333</v>
+        <v>5.25</v>
       </c>
       <c r="M32" t="n">
         <v>0.3333333333333333</v>
@@ -1857,37 +1857,37 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C33" t="n">
-        <v>8.198403697413969</v>
+        <v>-22.8798563925078</v>
       </c>
       <c r="D33" t="n">
-        <v>-9.60107559004272</v>
+        <v>17.78788893064</v>
       </c>
       <c r="E33" t="n">
-        <v>3000</v>
+        <v>1262.1673</v>
       </c>
       <c r="F33" t="n">
-        <v>15</v>
+        <v>2.95599</v>
       </c>
       <c r="G33" t="n">
-        <v>8.816666666666666</v>
+        <v>8.850000000000001</v>
       </c>
       <c r="H33" t="n">
-        <v>9.766666666666666</v>
+        <v>10.26666666666667</v>
       </c>
       <c r="I33" t="n">
-        <v>8.816666666666666</v>
+        <v>8.850000000000001</v>
       </c>
       <c r="J33" t="n">
-        <v>9.766666666666666</v>
+        <v>10.26666666666667</v>
       </c>
       <c r="K33" t="n">
-        <v>8.816666666666666</v>
+        <v>8.850000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>9.766666666666666</v>
+        <v>10.26666666666667</v>
       </c>
       <c r="M33" t="n">
         <v>0.3333333333333333</v>
@@ -1901,37 +1901,37 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C34" t="n">
-        <v>8.198403697413969</v>
+        <v>7.61494129207758</v>
       </c>
       <c r="D34" t="n">
-        <v>-9.60107559004272</v>
+        <v>8.631907896864689</v>
       </c>
       <c r="E34" t="n">
-        <v>3000</v>
+        <v>2528.1351</v>
       </c>
       <c r="F34" t="n">
-        <v>0.4452700000000007</v>
+        <v>5.33839</v>
       </c>
       <c r="G34" t="n">
-        <v>8.816666666666666</v>
+        <v>8.316666666666666</v>
       </c>
       <c r="H34" t="n">
-        <v>9.766666666666666</v>
+        <v>9.483333333333334</v>
       </c>
       <c r="I34" t="n">
-        <v>8.816666666666666</v>
+        <v>8.316666666666666</v>
       </c>
       <c r="J34" t="n">
-        <v>9.766666666666666</v>
+        <v>9.483333333333334</v>
       </c>
       <c r="K34" t="n">
-        <v>8.816666666666666</v>
+        <v>8.316666666666666</v>
       </c>
       <c r="L34" t="n">
-        <v>9.766666666666666</v>
+        <v>9.483333333333334</v>
       </c>
       <c r="M34" t="n">
         <v>0.3333333333333333</v>
@@ -1945,37 +1945,37 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C35" t="n">
-        <v>8.198403697413969</v>
+        <v>-3.82996615152896</v>
       </c>
       <c r="D35" t="n">
-        <v>-9.60107559004272</v>
+        <v>-27.8021080833649</v>
       </c>
       <c r="E35" t="n">
-        <v>771.6208000000006</v>
+        <v>45.81319999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>0.1362</v>
       </c>
       <c r="G35" t="n">
-        <v>8.816666666666666</v>
+        <v>7.833333333333334</v>
       </c>
       <c r="H35" t="n">
-        <v>9.766666666666666</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>8.816666666666666</v>
+        <v>7.833333333333334</v>
       </c>
       <c r="J35" t="n">
-        <v>9.766666666666666</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>8.816666666666666</v>
+        <v>7.833333333333334</v>
       </c>
       <c r="L35" t="n">
-        <v>9.766666666666666</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M35" t="n">
         <v>0.3333333333333333</v>
@@ -1989,37 +1989,37 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C36" t="n">
-        <v>0.323325874270734</v>
+        <v>-0.948882982472617</v>
       </c>
       <c r="D36" t="n">
-        <v>-37.5736956858047</v>
+        <v>-27.1587227180418</v>
       </c>
       <c r="E36" t="n">
-        <v>442.3342</v>
+        <v>1616.80205</v>
       </c>
       <c r="F36" t="n">
-        <v>1.12524</v>
+        <v>3.819855</v>
       </c>
       <c r="G36" t="n">
-        <v>5.133333333333333</v>
+        <v>9.850000000000001</v>
       </c>
       <c r="H36" t="n">
-        <v>6.4</v>
+        <v>11.11666666666667</v>
       </c>
       <c r="I36" t="n">
-        <v>5.133333333333333</v>
+        <v>9.850000000000001</v>
       </c>
       <c r="J36" t="n">
-        <v>6.4</v>
+        <v>11.11666666666667</v>
       </c>
       <c r="K36" t="n">
-        <v>5.133333333333333</v>
+        <v>9.850000000000001</v>
       </c>
       <c r="L36" t="n">
-        <v>6.4</v>
+        <v>11.11666666666667</v>
       </c>
       <c r="M36" t="n">
         <v>0.3333333333333333</v>
@@ -2033,37 +2033,37 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C37" t="n">
-        <v>-8.662441945648929</v>
+        <v>-0.948882982472617</v>
       </c>
       <c r="D37" t="n">
-        <v>-13.7461263895102</v>
+        <v>-27.1587227180418</v>
       </c>
       <c r="E37" t="n">
-        <v>527.2666</v>
+        <v>1616.80205</v>
       </c>
       <c r="F37" t="n">
-        <v>1.37982</v>
+        <v>3.819855</v>
       </c>
       <c r="G37" t="n">
-        <v>2.766666666666667</v>
+        <v>9.850000000000001</v>
       </c>
       <c r="H37" t="n">
-        <v>4.183333333333334</v>
+        <v>11.11666666666667</v>
       </c>
       <c r="I37" t="n">
-        <v>2.766666666666667</v>
+        <v>9.850000000000001</v>
       </c>
       <c r="J37" t="n">
-        <v>4.183333333333334</v>
+        <v>11.11666666666667</v>
       </c>
       <c r="K37" t="n">
-        <v>2.766666666666667</v>
+        <v>9.850000000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>4.183333333333334</v>
+        <v>11.11666666666667</v>
       </c>
       <c r="M37" t="n">
         <v>0.3333333333333333</v>
@@ -2077,37 +2077,37 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C38" t="n">
-        <v>13.090888292642</v>
+        <v>22.0320436347622</v>
       </c>
       <c r="D38" t="n">
-        <v>-10.9595442953867</v>
+        <v>-20.5978136037632</v>
       </c>
       <c r="E38" t="n">
-        <v>364.0498</v>
+        <v>1628.65575</v>
       </c>
       <c r="F38" t="n">
-        <v>1.5211</v>
+        <v>3.98015</v>
       </c>
       <c r="G38" t="n">
-        <v>10.91666666666667</v>
+        <v>11.45</v>
       </c>
       <c r="H38" t="n">
-        <v>12.13333333333333</v>
+        <v>12.58333333333333</v>
       </c>
       <c r="I38" t="n">
-        <v>10.91666666666667</v>
+        <v>11.45</v>
       </c>
       <c r="J38" t="n">
-        <v>12.13333333333333</v>
+        <v>12.58333333333333</v>
       </c>
       <c r="K38" t="n">
-        <v>10.91666666666667</v>
+        <v>11.45</v>
       </c>
       <c r="L38" t="n">
-        <v>12.13333333333333</v>
+        <v>12.58333333333333</v>
       </c>
       <c r="M38" t="n">
         <v>0.3333333333333333</v>
@@ -2121,37 +2121,37 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.079057338447202</v>
+        <v>22.0320436347622</v>
       </c>
       <c r="D39" t="n">
-        <v>-32.911273246347</v>
+        <v>-20.5978136037632</v>
       </c>
       <c r="E39" t="n">
-        <v>1692.5786</v>
+        <v>1628.65575</v>
       </c>
       <c r="F39" t="n">
-        <v>3.88436</v>
+        <v>3.98015</v>
       </c>
       <c r="G39" t="n">
-        <v>1.483333333333333</v>
+        <v>11.45</v>
       </c>
       <c r="H39" t="n">
-        <v>2.866666666666667</v>
+        <v>12.58333333333333</v>
       </c>
       <c r="I39" t="n">
-        <v>1.483333333333333</v>
+        <v>11.45</v>
       </c>
       <c r="J39" t="n">
-        <v>2.866666666666667</v>
+        <v>12.58333333333333</v>
       </c>
       <c r="K39" t="n">
-        <v>1.483333333333333</v>
+        <v>11.45</v>
       </c>
       <c r="L39" t="n">
-        <v>2.866666666666667</v>
+        <v>12.58333333333333</v>
       </c>
       <c r="M39" t="n">
         <v>0.3333333333333333</v>
@@ -2165,37 +2165,37 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C40" t="n">
-        <v>-27.7413684328977</v>
+        <v>-14.3588031854593</v>
       </c>
       <c r="D40" t="n">
-        <v>15.6205382398009</v>
+        <v>29.6057903264111</v>
       </c>
       <c r="E40" t="n">
-        <v>3000</v>
+        <v>873.9449999999999</v>
       </c>
       <c r="F40" t="n">
-        <v>10.30776</v>
+        <v>2.04764</v>
       </c>
       <c r="G40" t="n">
-        <v>7.266666666666667</v>
+        <v>9.633333333333333</v>
       </c>
       <c r="H40" t="n">
-        <v>8.350000000000001</v>
+        <v>11.05</v>
       </c>
       <c r="I40" t="n">
-        <v>7.266666666666667</v>
+        <v>9.633333333333333</v>
       </c>
       <c r="J40" t="n">
-        <v>8.350000000000001</v>
+        <v>11.05</v>
       </c>
       <c r="K40" t="n">
-        <v>7.266666666666667</v>
+        <v>9.633333333333333</v>
       </c>
       <c r="L40" t="n">
-        <v>8.350000000000001</v>
+        <v>11.05</v>
       </c>
       <c r="M40" t="n">
         <v>0.3333333333333333</v>
@@ -2209,37 +2209,37 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C41" t="n">
-        <v>-27.7413684328977</v>
+        <v>16.0800764301466</v>
       </c>
       <c r="D41" t="n">
-        <v>15.6205382398009</v>
+        <v>7.04621833529546</v>
       </c>
       <c r="E41" t="n">
-        <v>309.2547</v>
+        <v>334.852</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>0.73178</v>
       </c>
       <c r="G41" t="n">
-        <v>7.266666666666667</v>
+        <v>3.533333333333333</v>
       </c>
       <c r="H41" t="n">
-        <v>8.350000000000001</v>
+        <v>5.033333333333333</v>
       </c>
       <c r="I41" t="n">
-        <v>7.266666666666667</v>
+        <v>3.533333333333333</v>
       </c>
       <c r="J41" t="n">
-        <v>8.350000000000001</v>
+        <v>5.033333333333333</v>
       </c>
       <c r="K41" t="n">
-        <v>7.266666666666667</v>
+        <v>3.533333333333333</v>
       </c>
       <c r="L41" t="n">
-        <v>8.350000000000001</v>
+        <v>5.033333333333333</v>
       </c>
       <c r="M41" t="n">
         <v>0.3333333333333333</v>
@@ -2253,37 +2253,37 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C42" t="n">
-        <v>35.9798551608321</v>
+        <v>8.198403697413969</v>
       </c>
       <c r="D42" t="n">
-        <v>-8.834846436336671</v>
+        <v>-9.60107559004272</v>
       </c>
       <c r="E42" t="n">
-        <v>564.949</v>
+        <v>2257.206933333333</v>
       </c>
       <c r="F42" t="n">
-        <v>1.8194</v>
+        <v>5.148423333333334</v>
       </c>
       <c r="G42" t="n">
-        <v>1.416666666666666</v>
+        <v>8.816666666666666</v>
       </c>
       <c r="H42" t="n">
-        <v>2.716666666666667</v>
+        <v>9.766666666666666</v>
       </c>
       <c r="I42" t="n">
-        <v>1.416666666666666</v>
+        <v>8.816666666666666</v>
       </c>
       <c r="J42" t="n">
-        <v>2.716666666666667</v>
+        <v>9.766666666666666</v>
       </c>
       <c r="K42" t="n">
-        <v>1.416666666666666</v>
+        <v>8.816666666666666</v>
       </c>
       <c r="L42" t="n">
-        <v>2.716666666666667</v>
+        <v>9.766666666666666</v>
       </c>
       <c r="M42" t="n">
         <v>0.3333333333333333</v>
@@ -2297,37 +2297,37 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C43" t="n">
-        <v>-19.8657669761891</v>
+        <v>8.198403697413969</v>
       </c>
       <c r="D43" t="n">
-        <v>8.245091757030799</v>
+        <v>-9.60107559004272</v>
       </c>
       <c r="E43" t="n">
-        <v>1261.7326</v>
+        <v>2257.206933333333</v>
       </c>
       <c r="F43" t="n">
-        <v>4.06727</v>
+        <v>5.148423333333334</v>
       </c>
       <c r="G43" t="n">
-        <v>2.466666666666667</v>
+        <v>8.816666666666666</v>
       </c>
       <c r="H43" t="n">
-        <v>3.566666666666666</v>
+        <v>9.766666666666666</v>
       </c>
       <c r="I43" t="n">
-        <v>2.466666666666667</v>
+        <v>8.816666666666666</v>
       </c>
       <c r="J43" t="n">
-        <v>3.566666666666666</v>
+        <v>9.766666666666666</v>
       </c>
       <c r="K43" t="n">
-        <v>2.466666666666667</v>
+        <v>8.816666666666666</v>
       </c>
       <c r="L43" t="n">
-        <v>3.566666666666666</v>
+        <v>9.766666666666666</v>
       </c>
       <c r="M43" t="n">
         <v>0.3333333333333333</v>
@@ -2341,37 +2341,37 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C44" t="n">
-        <v>-14.7593829065892</v>
+        <v>8.198403697413969</v>
       </c>
       <c r="D44" t="n">
-        <v>-31.3415469493066</v>
+        <v>-9.60107559004272</v>
       </c>
       <c r="E44" t="n">
-        <v>3000</v>
+        <v>2257.206933333333</v>
       </c>
       <c r="F44" t="n">
-        <v>10.00717</v>
+        <v>5.148423333333334</v>
       </c>
       <c r="G44" t="n">
-        <v>6.133333333333333</v>
+        <v>8.816666666666666</v>
       </c>
       <c r="H44" t="n">
-        <v>7</v>
+        <v>9.766666666666666</v>
       </c>
       <c r="I44" t="n">
-        <v>6.133333333333333</v>
+        <v>8.816666666666666</v>
       </c>
       <c r="J44" t="n">
-        <v>7</v>
+        <v>9.766666666666666</v>
       </c>
       <c r="K44" t="n">
-        <v>6.133333333333333</v>
+        <v>8.816666666666666</v>
       </c>
       <c r="L44" t="n">
-        <v>7</v>
+        <v>9.766666666666666</v>
       </c>
       <c r="M44" t="n">
         <v>0.3333333333333333</v>
@@ -2385,37 +2385,37 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C45" t="n">
-        <v>-14.7593829065892</v>
+        <v>0.323325874270734</v>
       </c>
       <c r="D45" t="n">
-        <v>-31.3415469493066</v>
+        <v>-37.5736956858047</v>
       </c>
       <c r="E45" t="n">
-        <v>1024.8916</v>
+        <v>442.3342</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>1.12524</v>
       </c>
       <c r="G45" t="n">
-        <v>6.133333333333333</v>
+        <v>5.133333333333333</v>
       </c>
       <c r="H45" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="I45" t="n">
-        <v>6.133333333333333</v>
+        <v>5.133333333333333</v>
       </c>
       <c r="J45" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="K45" t="n">
-        <v>6.133333333333333</v>
+        <v>5.133333333333333</v>
       </c>
       <c r="L45" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="M45" t="n">
         <v>0.3333333333333333</v>
@@ -2429,37 +2429,37 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C46" t="n">
-        <v>-25.4478796473256</v>
+        <v>-8.662441945648929</v>
       </c>
       <c r="D46" t="n">
-        <v>8.265874726389081</v>
+        <v>-13.7461263895102</v>
       </c>
       <c r="E46" t="n">
-        <v>2691.1358</v>
+        <v>527.2666</v>
       </c>
       <c r="F46" t="n">
-        <v>7.9507</v>
+        <v>1.37982</v>
       </c>
       <c r="G46" t="n">
-        <v>9.866666666666667</v>
+        <v>2.766666666666667</v>
       </c>
       <c r="H46" t="n">
-        <v>11.06666666666667</v>
+        <v>4.183333333333334</v>
       </c>
       <c r="I46" t="n">
-        <v>9.866666666666667</v>
+        <v>2.766666666666667</v>
       </c>
       <c r="J46" t="n">
-        <v>11.06666666666667</v>
+        <v>4.183333333333334</v>
       </c>
       <c r="K46" t="n">
-        <v>9.866666666666667</v>
+        <v>2.766666666666667</v>
       </c>
       <c r="L46" t="n">
-        <v>11.06666666666667</v>
+        <v>4.183333333333334</v>
       </c>
       <c r="M46" t="n">
         <v>0.3333333333333333</v>
@@ -2473,37 +2473,37 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="C47" t="n">
-        <v>-6.39184845369064</v>
+        <v>13.090888292642</v>
       </c>
       <c r="D47" t="n">
-        <v>38.866308384005</v>
+        <v>-10.9595442953867</v>
       </c>
       <c r="E47" t="n">
-        <v>2786.4185</v>
+        <v>364.0498</v>
       </c>
       <c r="F47" t="n">
-        <v>7.85191</v>
+        <v>1.5211</v>
       </c>
       <c r="G47" t="n">
-        <v>4.633333333333333</v>
+        <v>10.91666666666667</v>
       </c>
       <c r="H47" t="n">
-        <v>5.85</v>
+        <v>12.13333333333333</v>
       </c>
       <c r="I47" t="n">
-        <v>4.633333333333333</v>
+        <v>10.91666666666667</v>
       </c>
       <c r="J47" t="n">
-        <v>5.85</v>
+        <v>12.13333333333333</v>
       </c>
       <c r="K47" t="n">
-        <v>4.633333333333333</v>
+        <v>10.91666666666667</v>
       </c>
       <c r="L47" t="n">
-        <v>5.85</v>
+        <v>12.13333333333333</v>
       </c>
       <c r="M47" t="n">
         <v>0.3333333333333333</v>
@@ -2517,37 +2517,37 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C48" t="n">
-        <v>-7.97960536037818</v>
+        <v>-0.079057338447202</v>
       </c>
       <c r="D48" t="n">
-        <v>-18.8049073592717</v>
+        <v>-32.911273246347</v>
       </c>
       <c r="E48" t="n">
-        <v>3000</v>
+        <v>1692.5786</v>
       </c>
       <c r="F48" t="n">
-        <v>15</v>
+        <v>3.88436</v>
       </c>
       <c r="G48" t="n">
-        <v>2.233333333333333</v>
+        <v>1.483333333333333</v>
       </c>
       <c r="H48" t="n">
-        <v>3.35</v>
+        <v>2.866666666666667</v>
       </c>
       <c r="I48" t="n">
-        <v>2.233333333333333</v>
+        <v>1.483333333333333</v>
       </c>
       <c r="J48" t="n">
-        <v>3.35</v>
+        <v>2.866666666666667</v>
       </c>
       <c r="K48" t="n">
-        <v>2.233333333333333</v>
+        <v>1.483333333333333</v>
       </c>
       <c r="L48" t="n">
-        <v>3.35</v>
+        <v>2.866666666666667</v>
       </c>
       <c r="M48" t="n">
         <v>0.3333333333333333</v>
@@ -2561,37 +2561,37 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C49" t="n">
-        <v>-7.97960536037818</v>
+        <v>-27.7413684328977</v>
       </c>
       <c r="D49" t="n">
-        <v>-18.8049073592717</v>
+        <v>15.6205382398009</v>
       </c>
       <c r="E49" t="n">
-        <v>3000</v>
+        <v>1654.62735</v>
       </c>
       <c r="F49" t="n">
-        <v>0.0269200000000005</v>
+        <v>5.15388</v>
       </c>
       <c r="G49" t="n">
-        <v>2.233333333333333</v>
+        <v>7.266666666666667</v>
       </c>
       <c r="H49" t="n">
-        <v>3.35</v>
+        <v>8.350000000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>2.233333333333333</v>
+        <v>7.266666666666667</v>
       </c>
       <c r="J49" t="n">
-        <v>3.35</v>
+        <v>8.350000000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>2.233333333333333</v>
+        <v>7.266666666666667</v>
       </c>
       <c r="L49" t="n">
-        <v>3.35</v>
+        <v>8.350000000000001</v>
       </c>
       <c r="M49" t="n">
         <v>0.3333333333333333</v>
@@ -2605,37 +2605,37 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C50" t="n">
-        <v>-7.97960536037818</v>
+        <v>-27.7413684328977</v>
       </c>
       <c r="D50" t="n">
-        <v>-18.8049073592717</v>
+        <v>15.6205382398009</v>
       </c>
       <c r="E50" t="n">
-        <v>341.8013000000001</v>
+        <v>1654.62735</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>5.15388</v>
       </c>
       <c r="G50" t="n">
-        <v>2.233333333333333</v>
+        <v>7.266666666666667</v>
       </c>
       <c r="H50" t="n">
-        <v>3.35</v>
+        <v>8.350000000000001</v>
       </c>
       <c r="I50" t="n">
-        <v>2.233333333333333</v>
+        <v>7.266666666666667</v>
       </c>
       <c r="J50" t="n">
-        <v>3.35</v>
+        <v>8.350000000000001</v>
       </c>
       <c r="K50" t="n">
-        <v>2.233333333333333</v>
+        <v>7.266666666666667</v>
       </c>
       <c r="L50" t="n">
-        <v>3.35</v>
+        <v>8.350000000000001</v>
       </c>
       <c r="M50" t="n">
         <v>0.3333333333333333</v>
@@ -2649,37 +2649,37 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C51" t="n">
-        <v>18.151206181933</v>
+        <v>35.9798551608321</v>
       </c>
       <c r="D51" t="n">
-        <v>-13.637299694184</v>
+        <v>-8.834846436336671</v>
       </c>
       <c r="E51" t="n">
-        <v>3000</v>
+        <v>564.949</v>
       </c>
       <c r="F51" t="n">
-        <v>13.61688</v>
+        <v>1.8194</v>
       </c>
       <c r="G51" t="n">
-        <v>8.883333333333333</v>
+        <v>1.416666666666666</v>
       </c>
       <c r="H51" t="n">
-        <v>10.28333333333333</v>
+        <v>2.716666666666667</v>
       </c>
       <c r="I51" t="n">
-        <v>8.883333333333333</v>
+        <v>1.416666666666666</v>
       </c>
       <c r="J51" t="n">
-        <v>10.28333333333333</v>
+        <v>2.716666666666667</v>
       </c>
       <c r="K51" t="n">
-        <v>8.883333333333333</v>
+        <v>1.416666666666666</v>
       </c>
       <c r="L51" t="n">
-        <v>10.28333333333333</v>
+        <v>2.716666666666667</v>
       </c>
       <c r="M51" t="n">
         <v>0.3333333333333333</v>
@@ -2693,37 +2693,37 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C52" t="n">
-        <v>18.151206181933</v>
+        <v>-19.8657669761891</v>
       </c>
       <c r="D52" t="n">
-        <v>-13.637299694184</v>
+        <v>8.245091757030799</v>
       </c>
       <c r="E52" t="n">
-        <v>2061.5807</v>
+        <v>1261.7326</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>4.06727</v>
       </c>
       <c r="G52" t="n">
-        <v>8.883333333333333</v>
+        <v>2.466666666666667</v>
       </c>
       <c r="H52" t="n">
-        <v>10.28333333333333</v>
+        <v>3.566666666666666</v>
       </c>
       <c r="I52" t="n">
-        <v>8.883333333333333</v>
+        <v>2.466666666666667</v>
       </c>
       <c r="J52" t="n">
-        <v>10.28333333333333</v>
+        <v>3.566666666666666</v>
       </c>
       <c r="K52" t="n">
-        <v>8.883333333333333</v>
+        <v>2.466666666666667</v>
       </c>
       <c r="L52" t="n">
-        <v>10.28333333333333</v>
+        <v>3.566666666666666</v>
       </c>
       <c r="M52" t="n">
         <v>0.3333333333333333</v>
@@ -2737,37 +2737,37 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C53" t="n">
-        <v>21.590843242742</v>
+        <v>-14.7593829065892</v>
       </c>
       <c r="D53" t="n">
-        <v>-11.0654463649764</v>
+        <v>-31.3415469493066</v>
       </c>
       <c r="E53" t="n">
-        <v>3000</v>
+        <v>2012.4458</v>
       </c>
       <c r="F53" t="n">
-        <v>11.62403</v>
+        <v>5.003585</v>
       </c>
       <c r="G53" t="n">
-        <v>9.016666666666666</v>
+        <v>6.133333333333333</v>
       </c>
       <c r="H53" t="n">
-        <v>10.48333333333333</v>
+        <v>7</v>
       </c>
       <c r="I53" t="n">
-        <v>9.016666666666666</v>
+        <v>6.133333333333333</v>
       </c>
       <c r="J53" t="n">
-        <v>10.48333333333333</v>
+        <v>7</v>
       </c>
       <c r="K53" t="n">
-        <v>9.016666666666666</v>
+        <v>6.133333333333333</v>
       </c>
       <c r="L53" t="n">
-        <v>10.48333333333333</v>
+        <v>7</v>
       </c>
       <c r="M53" t="n">
         <v>0.3333333333333333</v>
@@ -2781,37 +2781,37 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C54" t="n">
-        <v>21.590843242742</v>
+        <v>-14.7593829065892</v>
       </c>
       <c r="D54" t="n">
-        <v>-11.0654463649764</v>
+        <v>-31.3415469493066</v>
       </c>
       <c r="E54" t="n">
-        <v>1552.3089</v>
+        <v>2012.4458</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>5.003585</v>
       </c>
       <c r="G54" t="n">
-        <v>9.016666666666666</v>
+        <v>6.133333333333333</v>
       </c>
       <c r="H54" t="n">
-        <v>10.48333333333333</v>
+        <v>7</v>
       </c>
       <c r="I54" t="n">
-        <v>9.016666666666666</v>
+        <v>6.133333333333333</v>
       </c>
       <c r="J54" t="n">
-        <v>10.48333333333333</v>
+        <v>7</v>
       </c>
       <c r="K54" t="n">
-        <v>9.016666666666666</v>
+        <v>6.133333333333333</v>
       </c>
       <c r="L54" t="n">
-        <v>10.48333333333333</v>
+        <v>7</v>
       </c>
       <c r="M54" t="n">
         <v>0.3333333333333333</v>
@@ -2825,37 +2825,37 @@
         <v>53</v>
       </c>
       <c r="B55" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C55" t="n">
-        <v>19.4247893328668</v>
+        <v>-25.4478796473256</v>
       </c>
       <c r="D55" t="n">
-        <v>-17.0996049039402</v>
+        <v>8.265874726389081</v>
       </c>
       <c r="E55" t="n">
-        <v>3000</v>
+        <v>2691.1358</v>
       </c>
       <c r="F55" t="n">
-        <v>15</v>
+        <v>7.9507</v>
       </c>
       <c r="G55" t="n">
-        <v>7.616666666666667</v>
+        <v>9.866666666666667</v>
       </c>
       <c r="H55" t="n">
-        <v>8.600000000000001</v>
+        <v>11.06666666666667</v>
       </c>
       <c r="I55" t="n">
-        <v>7.616666666666667</v>
+        <v>9.866666666666667</v>
       </c>
       <c r="J55" t="n">
-        <v>8.600000000000001</v>
+        <v>11.06666666666667</v>
       </c>
       <c r="K55" t="n">
-        <v>7.616666666666667</v>
+        <v>9.866666666666667</v>
       </c>
       <c r="L55" t="n">
-        <v>8.600000000000001</v>
+        <v>11.06666666666667</v>
       </c>
       <c r="M55" t="n">
         <v>0.3333333333333333</v>
@@ -2869,37 +2869,37 @@
         <v>54</v>
       </c>
       <c r="B56" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C56" t="n">
-        <v>19.4247893328668</v>
+        <v>-6.39184845369064</v>
       </c>
       <c r="D56" t="n">
-        <v>-17.0996049039402</v>
+        <v>38.866308384005</v>
       </c>
       <c r="E56" t="n">
-        <v>2799.9256</v>
+        <v>2786.4185</v>
       </c>
       <c r="F56" t="n">
-        <v>3.41337</v>
+        <v>7.85191</v>
       </c>
       <c r="G56" t="n">
-        <v>7.616666666666667</v>
+        <v>4.633333333333333</v>
       </c>
       <c r="H56" t="n">
-        <v>8.600000000000001</v>
+        <v>5.85</v>
       </c>
       <c r="I56" t="n">
-        <v>7.616666666666667</v>
+        <v>4.633333333333333</v>
       </c>
       <c r="J56" t="n">
-        <v>8.600000000000001</v>
+        <v>5.85</v>
       </c>
       <c r="K56" t="n">
-        <v>7.616666666666667</v>
+        <v>4.633333333333333</v>
       </c>
       <c r="L56" t="n">
-        <v>8.600000000000001</v>
+        <v>5.85</v>
       </c>
       <c r="M56" t="n">
         <v>0.3333333333333333</v>
@@ -2913,37 +2913,37 @@
         <v>55</v>
       </c>
       <c r="B57" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C57" t="n">
-        <v>-3.94895297178467</v>
+        <v>-7.97960536037818</v>
       </c>
       <c r="D57" t="n">
-        <v>-34.8007269144264</v>
+        <v>-18.8049073592717</v>
       </c>
       <c r="E57" t="n">
-        <v>3000</v>
+        <v>2113.933766666667</v>
       </c>
       <c r="F57" t="n">
-        <v>10.88662</v>
+        <v>5.008973333333333</v>
       </c>
       <c r="G57" t="n">
-        <v>3.199999999999999</v>
+        <v>2.233333333333333</v>
       </c>
       <c r="H57" t="n">
-        <v>4.183333333333334</v>
+        <v>3.35</v>
       </c>
       <c r="I57" t="n">
-        <v>3.199999999999999</v>
+        <v>2.233333333333333</v>
       </c>
       <c r="J57" t="n">
-        <v>4.183333333333334</v>
+        <v>3.35</v>
       </c>
       <c r="K57" t="n">
-        <v>3.199999999999999</v>
+        <v>2.233333333333333</v>
       </c>
       <c r="L57" t="n">
-        <v>4.183333333333334</v>
+        <v>3.35</v>
       </c>
       <c r="M57" t="n">
         <v>0.3333333333333333</v>
@@ -2957,37 +2957,37 @@
         <v>56</v>
       </c>
       <c r="B58" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C58" t="n">
-        <v>-3.94895297178467</v>
+        <v>-7.97960536037818</v>
       </c>
       <c r="D58" t="n">
-        <v>-34.8007269144264</v>
+        <v>-18.8049073592717</v>
       </c>
       <c r="E58" t="n">
-        <v>319.8397</v>
+        <v>2113.933766666667</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>5.008973333333333</v>
       </c>
       <c r="G58" t="n">
-        <v>3.199999999999999</v>
+        <v>2.233333333333333</v>
       </c>
       <c r="H58" t="n">
-        <v>4.183333333333334</v>
+        <v>3.35</v>
       </c>
       <c r="I58" t="n">
-        <v>3.199999999999999</v>
+        <v>2.233333333333333</v>
       </c>
       <c r="J58" t="n">
-        <v>4.183333333333334</v>
+        <v>3.35</v>
       </c>
       <c r="K58" t="n">
-        <v>3.199999999999999</v>
+        <v>2.233333333333333</v>
       </c>
       <c r="L58" t="n">
-        <v>4.183333333333334</v>
+        <v>3.35</v>
       </c>
       <c r="M58" t="n">
         <v>0.3333333333333333</v>
@@ -3001,37 +3001,37 @@
         <v>57</v>
       </c>
       <c r="B59" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C59" t="n">
-        <v>10.5334022336896</v>
+        <v>-7.97960536037818</v>
       </c>
       <c r="D59" t="n">
-        <v>17.621635259999</v>
+        <v>-18.8049073592717</v>
       </c>
       <c r="E59" t="n">
-        <v>2784.5018</v>
+        <v>2113.933766666667</v>
       </c>
       <c r="F59" t="n">
-        <v>8.09606</v>
+        <v>5.008973333333333</v>
       </c>
       <c r="G59" t="n">
-        <v>10.91666666666667</v>
+        <v>2.233333333333333</v>
       </c>
       <c r="H59" t="n">
-        <v>11.91666666666667</v>
+        <v>3.35</v>
       </c>
       <c r="I59" t="n">
-        <v>10.91666666666667</v>
+        <v>2.233333333333333</v>
       </c>
       <c r="J59" t="n">
-        <v>11.91666666666667</v>
+        <v>3.35</v>
       </c>
       <c r="K59" t="n">
-        <v>10.91666666666667</v>
+        <v>2.233333333333333</v>
       </c>
       <c r="L59" t="n">
-        <v>11.91666666666667</v>
+        <v>3.35</v>
       </c>
       <c r="M59" t="n">
         <v>0.3333333333333333</v>
@@ -3045,37 +3045,37 @@
         <v>58</v>
       </c>
       <c r="B60" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C60" t="n">
-        <v>5.11105840595424</v>
+        <v>18.151206181933</v>
       </c>
       <c r="D60" t="n">
-        <v>10.9732978458469</v>
+        <v>-13.637299694184</v>
       </c>
       <c r="E60" t="n">
-        <v>3000</v>
+        <v>2530.79035</v>
       </c>
       <c r="F60" t="n">
-        <v>15</v>
+        <v>6.80844</v>
       </c>
       <c r="G60" t="n">
-        <v>8.100000000000001</v>
+        <v>8.883333333333333</v>
       </c>
       <c r="H60" t="n">
-        <v>9.466666666666665</v>
+        <v>10.28333333333333</v>
       </c>
       <c r="I60" t="n">
-        <v>8.100000000000001</v>
+        <v>8.883333333333333</v>
       </c>
       <c r="J60" t="n">
-        <v>9.466666666666665</v>
+        <v>10.28333333333333</v>
       </c>
       <c r="K60" t="n">
-        <v>8.100000000000001</v>
+        <v>8.883333333333333</v>
       </c>
       <c r="L60" t="n">
-        <v>9.466666666666665</v>
+        <v>10.28333333333333</v>
       </c>
       <c r="M60" t="n">
         <v>0.3333333333333333</v>
@@ -3089,37 +3089,37 @@
         <v>59</v>
       </c>
       <c r="B61" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C61" t="n">
-        <v>5.11105840595424</v>
+        <v>18.151206181933</v>
       </c>
       <c r="D61" t="n">
-        <v>10.9732978458469</v>
+        <v>-13.637299694184</v>
       </c>
       <c r="E61" t="n">
-        <v>3000</v>
+        <v>2530.79035</v>
       </c>
       <c r="F61" t="n">
-        <v>4.54918</v>
+        <v>6.80844</v>
       </c>
       <c r="G61" t="n">
-        <v>8.100000000000001</v>
+        <v>8.883333333333333</v>
       </c>
       <c r="H61" t="n">
-        <v>9.466666666666665</v>
+        <v>10.28333333333333</v>
       </c>
       <c r="I61" t="n">
-        <v>8.100000000000001</v>
+        <v>8.883333333333333</v>
       </c>
       <c r="J61" t="n">
-        <v>9.466666666666665</v>
+        <v>10.28333333333333</v>
       </c>
       <c r="K61" t="n">
-        <v>8.100000000000001</v>
+        <v>8.883333333333333</v>
       </c>
       <c r="L61" t="n">
-        <v>9.466666666666665</v>
+        <v>10.28333333333333</v>
       </c>
       <c r="M61" t="n">
         <v>0.3333333333333333</v>
@@ -3133,37 +3133,37 @@
         <v>60</v>
       </c>
       <c r="B62" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C62" t="n">
-        <v>5.11105840595424</v>
+        <v>21.590843242742</v>
       </c>
       <c r="D62" t="n">
-        <v>10.9732978458469</v>
+        <v>-11.0654463649764</v>
       </c>
       <c r="E62" t="n">
-        <v>2598.7276</v>
+        <v>2276.15445</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>5.812015</v>
       </c>
       <c r="G62" t="n">
-        <v>8.100000000000001</v>
+        <v>9.016666666666666</v>
       </c>
       <c r="H62" t="n">
-        <v>9.466666666666665</v>
+        <v>10.48333333333333</v>
       </c>
       <c r="I62" t="n">
-        <v>8.100000000000001</v>
+        <v>9.016666666666666</v>
       </c>
       <c r="J62" t="n">
-        <v>9.466666666666665</v>
+        <v>10.48333333333333</v>
       </c>
       <c r="K62" t="n">
-        <v>8.100000000000001</v>
+        <v>9.016666666666666</v>
       </c>
       <c r="L62" t="n">
-        <v>9.466666666666665</v>
+        <v>10.48333333333333</v>
       </c>
       <c r="M62" t="n">
         <v>0.3333333333333333</v>
@@ -3177,37 +3177,37 @@
         <v>61</v>
       </c>
       <c r="B63" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C63" t="n">
-        <v>30.4883697362318</v>
+        <v>21.590843242742</v>
       </c>
       <c r="D63" t="n">
-        <v>13.04953073461</v>
+        <v>-11.0654463649764</v>
       </c>
       <c r="E63" t="n">
-        <v>3000</v>
+        <v>2276.15445</v>
       </c>
       <c r="F63" t="n">
-        <v>13.53895</v>
+        <v>5.812015</v>
       </c>
       <c r="G63" t="n">
-        <v>5.1</v>
+        <v>9.016666666666666</v>
       </c>
       <c r="H63" t="n">
-        <v>6.033333333333333</v>
+        <v>10.48333333333333</v>
       </c>
       <c r="I63" t="n">
-        <v>5.1</v>
+        <v>9.016666666666666</v>
       </c>
       <c r="J63" t="n">
-        <v>6.033333333333333</v>
+        <v>10.48333333333333</v>
       </c>
       <c r="K63" t="n">
-        <v>5.1</v>
+        <v>9.016666666666666</v>
       </c>
       <c r="L63" t="n">
-        <v>6.033333333333333</v>
+        <v>10.48333333333333</v>
       </c>
       <c r="M63" t="n">
         <v>0.3333333333333333</v>
@@ -3221,37 +3221,37 @@
         <v>62</v>
       </c>
       <c r="B64" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C64" t="n">
-        <v>30.4883697362318</v>
+        <v>19.4247893328668</v>
       </c>
       <c r="D64" t="n">
-        <v>13.04953073461</v>
+        <v>-17.0996049039402</v>
       </c>
       <c r="E64" t="n">
-        <v>1486.836</v>
+        <v>2899.9628</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>9.206685</v>
       </c>
       <c r="G64" t="n">
-        <v>5.1</v>
+        <v>7.616666666666667</v>
       </c>
       <c r="H64" t="n">
-        <v>6.033333333333333</v>
+        <v>8.600000000000001</v>
       </c>
       <c r="I64" t="n">
-        <v>5.1</v>
+        <v>7.616666666666667</v>
       </c>
       <c r="J64" t="n">
-        <v>6.033333333333333</v>
+        <v>8.600000000000001</v>
       </c>
       <c r="K64" t="n">
-        <v>5.1</v>
+        <v>7.616666666666667</v>
       </c>
       <c r="L64" t="n">
-        <v>6.033333333333333</v>
+        <v>8.600000000000001</v>
       </c>
       <c r="M64" t="n">
         <v>0.3333333333333333</v>
@@ -3265,37 +3265,37 @@
         <v>63</v>
       </c>
       <c r="B65" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C65" t="n">
-        <v>-19.4837889125212</v>
+        <v>19.4247893328668</v>
       </c>
       <c r="D65" t="n">
-        <v>-8.728925143928519</v>
+        <v>-17.0996049039402</v>
       </c>
       <c r="E65" t="n">
-        <v>3000</v>
+        <v>2899.9628</v>
       </c>
       <c r="F65" t="n">
-        <v>15</v>
+        <v>9.206685</v>
       </c>
       <c r="G65" t="n">
-        <v>12.15</v>
+        <v>7.616666666666667</v>
       </c>
       <c r="H65" t="n">
-        <v>12.96666666666667</v>
+        <v>8.600000000000001</v>
       </c>
       <c r="I65" t="n">
-        <v>12.15</v>
+        <v>7.616666666666667</v>
       </c>
       <c r="J65" t="n">
-        <v>12.96666666666667</v>
+        <v>8.600000000000001</v>
       </c>
       <c r="K65" t="n">
-        <v>12.15</v>
+        <v>7.616666666666667</v>
       </c>
       <c r="L65" t="n">
-        <v>12.96666666666667</v>
+        <v>8.600000000000001</v>
       </c>
       <c r="M65" t="n">
         <v>0.3333333333333333</v>
@@ -3309,37 +3309,37 @@
         <v>64</v>
       </c>
       <c r="B66" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C66" t="n">
-        <v>-19.4837889125212</v>
+        <v>-3.94895297178467</v>
       </c>
       <c r="D66" t="n">
-        <v>-8.728925143928519</v>
+        <v>-34.8007269144264</v>
       </c>
       <c r="E66" t="n">
-        <v>3000</v>
+        <v>1659.91985</v>
       </c>
       <c r="F66" t="n">
-        <v>6.49775</v>
+        <v>5.44331</v>
       </c>
       <c r="G66" t="n">
-        <v>12.15</v>
+        <v>3.199999999999999</v>
       </c>
       <c r="H66" t="n">
-        <v>12.96666666666667</v>
+        <v>4.183333333333334</v>
       </c>
       <c r="I66" t="n">
-        <v>12.15</v>
+        <v>3.199999999999999</v>
       </c>
       <c r="J66" t="n">
-        <v>12.96666666666667</v>
+        <v>4.183333333333334</v>
       </c>
       <c r="K66" t="n">
-        <v>12.15</v>
+        <v>3.199999999999999</v>
       </c>
       <c r="L66" t="n">
-        <v>12.96666666666667</v>
+        <v>4.183333333333334</v>
       </c>
       <c r="M66" t="n">
         <v>0.3333333333333333</v>
@@ -3353,37 +3353,37 @@
         <v>65</v>
       </c>
       <c r="B67" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C67" t="n">
-        <v>-19.4837889125212</v>
+        <v>-3.94895297178467</v>
       </c>
       <c r="D67" t="n">
-        <v>-8.728925143928519</v>
+        <v>-34.8007269144264</v>
       </c>
       <c r="E67" t="n">
-        <v>1952.3101</v>
+        <v>1659.91985</v>
       </c>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>5.44331</v>
       </c>
       <c r="G67" t="n">
-        <v>12.15</v>
+        <v>3.199999999999999</v>
       </c>
       <c r="H67" t="n">
-        <v>12.96666666666667</v>
+        <v>4.183333333333334</v>
       </c>
       <c r="I67" t="n">
-        <v>12.15</v>
+        <v>3.199999999999999</v>
       </c>
       <c r="J67" t="n">
-        <v>12.96666666666667</v>
+        <v>4.183333333333334</v>
       </c>
       <c r="K67" t="n">
-        <v>12.15</v>
+        <v>3.199999999999999</v>
       </c>
       <c r="L67" t="n">
-        <v>12.96666666666667</v>
+        <v>4.183333333333334</v>
       </c>
       <c r="M67" t="n">
         <v>0.3333333333333333</v>
@@ -3397,37 +3397,37 @@
         <v>66</v>
       </c>
       <c r="B68" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C68" t="n">
-        <v>-8.69400896691041</v>
+        <v>10.5334022336896</v>
       </c>
       <c r="D68" t="n">
-        <v>16.0355565510262</v>
+        <v>17.621635259999</v>
       </c>
       <c r="E68" t="n">
-        <v>3000</v>
+        <v>2784.5018</v>
       </c>
       <c r="F68" t="n">
-        <v>9.759309999999999</v>
+        <v>8.09606</v>
       </c>
       <c r="G68" t="n">
-        <v>9.550000000000001</v>
+        <v>10.91666666666667</v>
       </c>
       <c r="H68" t="n">
-        <v>10.65</v>
+        <v>11.91666666666667</v>
       </c>
       <c r="I68" t="n">
-        <v>9.550000000000001</v>
+        <v>10.91666666666667</v>
       </c>
       <c r="J68" t="n">
-        <v>10.65</v>
+        <v>11.91666666666667</v>
       </c>
       <c r="K68" t="n">
-        <v>9.550000000000001</v>
+        <v>10.91666666666667</v>
       </c>
       <c r="L68" t="n">
-        <v>10.65</v>
+        <v>11.91666666666667</v>
       </c>
       <c r="M68" t="n">
         <v>0.3333333333333333</v>
@@ -3441,37 +3441,37 @@
         <v>67</v>
       </c>
       <c r="B69" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C69" t="n">
-        <v>-8.69400896691041</v>
+        <v>5.11105840595424</v>
       </c>
       <c r="D69" t="n">
-        <v>16.0355565510262</v>
+        <v>10.9732978458469</v>
       </c>
       <c r="E69" t="n">
-        <v>408.3843000000002</v>
+        <v>2866.242533333334</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>6.516393333333333</v>
       </c>
       <c r="G69" t="n">
-        <v>9.550000000000001</v>
+        <v>8.100000000000001</v>
       </c>
       <c r="H69" t="n">
-        <v>10.65</v>
+        <v>9.466666666666665</v>
       </c>
       <c r="I69" t="n">
-        <v>9.550000000000001</v>
+        <v>8.100000000000001</v>
       </c>
       <c r="J69" t="n">
-        <v>10.65</v>
+        <v>9.466666666666665</v>
       </c>
       <c r="K69" t="n">
-        <v>9.550000000000001</v>
+        <v>8.100000000000001</v>
       </c>
       <c r="L69" t="n">
-        <v>10.65</v>
+        <v>9.466666666666665</v>
       </c>
       <c r="M69" t="n">
         <v>0.3333333333333333</v>
@@ -3485,37 +3485,37 @@
         <v>68</v>
       </c>
       <c r="B70" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C70" t="n">
-        <v>-9.42229186702531</v>
+        <v>5.11105840595424</v>
       </c>
       <c r="D70" t="n">
-        <v>-18.809064939498</v>
+        <v>10.9732978458469</v>
       </c>
       <c r="E70" t="n">
-        <v>3000</v>
+        <v>2866.242533333334</v>
       </c>
       <c r="F70" t="n">
-        <v>15</v>
+        <v>6.516393333333333</v>
       </c>
       <c r="G70" t="n">
-        <v>7.083333333333334</v>
+        <v>8.100000000000001</v>
       </c>
       <c r="H70" t="n">
-        <v>8.533333333333335</v>
+        <v>9.466666666666665</v>
       </c>
       <c r="I70" t="n">
-        <v>7.083333333333334</v>
+        <v>8.100000000000001</v>
       </c>
       <c r="J70" t="n">
-        <v>8.533333333333335</v>
+        <v>9.466666666666665</v>
       </c>
       <c r="K70" t="n">
-        <v>7.083333333333334</v>
+        <v>8.100000000000001</v>
       </c>
       <c r="L70" t="n">
-        <v>8.533333333333335</v>
+        <v>9.466666666666665</v>
       </c>
       <c r="M70" t="n">
         <v>0.3333333333333333</v>
@@ -3529,37 +3529,37 @@
         <v>69</v>
       </c>
       <c r="B71" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C71" t="n">
-        <v>-9.42229186702531</v>
+        <v>5.11105840595424</v>
       </c>
       <c r="D71" t="n">
-        <v>-18.809064939498</v>
+        <v>10.9732978458469</v>
       </c>
       <c r="E71" t="n">
-        <v>3000</v>
+        <v>2866.242533333334</v>
       </c>
       <c r="F71" t="n">
-        <v>2.089220000000001</v>
+        <v>6.516393333333333</v>
       </c>
       <c r="G71" t="n">
-        <v>7.083333333333334</v>
+        <v>8.100000000000001</v>
       </c>
       <c r="H71" t="n">
-        <v>8.533333333333335</v>
+        <v>9.466666666666665</v>
       </c>
       <c r="I71" t="n">
-        <v>7.083333333333334</v>
+        <v>8.100000000000001</v>
       </c>
       <c r="J71" t="n">
-        <v>8.533333333333335</v>
+        <v>9.466666666666665</v>
       </c>
       <c r="K71" t="n">
-        <v>7.083333333333334</v>
+        <v>8.100000000000001</v>
       </c>
       <c r="L71" t="n">
-        <v>8.533333333333335</v>
+        <v>9.466666666666665</v>
       </c>
       <c r="M71" t="n">
         <v>0.3333333333333333</v>
@@ -3573,37 +3573,37 @@
         <v>70</v>
       </c>
       <c r="B72" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C72" t="n">
-        <v>-9.42229186702531</v>
+        <v>30.4883697362318</v>
       </c>
       <c r="D72" t="n">
-        <v>-18.809064939498</v>
+        <v>13.04953073461</v>
       </c>
       <c r="E72" t="n">
-        <v>715.3882000000003</v>
+        <v>2243.418</v>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>6.769475</v>
       </c>
       <c r="G72" t="n">
-        <v>7.083333333333334</v>
+        <v>5.1</v>
       </c>
       <c r="H72" t="n">
-        <v>8.533333333333335</v>
+        <v>6.033333333333333</v>
       </c>
       <c r="I72" t="n">
-        <v>7.083333333333334</v>
+        <v>5.1</v>
       </c>
       <c r="J72" t="n">
-        <v>8.533333333333335</v>
+        <v>6.033333333333333</v>
       </c>
       <c r="K72" t="n">
-        <v>7.083333333333334</v>
+        <v>5.1</v>
       </c>
       <c r="L72" t="n">
-        <v>8.533333333333335</v>
+        <v>6.033333333333333</v>
       </c>
       <c r="M72" t="n">
         <v>0.3333333333333333</v>
@@ -3617,37 +3617,37 @@
         <v>71</v>
       </c>
       <c r="B73" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C73" t="n">
-        <v>16.6645391539304</v>
+        <v>30.4883697362318</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.259417867939575</v>
+        <v>13.04953073461</v>
       </c>
       <c r="E73" t="n">
-        <v>3000</v>
+        <v>2243.418</v>
       </c>
       <c r="F73" t="n">
-        <v>15</v>
+        <v>6.769475</v>
       </c>
       <c r="G73" t="n">
-        <v>9.983333333333334</v>
+        <v>5.1</v>
       </c>
       <c r="H73" t="n">
-        <v>10.86666666666667</v>
+        <v>6.033333333333333</v>
       </c>
       <c r="I73" t="n">
-        <v>9.983333333333334</v>
+        <v>5.1</v>
       </c>
       <c r="J73" t="n">
-        <v>10.86666666666667</v>
+        <v>6.033333333333333</v>
       </c>
       <c r="K73" t="n">
-        <v>9.983333333333334</v>
+        <v>5.1</v>
       </c>
       <c r="L73" t="n">
-        <v>10.86666666666667</v>
+        <v>6.033333333333333</v>
       </c>
       <c r="M73" t="n">
         <v>0.3333333333333333</v>
@@ -3661,37 +3661,37 @@
         <v>72</v>
       </c>
       <c r="B74" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C74" t="n">
-        <v>16.6645391539304</v>
+        <v>-19.4837889125212</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.259417867939575</v>
+        <v>-8.728925143928519</v>
       </c>
       <c r="E74" t="n">
-        <v>3000</v>
+        <v>2650.770033333333</v>
       </c>
       <c r="F74" t="n">
-        <v>3.75874</v>
+        <v>7.165916666666667</v>
       </c>
       <c r="G74" t="n">
-        <v>9.983333333333334</v>
+        <v>12.15</v>
       </c>
       <c r="H74" t="n">
-        <v>10.86666666666667</v>
+        <v>12.96666666666667</v>
       </c>
       <c r="I74" t="n">
-        <v>9.983333333333334</v>
+        <v>12.15</v>
       </c>
       <c r="J74" t="n">
-        <v>10.86666666666667</v>
+        <v>12.96666666666667</v>
       </c>
       <c r="K74" t="n">
-        <v>9.983333333333334</v>
+        <v>12.15</v>
       </c>
       <c r="L74" t="n">
-        <v>10.86666666666667</v>
+        <v>12.96666666666667</v>
       </c>
       <c r="M74" t="n">
         <v>0.3333333333333333</v>
@@ -3705,37 +3705,37 @@
         <v>73</v>
       </c>
       <c r="B75" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C75" t="n">
-        <v>16.6645391539304</v>
+        <v>-19.4837889125212</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.259417867939575</v>
+        <v>-8.728925143928519</v>
       </c>
       <c r="E75" t="n">
-        <v>963.8459000000003</v>
+        <v>2650.770033333333</v>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>7.165916666666667</v>
       </c>
       <c r="G75" t="n">
-        <v>9.983333333333334</v>
+        <v>12.15</v>
       </c>
       <c r="H75" t="n">
-        <v>10.86666666666667</v>
+        <v>12.96666666666667</v>
       </c>
       <c r="I75" t="n">
-        <v>9.983333333333334</v>
+        <v>12.15</v>
       </c>
       <c r="J75" t="n">
-        <v>10.86666666666667</v>
+        <v>12.96666666666667</v>
       </c>
       <c r="K75" t="n">
-        <v>9.983333333333334</v>
+        <v>12.15</v>
       </c>
       <c r="L75" t="n">
-        <v>10.86666666666667</v>
+        <v>12.96666666666667</v>
       </c>
       <c r="M75" t="n">
         <v>0.3333333333333333</v>
@@ -3749,37 +3749,37 @@
         <v>74</v>
       </c>
       <c r="B76" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C76" t="n">
-        <v>-7.26957106603941</v>
+        <v>-19.4837889125212</v>
       </c>
       <c r="D76" t="n">
-        <v>-30.7450666987351</v>
+        <v>-8.728925143928519</v>
       </c>
       <c r="E76" t="n">
-        <v>3000</v>
+        <v>2650.770033333333</v>
       </c>
       <c r="F76" t="n">
-        <v>15</v>
+        <v>7.165916666666667</v>
       </c>
       <c r="G76" t="n">
-        <v>9.333333333333332</v>
+        <v>12.15</v>
       </c>
       <c r="H76" t="n">
-        <v>10.73333333333333</v>
+        <v>12.96666666666667</v>
       </c>
       <c r="I76" t="n">
-        <v>9.333333333333332</v>
+        <v>12.15</v>
       </c>
       <c r="J76" t="n">
-        <v>10.73333333333333</v>
+        <v>12.96666666666667</v>
       </c>
       <c r="K76" t="n">
-        <v>9.333333333333332</v>
+        <v>12.15</v>
       </c>
       <c r="L76" t="n">
-        <v>10.73333333333333</v>
+        <v>12.96666666666667</v>
       </c>
       <c r="M76" t="n">
         <v>0.3333333333333333</v>
@@ -3793,37 +3793,37 @@
         <v>75</v>
       </c>
       <c r="B77" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C77" t="n">
-        <v>-7.26957106603941</v>
+        <v>-8.69400896691041</v>
       </c>
       <c r="D77" t="n">
-        <v>-30.7450666987351</v>
+        <v>16.0355565510262</v>
       </c>
       <c r="E77" t="n">
-        <v>3000</v>
+        <v>1704.19215</v>
       </c>
       <c r="F77" t="n">
-        <v>4.672920000000001</v>
+        <v>4.879655</v>
       </c>
       <c r="G77" t="n">
-        <v>9.333333333333332</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="H77" t="n">
-        <v>10.73333333333333</v>
+        <v>10.65</v>
       </c>
       <c r="I77" t="n">
-        <v>9.333333333333332</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="J77" t="n">
-        <v>10.73333333333333</v>
+        <v>10.65</v>
       </c>
       <c r="K77" t="n">
-        <v>9.333333333333332</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="L77" t="n">
-        <v>10.73333333333333</v>
+        <v>10.65</v>
       </c>
       <c r="M77" t="n">
         <v>0.3333333333333333</v>
@@ -3837,37 +3837,37 @@
         <v>76</v>
       </c>
       <c r="B78" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C78" t="n">
-        <v>-7.26957106603941</v>
+        <v>-8.69400896691041</v>
       </c>
       <c r="D78" t="n">
-        <v>-30.7450666987351</v>
+        <v>16.0355565510262</v>
       </c>
       <c r="E78" t="n">
-        <v>1418.6583</v>
+        <v>1704.19215</v>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>4.879655</v>
       </c>
       <c r="G78" t="n">
-        <v>9.333333333333332</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="H78" t="n">
-        <v>10.73333333333333</v>
+        <v>10.65</v>
       </c>
       <c r="I78" t="n">
-        <v>9.333333333333332</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="J78" t="n">
-        <v>10.73333333333333</v>
+        <v>10.65</v>
       </c>
       <c r="K78" t="n">
-        <v>9.333333333333332</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="L78" t="n">
-        <v>10.73333333333333</v>
+        <v>10.65</v>
       </c>
       <c r="M78" t="n">
         <v>0.3333333333333333</v>
@@ -3881,37 +3881,37 @@
         <v>77</v>
       </c>
       <c r="B79" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C79" t="n">
-        <v>-30.4738708628108</v>
+        <v>-9.42229186702531</v>
       </c>
       <c r="D79" t="n">
-        <v>0.417718230968227</v>
+        <v>-18.809064939498</v>
       </c>
       <c r="E79" t="n">
-        <v>3000</v>
+        <v>2238.462733333333</v>
       </c>
       <c r="F79" t="n">
-        <v>15</v>
+        <v>5.696406666666667</v>
       </c>
       <c r="G79" t="n">
-        <v>9.916666666666668</v>
+        <v>7.083333333333334</v>
       </c>
       <c r="H79" t="n">
-        <v>11.2</v>
+        <v>8.533333333333335</v>
       </c>
       <c r="I79" t="n">
-        <v>9.916666666666668</v>
+        <v>7.083333333333334</v>
       </c>
       <c r="J79" t="n">
-        <v>11.2</v>
+        <v>8.533333333333335</v>
       </c>
       <c r="K79" t="n">
-        <v>9.916666666666668</v>
+        <v>7.083333333333334</v>
       </c>
       <c r="L79" t="n">
-        <v>11.2</v>
+        <v>8.533333333333335</v>
       </c>
       <c r="M79" t="n">
         <v>0.3333333333333333</v>
@@ -3925,37 +3925,37 @@
         <v>78</v>
       </c>
       <c r="B80" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C80" t="n">
-        <v>-30.4738708628108</v>
+        <v>-9.42229186702531</v>
       </c>
       <c r="D80" t="n">
-        <v>0.417718230968227</v>
+        <v>-18.809064939498</v>
       </c>
       <c r="E80" t="n">
-        <v>3000</v>
+        <v>2238.462733333333</v>
       </c>
       <c r="F80" t="n">
-        <v>15</v>
+        <v>5.696406666666667</v>
       </c>
       <c r="G80" t="n">
-        <v>9.916666666666668</v>
+        <v>7.083333333333334</v>
       </c>
       <c r="H80" t="n">
-        <v>11.2</v>
+        <v>8.533333333333335</v>
       </c>
       <c r="I80" t="n">
-        <v>9.916666666666668</v>
+        <v>7.083333333333334</v>
       </c>
       <c r="J80" t="n">
-        <v>11.2</v>
+        <v>8.533333333333335</v>
       </c>
       <c r="K80" t="n">
-        <v>9.916666666666668</v>
+        <v>7.083333333333334</v>
       </c>
       <c r="L80" t="n">
-        <v>11.2</v>
+        <v>8.533333333333335</v>
       </c>
       <c r="M80" t="n">
         <v>0.3333333333333333</v>
@@ -3969,37 +3969,37 @@
         <v>79</v>
       </c>
       <c r="B81" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C81" t="n">
-        <v>-30.4738708628108</v>
+        <v>-9.42229186702531</v>
       </c>
       <c r="D81" t="n">
-        <v>0.417718230968227</v>
+        <v>-18.809064939498</v>
       </c>
       <c r="E81" t="n">
-        <v>3000</v>
+        <v>2238.462733333333</v>
       </c>
       <c r="F81" t="n">
-        <v>0.798490000000001</v>
+        <v>5.696406666666667</v>
       </c>
       <c r="G81" t="n">
-        <v>9.916666666666668</v>
+        <v>7.083333333333334</v>
       </c>
       <c r="H81" t="n">
-        <v>11.2</v>
+        <v>8.533333333333335</v>
       </c>
       <c r="I81" t="n">
-        <v>9.916666666666668</v>
+        <v>7.083333333333334</v>
       </c>
       <c r="J81" t="n">
-        <v>11.2</v>
+        <v>8.533333333333335</v>
       </c>
       <c r="K81" t="n">
-        <v>9.916666666666668</v>
+        <v>7.083333333333334</v>
       </c>
       <c r="L81" t="n">
-        <v>11.2</v>
+        <v>8.533333333333335</v>
       </c>
       <c r="M81" t="n">
         <v>0.3333333333333333</v>
@@ -4013,37 +4013,37 @@
         <v>80</v>
       </c>
       <c r="B82" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C82" t="n">
-        <v>-30.4738708628108</v>
+        <v>16.6645391539304</v>
       </c>
       <c r="D82" t="n">
-        <v>0.417718230968227</v>
+        <v>-0.259417867939575</v>
       </c>
       <c r="E82" t="n">
-        <v>3000</v>
+        <v>2321.281966666667</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>6.252913333333333</v>
       </c>
       <c r="G82" t="n">
-        <v>9.916666666666668</v>
+        <v>9.983333333333334</v>
       </c>
       <c r="H82" t="n">
-        <v>11.2</v>
+        <v>10.86666666666667</v>
       </c>
       <c r="I82" t="n">
-        <v>9.916666666666668</v>
+        <v>9.983333333333334</v>
       </c>
       <c r="J82" t="n">
-        <v>11.2</v>
+        <v>10.86666666666667</v>
       </c>
       <c r="K82" t="n">
-        <v>9.916666666666668</v>
+        <v>9.983333333333334</v>
       </c>
       <c r="L82" t="n">
-        <v>11.2</v>
+        <v>10.86666666666667</v>
       </c>
       <c r="M82" t="n">
         <v>0.3333333333333333</v>
@@ -4057,37 +4057,37 @@
         <v>81</v>
       </c>
       <c r="B83" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C83" t="n">
-        <v>-30.4738708628108</v>
+        <v>16.6645391539304</v>
       </c>
       <c r="D83" t="n">
-        <v>0.417718230968227</v>
+        <v>-0.259417867939575</v>
       </c>
       <c r="E83" t="n">
-        <v>197.6473000000005</v>
+        <v>2321.281966666667</v>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>6.252913333333333</v>
       </c>
       <c r="G83" t="n">
-        <v>9.916666666666668</v>
+        <v>9.983333333333334</v>
       </c>
       <c r="H83" t="n">
-        <v>11.2</v>
+        <v>10.86666666666667</v>
       </c>
       <c r="I83" t="n">
-        <v>9.916666666666668</v>
+        <v>9.983333333333334</v>
       </c>
       <c r="J83" t="n">
-        <v>11.2</v>
+        <v>10.86666666666667</v>
       </c>
       <c r="K83" t="n">
-        <v>9.916666666666668</v>
+        <v>9.983333333333334</v>
       </c>
       <c r="L83" t="n">
-        <v>11.2</v>
+        <v>10.86666666666667</v>
       </c>
       <c r="M83" t="n">
         <v>0.3333333333333333</v>
@@ -4101,37 +4101,37 @@
         <v>82</v>
       </c>
       <c r="B84" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C84" t="n">
-        <v>30.9734492073973</v>
+        <v>16.6645391539304</v>
       </c>
       <c r="D84" t="n">
-        <v>-24.4269327966448</v>
+        <v>-0.259417867939575</v>
       </c>
       <c r="E84" t="n">
-        <v>3000</v>
+        <v>2321.281966666667</v>
       </c>
       <c r="F84" t="n">
-        <v>15</v>
+        <v>6.252913333333333</v>
       </c>
       <c r="G84" t="n">
-        <v>5.833333333333334</v>
+        <v>9.983333333333334</v>
       </c>
       <c r="H84" t="n">
-        <v>7.15</v>
+        <v>10.86666666666667</v>
       </c>
       <c r="I84" t="n">
-        <v>5.833333333333334</v>
+        <v>9.983333333333334</v>
       </c>
       <c r="J84" t="n">
-        <v>7.15</v>
+        <v>10.86666666666667</v>
       </c>
       <c r="K84" t="n">
-        <v>5.833333333333334</v>
+        <v>9.983333333333334</v>
       </c>
       <c r="L84" t="n">
-        <v>7.15</v>
+        <v>10.86666666666667</v>
       </c>
       <c r="M84" t="n">
         <v>0.3333333333333333</v>
@@ -4145,37 +4145,37 @@
         <v>83</v>
       </c>
       <c r="B85" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C85" t="n">
-        <v>30.9734492073973</v>
+        <v>-7.26957106603941</v>
       </c>
       <c r="D85" t="n">
-        <v>-24.4269327966448</v>
+        <v>-30.7450666987351</v>
       </c>
       <c r="E85" t="n">
-        <v>3000</v>
+        <v>2472.8861</v>
       </c>
       <c r="F85" t="n">
-        <v>2.729420000000001</v>
+        <v>6.55764</v>
       </c>
       <c r="G85" t="n">
-        <v>5.833333333333334</v>
+        <v>9.333333333333332</v>
       </c>
       <c r="H85" t="n">
-        <v>7.15</v>
+        <v>10.73333333333333</v>
       </c>
       <c r="I85" t="n">
-        <v>5.833333333333334</v>
+        <v>9.333333333333332</v>
       </c>
       <c r="J85" t="n">
-        <v>7.15</v>
+        <v>10.73333333333333</v>
       </c>
       <c r="K85" t="n">
-        <v>5.833333333333334</v>
+        <v>9.333333333333332</v>
       </c>
       <c r="L85" t="n">
-        <v>7.15</v>
+        <v>10.73333333333333</v>
       </c>
       <c r="M85" t="n">
         <v>0.3333333333333333</v>
@@ -4189,37 +4189,37 @@
         <v>84</v>
       </c>
       <c r="B86" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C86" t="n">
-        <v>30.9734492073973</v>
+        <v>-7.26957106603941</v>
       </c>
       <c r="D86" t="n">
-        <v>-24.4269327966448</v>
+        <v>-30.7450666987351</v>
       </c>
       <c r="E86" t="n">
-        <v>1065.1609</v>
+        <v>2472.8861</v>
       </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>6.55764</v>
       </c>
       <c r="G86" t="n">
-        <v>5.833333333333334</v>
+        <v>9.333333333333332</v>
       </c>
       <c r="H86" t="n">
-        <v>7.15</v>
+        <v>10.73333333333333</v>
       </c>
       <c r="I86" t="n">
-        <v>5.833333333333334</v>
+        <v>9.333333333333332</v>
       </c>
       <c r="J86" t="n">
-        <v>7.15</v>
+        <v>10.73333333333333</v>
       </c>
       <c r="K86" t="n">
-        <v>5.833333333333334</v>
+        <v>9.333333333333332</v>
       </c>
       <c r="L86" t="n">
-        <v>7.15</v>
+        <v>10.73333333333333</v>
       </c>
       <c r="M86" t="n">
         <v>0.3333333333333333</v>
@@ -4233,37 +4233,37 @@
         <v>85</v>
       </c>
       <c r="B87" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C87" t="n">
-        <v>35.8691630924626</v>
+        <v>-7.26957106603941</v>
       </c>
       <c r="D87" t="n">
-        <v>6.80594557114049</v>
+        <v>-30.7450666987351</v>
       </c>
       <c r="E87" t="n">
-        <v>3000</v>
+        <v>2472.8861</v>
       </c>
       <c r="F87" t="n">
-        <v>15</v>
+        <v>6.55764</v>
       </c>
       <c r="G87" t="n">
-        <v>6.633333333333333</v>
+        <v>9.333333333333332</v>
       </c>
       <c r="H87" t="n">
-        <v>7.983333333333333</v>
+        <v>10.73333333333333</v>
       </c>
       <c r="I87" t="n">
-        <v>6.633333333333333</v>
+        <v>9.333333333333332</v>
       </c>
       <c r="J87" t="n">
-        <v>7.983333333333333</v>
+        <v>10.73333333333333</v>
       </c>
       <c r="K87" t="n">
-        <v>6.633333333333333</v>
+        <v>9.333333333333332</v>
       </c>
       <c r="L87" t="n">
-        <v>7.983333333333333</v>
+        <v>10.73333333333333</v>
       </c>
       <c r="M87" t="n">
         <v>0.3333333333333333</v>
@@ -4277,37 +4277,37 @@
         <v>86</v>
       </c>
       <c r="B88" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C88" t="n">
-        <v>35.8691630924626</v>
+        <v>-30.4738708628108</v>
       </c>
       <c r="D88" t="n">
-        <v>6.80594557114049</v>
+        <v>0.417718230968227</v>
       </c>
       <c r="E88" t="n">
-        <v>3000</v>
+        <v>2439.52946</v>
       </c>
       <c r="F88" t="n">
-        <v>1.914529999999999</v>
+        <v>6.159698000000001</v>
       </c>
       <c r="G88" t="n">
-        <v>6.633333333333333</v>
+        <v>9.916666666666668</v>
       </c>
       <c r="H88" t="n">
-        <v>7.983333333333333</v>
+        <v>11.2</v>
       </c>
       <c r="I88" t="n">
-        <v>6.633333333333333</v>
+        <v>9.916666666666668</v>
       </c>
       <c r="J88" t="n">
-        <v>7.983333333333333</v>
+        <v>11.2</v>
       </c>
       <c r="K88" t="n">
-        <v>6.633333333333333</v>
+        <v>9.916666666666668</v>
       </c>
       <c r="L88" t="n">
-        <v>7.983333333333333</v>
+        <v>11.2</v>
       </c>
       <c r="M88" t="n">
         <v>0.3333333333333333</v>
@@ -4321,37 +4321,37 @@
         <v>87</v>
       </c>
       <c r="B89" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C89" t="n">
-        <v>35.8691630924626</v>
+        <v>-30.4738708628108</v>
       </c>
       <c r="D89" t="n">
-        <v>6.80594557114049</v>
+        <v>0.417718230968227</v>
       </c>
       <c r="E89" t="n">
-        <v>609.6530000000002</v>
+        <v>2439.52946</v>
       </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>6.159698000000001</v>
       </c>
       <c r="G89" t="n">
-        <v>6.633333333333333</v>
+        <v>9.916666666666668</v>
       </c>
       <c r="H89" t="n">
-        <v>7.983333333333333</v>
+        <v>11.2</v>
       </c>
       <c r="I89" t="n">
-        <v>6.633333333333333</v>
+        <v>9.916666666666668</v>
       </c>
       <c r="J89" t="n">
-        <v>7.983333333333333</v>
+        <v>11.2</v>
       </c>
       <c r="K89" t="n">
-        <v>6.633333333333333</v>
+        <v>9.916666666666668</v>
       </c>
       <c r="L89" t="n">
-        <v>7.983333333333333</v>
+        <v>11.2</v>
       </c>
       <c r="M89" t="n">
         <v>0.3333333333333333</v>
@@ -4365,37 +4365,37 @@
         <v>88</v>
       </c>
       <c r="B90" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C90" t="n">
-        <v>29.2918813421379</v>
+        <v>-30.4738708628108</v>
       </c>
       <c r="D90" t="n">
-        <v>-11.2363981231824</v>
+        <v>0.417718230968227</v>
       </c>
       <c r="E90" t="n">
-        <v>2933.964</v>
+        <v>2439.52946</v>
       </c>
       <c r="F90" t="n">
-        <v>9.727729999999999</v>
+        <v>6.159698000000001</v>
       </c>
       <c r="G90" t="n">
-        <v>6.300000000000001</v>
+        <v>9.916666666666668</v>
       </c>
       <c r="H90" t="n">
-        <v>7.383333333333333</v>
+        <v>11.2</v>
       </c>
       <c r="I90" t="n">
-        <v>6.300000000000001</v>
+        <v>9.916666666666668</v>
       </c>
       <c r="J90" t="n">
-        <v>7.383333333333333</v>
+        <v>11.2</v>
       </c>
       <c r="K90" t="n">
-        <v>6.300000000000001</v>
+        <v>9.916666666666668</v>
       </c>
       <c r="L90" t="n">
-        <v>7.383333333333333</v>
+        <v>11.2</v>
       </c>
       <c r="M90" t="n">
         <v>0.3333333333333333</v>
@@ -4409,37 +4409,37 @@
         <v>89</v>
       </c>
       <c r="B91" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C91" t="n">
-        <v>-32.4103858046121</v>
+        <v>-30.4738708628108</v>
       </c>
       <c r="D91" t="n">
-        <v>-2.65068011202597</v>
+        <v>0.417718230968227</v>
       </c>
       <c r="E91" t="n">
-        <v>3000</v>
+        <v>2439.52946</v>
       </c>
       <c r="F91" t="n">
-        <v>15</v>
+        <v>6.159698000000001</v>
       </c>
       <c r="G91" t="n">
-        <v>3.25</v>
+        <v>9.916666666666668</v>
       </c>
       <c r="H91" t="n">
-        <v>4.65</v>
+        <v>11.2</v>
       </c>
       <c r="I91" t="n">
-        <v>3.25</v>
+        <v>9.916666666666668</v>
       </c>
       <c r="J91" t="n">
-        <v>4.65</v>
+        <v>11.2</v>
       </c>
       <c r="K91" t="n">
-        <v>3.25</v>
+        <v>9.916666666666668</v>
       </c>
       <c r="L91" t="n">
-        <v>4.65</v>
+        <v>11.2</v>
       </c>
       <c r="M91" t="n">
         <v>0.3333333333333333</v>
@@ -4453,37 +4453,37 @@
         <v>90</v>
       </c>
       <c r="B92" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C92" t="n">
-        <v>-32.4103858046121</v>
+        <v>-30.4738708628108</v>
       </c>
       <c r="D92" t="n">
-        <v>-2.65068011202597</v>
+        <v>0.417718230968227</v>
       </c>
       <c r="E92" t="n">
-        <v>3000</v>
+        <v>2439.52946</v>
       </c>
       <c r="F92" t="n">
-        <v>8.245070000000002</v>
+        <v>6.159698000000001</v>
       </c>
       <c r="G92" t="n">
-        <v>3.25</v>
+        <v>9.916666666666668</v>
       </c>
       <c r="H92" t="n">
-        <v>4.65</v>
+        <v>11.2</v>
       </c>
       <c r="I92" t="n">
-        <v>3.25</v>
+        <v>9.916666666666668</v>
       </c>
       <c r="J92" t="n">
-        <v>4.65</v>
+        <v>11.2</v>
       </c>
       <c r="K92" t="n">
-        <v>3.25</v>
+        <v>9.916666666666668</v>
       </c>
       <c r="L92" t="n">
-        <v>4.65</v>
+        <v>11.2</v>
       </c>
       <c r="M92" t="n">
         <v>0.3333333333333333</v>
@@ -4497,37 +4497,37 @@
         <v>91</v>
       </c>
       <c r="B93" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C93" t="n">
-        <v>-32.4103858046121</v>
+        <v>30.9734492073973</v>
       </c>
       <c r="D93" t="n">
-        <v>-2.65068011202597</v>
+        <v>-24.4269327966448</v>
       </c>
       <c r="E93" t="n">
-        <v>2807.3868</v>
+        <v>2355.053633333333</v>
       </c>
       <c r="F93" t="n">
-        <v>0</v>
+        <v>5.909806666666667</v>
       </c>
       <c r="G93" t="n">
-        <v>3.25</v>
+        <v>5.833333333333334</v>
       </c>
       <c r="H93" t="n">
-        <v>4.65</v>
+        <v>7.15</v>
       </c>
       <c r="I93" t="n">
-        <v>3.25</v>
+        <v>5.833333333333334</v>
       </c>
       <c r="J93" t="n">
-        <v>4.65</v>
+        <v>7.15</v>
       </c>
       <c r="K93" t="n">
-        <v>3.25</v>
+        <v>5.833333333333334</v>
       </c>
       <c r="L93" t="n">
-        <v>4.65</v>
+        <v>7.15</v>
       </c>
       <c r="M93" t="n">
         <v>0.3333333333333333</v>
@@ -4541,37 +4541,37 @@
         <v>92</v>
       </c>
       <c r="B94" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C94" t="n">
-        <v>14.512163776104</v>
+        <v>30.9734492073973</v>
       </c>
       <c r="D94" t="n">
-        <v>29.3929978248616</v>
+        <v>-24.4269327966448</v>
       </c>
       <c r="E94" t="n">
-        <v>3000</v>
+        <v>2355.053633333333</v>
       </c>
       <c r="F94" t="n">
-        <v>15</v>
+        <v>5.909806666666667</v>
       </c>
       <c r="G94" t="n">
-        <v>2.383333333333333</v>
+        <v>5.833333333333334</v>
       </c>
       <c r="H94" t="n">
-        <v>3.6</v>
+        <v>7.15</v>
       </c>
       <c r="I94" t="n">
-        <v>2.383333333333333</v>
+        <v>5.833333333333334</v>
       </c>
       <c r="J94" t="n">
-        <v>3.6</v>
+        <v>7.15</v>
       </c>
       <c r="K94" t="n">
-        <v>2.383333333333333</v>
+        <v>5.833333333333334</v>
       </c>
       <c r="L94" t="n">
-        <v>3.6</v>
+        <v>7.15</v>
       </c>
       <c r="M94" t="n">
         <v>0.3333333333333333</v>
@@ -4585,37 +4585,37 @@
         <v>93</v>
       </c>
       <c r="B95" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C95" t="n">
-        <v>14.512163776104</v>
+        <v>30.9734492073973</v>
       </c>
       <c r="D95" t="n">
-        <v>29.3929978248616</v>
+        <v>-24.4269327966448</v>
       </c>
       <c r="E95" t="n">
-        <v>3000</v>
+        <v>2355.053633333333</v>
       </c>
       <c r="F95" t="n">
-        <v>11.01759</v>
+        <v>5.909806666666667</v>
       </c>
       <c r="G95" t="n">
-        <v>2.383333333333333</v>
+        <v>5.833333333333334</v>
       </c>
       <c r="H95" t="n">
-        <v>3.6</v>
+        <v>7.15</v>
       </c>
       <c r="I95" t="n">
-        <v>2.383333333333333</v>
+        <v>5.833333333333334</v>
       </c>
       <c r="J95" t="n">
-        <v>3.6</v>
+        <v>7.15</v>
       </c>
       <c r="K95" t="n">
-        <v>2.383333333333333</v>
+        <v>5.833333333333334</v>
       </c>
       <c r="L95" t="n">
-        <v>3.6</v>
+        <v>7.15</v>
       </c>
       <c r="M95" t="n">
         <v>0.3333333333333333</v>
@@ -4629,37 +4629,37 @@
         <v>94</v>
       </c>
       <c r="B96" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C96" t="n">
-        <v>14.512163776104</v>
+        <v>35.8691630924626</v>
       </c>
       <c r="D96" t="n">
-        <v>29.3929978248616</v>
+        <v>6.80594557114049</v>
       </c>
       <c r="E96" t="n">
-        <v>3000</v>
+        <v>2203.217666666667</v>
       </c>
       <c r="F96" t="n">
-        <v>0</v>
+        <v>5.638176666666666</v>
       </c>
       <c r="G96" t="n">
-        <v>2.383333333333333</v>
+        <v>6.633333333333333</v>
       </c>
       <c r="H96" t="n">
-        <v>3.6</v>
+        <v>7.983333333333333</v>
       </c>
       <c r="I96" t="n">
-        <v>2.383333333333333</v>
+        <v>6.633333333333333</v>
       </c>
       <c r="J96" t="n">
-        <v>3.6</v>
+        <v>7.983333333333333</v>
       </c>
       <c r="K96" t="n">
-        <v>2.383333333333333</v>
+        <v>6.633333333333333</v>
       </c>
       <c r="L96" t="n">
-        <v>3.6</v>
+        <v>7.983333333333333</v>
       </c>
       <c r="M96" t="n">
         <v>0.3333333333333333</v>
@@ -4673,37 +4673,37 @@
         <v>95</v>
       </c>
       <c r="B97" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C97" t="n">
-        <v>14.512163776104</v>
+        <v>35.8691630924626</v>
       </c>
       <c r="D97" t="n">
-        <v>29.3929978248616</v>
+        <v>6.80594557114049</v>
       </c>
       <c r="E97" t="n">
-        <v>906.6291999999994</v>
+        <v>2203.217666666667</v>
       </c>
       <c r="F97" t="n">
-        <v>0</v>
+        <v>5.638176666666666</v>
       </c>
       <c r="G97" t="n">
-        <v>2.383333333333333</v>
+        <v>6.633333333333333</v>
       </c>
       <c r="H97" t="n">
-        <v>3.6</v>
+        <v>7.983333333333333</v>
       </c>
       <c r="I97" t="n">
-        <v>2.383333333333333</v>
+        <v>6.633333333333333</v>
       </c>
       <c r="J97" t="n">
-        <v>3.6</v>
+        <v>7.983333333333333</v>
       </c>
       <c r="K97" t="n">
-        <v>2.383333333333333</v>
+        <v>6.633333333333333</v>
       </c>
       <c r="L97" t="n">
-        <v>3.6</v>
+        <v>7.983333333333333</v>
       </c>
       <c r="M97" t="n">
         <v>0.3333333333333333</v>
@@ -4717,37 +4717,37 @@
         <v>96</v>
       </c>
       <c r="B98" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C98" t="n">
-        <v>7.25597388908157</v>
+        <v>35.8691630924626</v>
       </c>
       <c r="D98" t="n">
-        <v>-33.7475199378438</v>
+        <v>6.80594557114049</v>
       </c>
       <c r="E98" t="n">
-        <v>3000</v>
+        <v>2203.217666666667</v>
       </c>
       <c r="F98" t="n">
-        <v>15</v>
+        <v>5.638176666666666</v>
       </c>
       <c r="G98" t="n">
-        <v>4.283333333333333</v>
+        <v>6.633333333333333</v>
       </c>
       <c r="H98" t="n">
-        <v>5.716666666666667</v>
+        <v>7.983333333333333</v>
       </c>
       <c r="I98" t="n">
-        <v>4.283333333333333</v>
+        <v>6.633333333333333</v>
       </c>
       <c r="J98" t="n">
-        <v>5.716666666666667</v>
+        <v>7.983333333333333</v>
       </c>
       <c r="K98" t="n">
-        <v>4.283333333333333</v>
+        <v>6.633333333333333</v>
       </c>
       <c r="L98" t="n">
-        <v>5.716666666666667</v>
+        <v>7.983333333333333</v>
       </c>
       <c r="M98" t="n">
         <v>0.3333333333333333</v>
@@ -4761,37 +4761,37 @@
         <v>97</v>
       </c>
       <c r="B99" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C99" t="n">
-        <v>7.25597388908157</v>
+        <v>29.2918813421379</v>
       </c>
       <c r="D99" t="n">
-        <v>-33.7475199378438</v>
+        <v>-11.2363981231824</v>
       </c>
       <c r="E99" t="n">
-        <v>3000</v>
+        <v>2933.964</v>
       </c>
       <c r="F99" t="n">
-        <v>3.40521</v>
+        <v>9.727729999999999</v>
       </c>
       <c r="G99" t="n">
-        <v>4.283333333333333</v>
+        <v>6.300000000000001</v>
       </c>
       <c r="H99" t="n">
-        <v>5.716666666666667</v>
+        <v>7.383333333333333</v>
       </c>
       <c r="I99" t="n">
-        <v>4.283333333333333</v>
+        <v>6.300000000000001</v>
       </c>
       <c r="J99" t="n">
-        <v>5.716666666666667</v>
+        <v>7.383333333333333</v>
       </c>
       <c r="K99" t="n">
-        <v>4.283333333333333</v>
+        <v>6.300000000000001</v>
       </c>
       <c r="L99" t="n">
-        <v>5.716666666666667</v>
+        <v>7.383333333333333</v>
       </c>
       <c r="M99" t="n">
         <v>0.3333333333333333</v>
@@ -4805,37 +4805,37 @@
         <v>98</v>
       </c>
       <c r="B100" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C100" t="n">
-        <v>7.25597388908157</v>
+        <v>-32.4103858046121</v>
       </c>
       <c r="D100" t="n">
-        <v>-33.7475199378438</v>
+        <v>-2.65068011202597</v>
       </c>
       <c r="E100" t="n">
-        <v>14.0654999999997</v>
+        <v>2935.7956</v>
       </c>
       <c r="F100" t="n">
-        <v>0</v>
+        <v>7.748356666666667</v>
       </c>
       <c r="G100" t="n">
-        <v>4.283333333333333</v>
+        <v>3.25</v>
       </c>
       <c r="H100" t="n">
-        <v>5.716666666666667</v>
+        <v>4.65</v>
       </c>
       <c r="I100" t="n">
-        <v>4.283333333333333</v>
+        <v>3.25</v>
       </c>
       <c r="J100" t="n">
-        <v>5.716666666666667</v>
+        <v>4.65</v>
       </c>
       <c r="K100" t="n">
-        <v>4.283333333333333</v>
+        <v>3.25</v>
       </c>
       <c r="L100" t="n">
-        <v>5.716666666666667</v>
+        <v>4.65</v>
       </c>
       <c r="M100" t="n">
         <v>0.3333333333333333</v>
@@ -4849,37 +4849,37 @@
         <v>99</v>
       </c>
       <c r="B101" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C101" t="n">
-        <v>-14.3803349502555</v>
+        <v>-32.4103858046121</v>
       </c>
       <c r="D101" t="n">
-        <v>-0.886084812651717</v>
+        <v>-2.65068011202597</v>
       </c>
       <c r="E101" t="n">
-        <v>3000</v>
+        <v>2935.7956</v>
       </c>
       <c r="F101" t="n">
-        <v>15</v>
+        <v>7.748356666666667</v>
       </c>
       <c r="G101" t="n">
-        <v>11.18333333333333</v>
+        <v>3.25</v>
       </c>
       <c r="H101" t="n">
-        <v>12.01666666666667</v>
+        <v>4.65</v>
       </c>
       <c r="I101" t="n">
-        <v>11.18333333333333</v>
+        <v>3.25</v>
       </c>
       <c r="J101" t="n">
-        <v>12.01666666666667</v>
+        <v>4.65</v>
       </c>
       <c r="K101" t="n">
-        <v>11.18333333333333</v>
+        <v>3.25</v>
       </c>
       <c r="L101" t="n">
-        <v>12.01666666666667</v>
+        <v>4.65</v>
       </c>
       <c r="M101" t="n">
         <v>0.3333333333333333</v>
@@ -4893,37 +4893,37 @@
         <v>100</v>
       </c>
       <c r="B102" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C102" t="n">
-        <v>-14.3803349502555</v>
+        <v>-32.4103858046121</v>
       </c>
       <c r="D102" t="n">
-        <v>-0.886084812651717</v>
+        <v>-2.65068011202597</v>
       </c>
       <c r="E102" t="n">
-        <v>3000</v>
+        <v>2935.7956</v>
       </c>
       <c r="F102" t="n">
-        <v>10.12844</v>
+        <v>7.748356666666667</v>
       </c>
       <c r="G102" t="n">
-        <v>11.18333333333333</v>
+        <v>3.25</v>
       </c>
       <c r="H102" t="n">
-        <v>12.01666666666667</v>
+        <v>4.65</v>
       </c>
       <c r="I102" t="n">
-        <v>11.18333333333333</v>
+        <v>3.25</v>
       </c>
       <c r="J102" t="n">
-        <v>12.01666666666667</v>
+        <v>4.65</v>
       </c>
       <c r="K102" t="n">
-        <v>11.18333333333333</v>
+        <v>3.25</v>
       </c>
       <c r="L102" t="n">
-        <v>12.01666666666667</v>
+        <v>4.65</v>
       </c>
       <c r="M102" t="n">
         <v>0.3333333333333333</v>
@@ -4937,37 +4937,37 @@
         <v>101</v>
       </c>
       <c r="B103" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C103" t="n">
-        <v>-14.3803349502555</v>
+        <v>14.512163776104</v>
       </c>
       <c r="D103" t="n">
-        <v>-0.886084812651717</v>
+        <v>29.3929978248616</v>
       </c>
       <c r="E103" t="n">
-        <v>2804.294400000001</v>
+        <v>2476.6573</v>
       </c>
       <c r="F103" t="n">
-        <v>0</v>
+        <v>6.5043975</v>
       </c>
       <c r="G103" t="n">
-        <v>11.18333333333333</v>
+        <v>2.383333333333333</v>
       </c>
       <c r="H103" t="n">
-        <v>12.01666666666667</v>
+        <v>3.6</v>
       </c>
       <c r="I103" t="n">
-        <v>11.18333333333333</v>
+        <v>2.383333333333333</v>
       </c>
       <c r="J103" t="n">
-        <v>12.01666666666667</v>
+        <v>3.6</v>
       </c>
       <c r="K103" t="n">
-        <v>11.18333333333333</v>
+        <v>2.383333333333333</v>
       </c>
       <c r="L103" t="n">
-        <v>12.01666666666667</v>
+        <v>3.6</v>
       </c>
       <c r="M103" t="n">
         <v>0.3333333333333333</v>
@@ -4981,37 +4981,37 @@
         <v>102</v>
       </c>
       <c r="B104" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C104" t="n">
-        <v>-18.8423929163792</v>
+        <v>14.512163776104</v>
       </c>
       <c r="D104" t="n">
-        <v>25.2549085872536</v>
+        <v>29.3929978248616</v>
       </c>
       <c r="E104" t="n">
-        <v>3000</v>
+        <v>2476.6573</v>
       </c>
       <c r="F104" t="n">
-        <v>15</v>
+        <v>6.5043975</v>
       </c>
       <c r="G104" t="n">
-        <v>7.866666666666667</v>
+        <v>2.383333333333333</v>
       </c>
       <c r="H104" t="n">
-        <v>9.233333333333334</v>
+        <v>3.6</v>
       </c>
       <c r="I104" t="n">
-        <v>7.866666666666667</v>
+        <v>2.383333333333333</v>
       </c>
       <c r="J104" t="n">
-        <v>9.233333333333334</v>
+        <v>3.6</v>
       </c>
       <c r="K104" t="n">
-        <v>7.866666666666667</v>
+        <v>2.383333333333333</v>
       </c>
       <c r="L104" t="n">
-        <v>9.233333333333334</v>
+        <v>3.6</v>
       </c>
       <c r="M104" t="n">
         <v>0.3333333333333333</v>
@@ -5025,37 +5025,37 @@
         <v>103</v>
       </c>
       <c r="B105" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C105" t="n">
-        <v>-18.8423929163792</v>
+        <v>14.512163776104</v>
       </c>
       <c r="D105" t="n">
-        <v>25.2549085872536</v>
+        <v>29.3929978248616</v>
       </c>
       <c r="E105" t="n">
-        <v>3000</v>
+        <v>2476.6573</v>
       </c>
       <c r="F105" t="n">
-        <v>8.777850000000001</v>
+        <v>6.5043975</v>
       </c>
       <c r="G105" t="n">
-        <v>7.866666666666667</v>
+        <v>2.383333333333333</v>
       </c>
       <c r="H105" t="n">
-        <v>9.233333333333334</v>
+        <v>3.6</v>
       </c>
       <c r="I105" t="n">
-        <v>7.866666666666667</v>
+        <v>2.383333333333333</v>
       </c>
       <c r="J105" t="n">
-        <v>9.233333333333334</v>
+        <v>3.6</v>
       </c>
       <c r="K105" t="n">
-        <v>7.866666666666667</v>
+        <v>2.383333333333333</v>
       </c>
       <c r="L105" t="n">
-        <v>9.233333333333334</v>
+        <v>3.6</v>
       </c>
       <c r="M105" t="n">
         <v>0.3333333333333333</v>
@@ -5069,37 +5069,37 @@
         <v>104</v>
       </c>
       <c r="B106" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C106" t="n">
-        <v>-18.8423929163792</v>
+        <v>14.512163776104</v>
       </c>
       <c r="D106" t="n">
-        <v>25.2549085872536</v>
+        <v>29.3929978248616</v>
       </c>
       <c r="E106" t="n">
-        <v>2692.99</v>
+        <v>2476.6573</v>
       </c>
       <c r="F106" t="n">
-        <v>0</v>
+        <v>6.5043975</v>
       </c>
       <c r="G106" t="n">
-        <v>7.866666666666667</v>
+        <v>2.383333333333333</v>
       </c>
       <c r="H106" t="n">
-        <v>9.233333333333334</v>
+        <v>3.6</v>
       </c>
       <c r="I106" t="n">
-        <v>7.866666666666667</v>
+        <v>2.383333333333333</v>
       </c>
       <c r="J106" t="n">
-        <v>9.233333333333334</v>
+        <v>3.6</v>
       </c>
       <c r="K106" t="n">
-        <v>7.866666666666667</v>
+        <v>2.383333333333333</v>
       </c>
       <c r="L106" t="n">
-        <v>9.233333333333334</v>
+        <v>3.6</v>
       </c>
       <c r="M106" t="n">
         <v>0.3333333333333333</v>
@@ -5113,37 +5113,37 @@
         <v>105</v>
       </c>
       <c r="B107" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C107" t="n">
-        <v>29.553914624618</v>
+        <v>7.25597388908157</v>
       </c>
       <c r="D107" t="n">
-        <v>-15.7832896589862</v>
+        <v>-33.7475199378438</v>
       </c>
       <c r="E107" t="n">
-        <v>3000</v>
+        <v>2004.6885</v>
       </c>
       <c r="F107" t="n">
-        <v>15</v>
+        <v>6.13507</v>
       </c>
       <c r="G107" t="n">
-        <v>6.15</v>
+        <v>4.283333333333333</v>
       </c>
       <c r="H107" t="n">
-        <v>7.083333333333334</v>
+        <v>5.716666666666667</v>
       </c>
       <c r="I107" t="n">
-        <v>6.15</v>
+        <v>4.283333333333333</v>
       </c>
       <c r="J107" t="n">
-        <v>7.083333333333334</v>
+        <v>5.716666666666667</v>
       </c>
       <c r="K107" t="n">
-        <v>6.15</v>
+        <v>4.283333333333333</v>
       </c>
       <c r="L107" t="n">
-        <v>7.083333333333334</v>
+        <v>5.716666666666667</v>
       </c>
       <c r="M107" t="n">
         <v>0.3333333333333333</v>
@@ -5157,37 +5157,37 @@
         <v>106</v>
       </c>
       <c r="B108" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C108" t="n">
-        <v>29.553914624618</v>
+        <v>7.25597388908157</v>
       </c>
       <c r="D108" t="n">
-        <v>-15.7832896589862</v>
+        <v>-33.7475199378438</v>
       </c>
       <c r="E108" t="n">
-        <v>3000</v>
+        <v>2004.6885</v>
       </c>
       <c r="F108" t="n">
-        <v>6.387280000000001</v>
+        <v>6.13507</v>
       </c>
       <c r="G108" t="n">
-        <v>6.15</v>
+        <v>4.283333333333333</v>
       </c>
       <c r="H108" t="n">
-        <v>7.083333333333334</v>
+        <v>5.716666666666667</v>
       </c>
       <c r="I108" t="n">
-        <v>6.15</v>
+        <v>4.283333333333333</v>
       </c>
       <c r="J108" t="n">
-        <v>7.083333333333334</v>
+        <v>5.716666666666667</v>
       </c>
       <c r="K108" t="n">
-        <v>6.15</v>
+        <v>4.283333333333333</v>
       </c>
       <c r="L108" t="n">
-        <v>7.083333333333334</v>
+        <v>5.716666666666667</v>
       </c>
       <c r="M108" t="n">
         <v>0.3333333333333333</v>
@@ -5201,37 +5201,37 @@
         <v>107</v>
       </c>
       <c r="B109" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C109" t="n">
-        <v>29.553914624618</v>
+        <v>7.25597388908157</v>
       </c>
       <c r="D109" t="n">
-        <v>-15.7832896589862</v>
+        <v>-33.7475199378438</v>
       </c>
       <c r="E109" t="n">
-        <v>2849.7672</v>
+        <v>2004.6885</v>
       </c>
       <c r="F109" t="n">
-        <v>0</v>
+        <v>6.13507</v>
       </c>
       <c r="G109" t="n">
-        <v>6.15</v>
+        <v>4.283333333333333</v>
       </c>
       <c r="H109" t="n">
-        <v>7.083333333333334</v>
+        <v>5.716666666666667</v>
       </c>
       <c r="I109" t="n">
-        <v>6.15</v>
+        <v>4.283333333333333</v>
       </c>
       <c r="J109" t="n">
-        <v>7.083333333333334</v>
+        <v>5.716666666666667</v>
       </c>
       <c r="K109" t="n">
-        <v>6.15</v>
+        <v>4.283333333333333</v>
       </c>
       <c r="L109" t="n">
-        <v>7.083333333333334</v>
+        <v>5.716666666666667</v>
       </c>
       <c r="M109" t="n">
         <v>0.3333333333333333</v>
@@ -5245,37 +5245,37 @@
         <v>108</v>
       </c>
       <c r="B110" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C110" t="n">
-        <v>-13.5633988058324</v>
+        <v>-14.3803349502555</v>
       </c>
       <c r="D110" t="n">
-        <v>35.7117550694904</v>
+        <v>-0.886084812651717</v>
       </c>
       <c r="E110" t="n">
-        <v>3000</v>
+        <v>2934.7648</v>
       </c>
       <c r="F110" t="n">
-        <v>14.76431</v>
+        <v>8.376146666666667</v>
       </c>
       <c r="G110" t="n">
-        <v>7.949999999999999</v>
+        <v>11.18333333333333</v>
       </c>
       <c r="H110" t="n">
-        <v>9.383333333333333</v>
+        <v>12.01666666666667</v>
       </c>
       <c r="I110" t="n">
-        <v>7.949999999999999</v>
+        <v>11.18333333333333</v>
       </c>
       <c r="J110" t="n">
-        <v>9.383333333333333</v>
+        <v>12.01666666666667</v>
       </c>
       <c r="K110" t="n">
-        <v>7.949999999999999</v>
+        <v>11.18333333333333</v>
       </c>
       <c r="L110" t="n">
-        <v>9.383333333333333</v>
+        <v>12.01666666666667</v>
       </c>
       <c r="M110" t="n">
         <v>0.3333333333333333</v>
@@ -5289,37 +5289,37 @@
         <v>109</v>
       </c>
       <c r="B111" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C111" t="n">
-        <v>-13.5633988058324</v>
+        <v>-14.3803349502555</v>
       </c>
       <c r="D111" t="n">
-        <v>35.7117550694904</v>
+        <v>-0.886084812651717</v>
       </c>
       <c r="E111" t="n">
-        <v>3000</v>
+        <v>2934.7648</v>
       </c>
       <c r="F111" t="n">
-        <v>0</v>
+        <v>8.376146666666667</v>
       </c>
       <c r="G111" t="n">
-        <v>7.949999999999999</v>
+        <v>11.18333333333333</v>
       </c>
       <c r="H111" t="n">
-        <v>9.383333333333333</v>
+        <v>12.01666666666667</v>
       </c>
       <c r="I111" t="n">
-        <v>7.949999999999999</v>
+        <v>11.18333333333333</v>
       </c>
       <c r="J111" t="n">
-        <v>9.383333333333333</v>
+        <v>12.01666666666667</v>
       </c>
       <c r="K111" t="n">
-        <v>7.949999999999999</v>
+        <v>11.18333333333333</v>
       </c>
       <c r="L111" t="n">
-        <v>9.383333333333333</v>
+        <v>12.01666666666667</v>
       </c>
       <c r="M111" t="n">
         <v>0.3333333333333333</v>
@@ -5333,37 +5333,37 @@
         <v>110</v>
       </c>
       <c r="B112" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C112" t="n">
-        <v>-13.5633988058324</v>
+        <v>-14.3803349502555</v>
       </c>
       <c r="D112" t="n">
-        <v>35.7117550694904</v>
+        <v>-0.886084812651717</v>
       </c>
       <c r="E112" t="n">
-        <v>552.5866999999998</v>
+        <v>2934.7648</v>
       </c>
       <c r="F112" t="n">
-        <v>0</v>
+        <v>8.376146666666667</v>
       </c>
       <c r="G112" t="n">
-        <v>7.949999999999999</v>
+        <v>11.18333333333333</v>
       </c>
       <c r="H112" t="n">
-        <v>9.383333333333333</v>
+        <v>12.01666666666667</v>
       </c>
       <c r="I112" t="n">
-        <v>7.949999999999999</v>
+        <v>11.18333333333333</v>
       </c>
       <c r="J112" t="n">
-        <v>9.383333333333333</v>
+        <v>12.01666666666667</v>
       </c>
       <c r="K112" t="n">
-        <v>7.949999999999999</v>
+        <v>11.18333333333333</v>
       </c>
       <c r="L112" t="n">
-        <v>9.383333333333333</v>
+        <v>12.01666666666667</v>
       </c>
       <c r="M112" t="n">
         <v>0.3333333333333333</v>
@@ -5377,37 +5377,37 @@
         <v>111</v>
       </c>
       <c r="B113" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C113" t="n">
-        <v>10.9979131123698</v>
+        <v>-18.8423929163792</v>
       </c>
       <c r="D113" t="n">
-        <v>-14.3764159181384</v>
+        <v>25.2549085872536</v>
       </c>
       <c r="E113" t="n">
-        <v>2791.0139</v>
+        <v>2897.663333333333</v>
       </c>
       <c r="F113" t="n">
-        <v>8.679600000000001</v>
+        <v>7.92595</v>
       </c>
       <c r="G113" t="n">
-        <v>1.166666666666666</v>
+        <v>7.866666666666667</v>
       </c>
       <c r="H113" t="n">
-        <v>2.550000000000001</v>
+        <v>9.233333333333334</v>
       </c>
       <c r="I113" t="n">
-        <v>1.166666666666666</v>
+        <v>7.866666666666667</v>
       </c>
       <c r="J113" t="n">
-        <v>2.550000000000001</v>
+        <v>9.233333333333334</v>
       </c>
       <c r="K113" t="n">
-        <v>1.166666666666666</v>
+        <v>7.866666666666667</v>
       </c>
       <c r="L113" t="n">
-        <v>2.550000000000001</v>
+        <v>9.233333333333334</v>
       </c>
       <c r="M113" t="n">
         <v>0.3333333333333333</v>
@@ -5421,37 +5421,37 @@
         <v>112</v>
       </c>
       <c r="B114" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C114" t="n">
-        <v>15.2856210779678</v>
+        <v>-18.8423929163792</v>
       </c>
       <c r="D114" t="n">
-        <v>-28.0053274336459</v>
+        <v>25.2549085872536</v>
       </c>
       <c r="E114" t="n">
-        <v>2860.4382</v>
+        <v>2897.663333333333</v>
       </c>
       <c r="F114" t="n">
-        <v>8.924939999999999</v>
+        <v>7.92595</v>
       </c>
       <c r="G114" t="n">
-        <v>10.86666666666667</v>
+        <v>7.866666666666667</v>
       </c>
       <c r="H114" t="n">
-        <v>12.26666666666667</v>
+        <v>9.233333333333334</v>
       </c>
       <c r="I114" t="n">
-        <v>10.86666666666667</v>
+        <v>7.866666666666667</v>
       </c>
       <c r="J114" t="n">
-        <v>12.26666666666667</v>
+        <v>9.233333333333334</v>
       </c>
       <c r="K114" t="n">
-        <v>10.86666666666667</v>
+        <v>7.866666666666667</v>
       </c>
       <c r="L114" t="n">
-        <v>12.26666666666667</v>
+        <v>9.233333333333334</v>
       </c>
       <c r="M114" t="n">
         <v>0.3333333333333333</v>
@@ -5465,37 +5465,37 @@
         <v>113</v>
       </c>
       <c r="B115" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C115" t="n">
-        <v>-6.89120148830592</v>
+        <v>-18.8423929163792</v>
       </c>
       <c r="D115" t="n">
-        <v>36.8225598526382</v>
+        <v>25.2549085872536</v>
       </c>
       <c r="E115" t="n">
-        <v>3000</v>
+        <v>2897.663333333333</v>
       </c>
       <c r="F115" t="n">
-        <v>15</v>
+        <v>7.92595</v>
       </c>
       <c r="G115" t="n">
-        <v>10.51666666666667</v>
+        <v>7.866666666666667</v>
       </c>
       <c r="H115" t="n">
-        <v>11.8</v>
+        <v>9.233333333333334</v>
       </c>
       <c r="I115" t="n">
-        <v>10.51666666666667</v>
+        <v>7.866666666666667</v>
       </c>
       <c r="J115" t="n">
-        <v>11.8</v>
+        <v>9.233333333333334</v>
       </c>
       <c r="K115" t="n">
-        <v>10.51666666666667</v>
+        <v>7.866666666666667</v>
       </c>
       <c r="L115" t="n">
-        <v>11.8</v>
+        <v>9.233333333333334</v>
       </c>
       <c r="M115" t="n">
         <v>0.3333333333333333</v>
@@ -5509,37 +5509,37 @@
         <v>114</v>
       </c>
       <c r="B116" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C116" t="n">
-        <v>-6.89120148830592</v>
+        <v>29.553914624618</v>
       </c>
       <c r="D116" t="n">
-        <v>36.8225598526382</v>
+        <v>-15.7832896589862</v>
       </c>
       <c r="E116" t="n">
-        <v>3000</v>
+        <v>2949.9224</v>
       </c>
       <c r="F116" t="n">
-        <v>2.4329</v>
+        <v>7.129093333333334</v>
       </c>
       <c r="G116" t="n">
-        <v>10.51666666666667</v>
+        <v>6.15</v>
       </c>
       <c r="H116" t="n">
-        <v>11.8</v>
+        <v>7.083333333333334</v>
       </c>
       <c r="I116" t="n">
-        <v>10.51666666666667</v>
+        <v>6.15</v>
       </c>
       <c r="J116" t="n">
-        <v>11.8</v>
+        <v>7.083333333333334</v>
       </c>
       <c r="K116" t="n">
-        <v>10.51666666666667</v>
+        <v>6.15</v>
       </c>
       <c r="L116" t="n">
-        <v>11.8</v>
+        <v>7.083333333333334</v>
       </c>
       <c r="M116" t="n">
         <v>0.3333333333333333</v>
@@ -5553,37 +5553,37 @@
         <v>115</v>
       </c>
       <c r="B117" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C117" t="n">
-        <v>-6.89120148830592</v>
+        <v>29.553914624618</v>
       </c>
       <c r="D117" t="n">
-        <v>36.8225598526382</v>
+        <v>-15.7832896589862</v>
       </c>
       <c r="E117" t="n">
-        <v>1414.9874</v>
+        <v>2949.9224</v>
       </c>
       <c r="F117" t="n">
-        <v>0</v>
+        <v>7.129093333333334</v>
       </c>
       <c r="G117" t="n">
-        <v>10.51666666666667</v>
+        <v>6.15</v>
       </c>
       <c r="H117" t="n">
-        <v>11.8</v>
+        <v>7.083333333333334</v>
       </c>
       <c r="I117" t="n">
-        <v>10.51666666666667</v>
+        <v>6.15</v>
       </c>
       <c r="J117" t="n">
-        <v>11.8</v>
+        <v>7.083333333333334</v>
       </c>
       <c r="K117" t="n">
-        <v>10.51666666666667</v>
+        <v>6.15</v>
       </c>
       <c r="L117" t="n">
-        <v>11.8</v>
+        <v>7.083333333333334</v>
       </c>
       <c r="M117" t="n">
         <v>0.3333333333333333</v>
@@ -5597,37 +5597,37 @@
         <v>116</v>
       </c>
       <c r="B118" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C118" t="n">
-        <v>-10.2808334321244</v>
+        <v>29.553914624618</v>
       </c>
       <c r="D118" t="n">
-        <v>29.5869615259404</v>
+        <v>-15.7832896589862</v>
       </c>
       <c r="E118" t="n">
-        <v>2288.8859</v>
+        <v>2949.9224</v>
       </c>
       <c r="F118" t="n">
-        <v>6.06402</v>
+        <v>7.129093333333334</v>
       </c>
       <c r="G118" t="n">
-        <v>7.766666666666667</v>
+        <v>6.15</v>
       </c>
       <c r="H118" t="n">
-        <v>9.149999999999999</v>
+        <v>7.083333333333334</v>
       </c>
       <c r="I118" t="n">
-        <v>7.766666666666667</v>
+        <v>6.15</v>
       </c>
       <c r="J118" t="n">
-        <v>9.149999999999999</v>
+        <v>7.083333333333334</v>
       </c>
       <c r="K118" t="n">
-        <v>7.766666666666667</v>
+        <v>6.15</v>
       </c>
       <c r="L118" t="n">
-        <v>9.149999999999999</v>
+        <v>7.083333333333334</v>
       </c>
       <c r="M118" t="n">
         <v>0.3333333333333333</v>
@@ -5641,37 +5641,37 @@
         <v>117</v>
       </c>
       <c r="B119" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C119" t="n">
-        <v>-12.9249626484284</v>
+        <v>-13.5633988058324</v>
       </c>
       <c r="D119" t="n">
-        <v>-33.6033227158668</v>
+        <v>35.7117550694904</v>
       </c>
       <c r="E119" t="n">
-        <v>3000</v>
+        <v>2184.195566666667</v>
       </c>
       <c r="F119" t="n">
-        <v>15</v>
+        <v>4.921436666666667</v>
       </c>
       <c r="G119" t="n">
-        <v>3.6</v>
+        <v>7.949999999999999</v>
       </c>
       <c r="H119" t="n">
-        <v>4.583333333333334</v>
+        <v>9.383333333333333</v>
       </c>
       <c r="I119" t="n">
-        <v>3.6</v>
+        <v>7.949999999999999</v>
       </c>
       <c r="J119" t="n">
-        <v>4.583333333333334</v>
+        <v>9.383333333333333</v>
       </c>
       <c r="K119" t="n">
-        <v>3.6</v>
+        <v>7.949999999999999</v>
       </c>
       <c r="L119" t="n">
-        <v>4.583333333333334</v>
+        <v>9.383333333333333</v>
       </c>
       <c r="M119" t="n">
         <v>0.3333333333333333</v>
@@ -5685,37 +5685,37 @@
         <v>118</v>
       </c>
       <c r="B120" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C120" t="n">
-        <v>-12.9249626484284</v>
+        <v>-13.5633988058324</v>
       </c>
       <c r="D120" t="n">
-        <v>-33.6033227158668</v>
+        <v>35.7117550694904</v>
       </c>
       <c r="E120" t="n">
-        <v>2674.651</v>
+        <v>2184.195566666667</v>
       </c>
       <c r="F120" t="n">
-        <v>1.365729999999999</v>
+        <v>4.921436666666667</v>
       </c>
       <c r="G120" t="n">
-        <v>3.6</v>
+        <v>7.949999999999999</v>
       </c>
       <c r="H120" t="n">
-        <v>4.583333333333334</v>
+        <v>9.383333333333333</v>
       </c>
       <c r="I120" t="n">
-        <v>3.6</v>
+        <v>7.949999999999999</v>
       </c>
       <c r="J120" t="n">
-        <v>4.583333333333334</v>
+        <v>9.383333333333333</v>
       </c>
       <c r="K120" t="n">
-        <v>3.6</v>
+        <v>7.949999999999999</v>
       </c>
       <c r="L120" t="n">
-        <v>4.583333333333334</v>
+        <v>9.383333333333333</v>
       </c>
       <c r="M120" t="n">
         <v>0.3333333333333333</v>
@@ -5729,37 +5729,37 @@
         <v>119</v>
       </c>
       <c r="B121" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C121" t="n">
-        <v>-21.4142706428761</v>
+        <v>-13.5633988058324</v>
       </c>
       <c r="D121" t="n">
-        <v>-0.0177783553764303</v>
+        <v>35.7117550694904</v>
       </c>
       <c r="E121" t="n">
-        <v>3000</v>
+        <v>2184.195566666667</v>
       </c>
       <c r="F121" t="n">
-        <v>10.0436</v>
+        <v>4.921436666666667</v>
       </c>
       <c r="G121" t="n">
-        <v>11.31666666666667</v>
+        <v>7.949999999999999</v>
       </c>
       <c r="H121" t="n">
-        <v>12.75</v>
+        <v>9.383333333333333</v>
       </c>
       <c r="I121" t="n">
-        <v>11.31666666666667</v>
+        <v>7.949999999999999</v>
       </c>
       <c r="J121" t="n">
-        <v>12.75</v>
+        <v>9.383333333333333</v>
       </c>
       <c r="K121" t="n">
-        <v>11.31666666666667</v>
+        <v>7.949999999999999</v>
       </c>
       <c r="L121" t="n">
-        <v>12.75</v>
+        <v>9.383333333333333</v>
       </c>
       <c r="M121" t="n">
         <v>0.3333333333333333</v>
@@ -5773,37 +5773,37 @@
         <v>120</v>
       </c>
       <c r="B122" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C122" t="n">
-        <v>-21.4142706428761</v>
+        <v>10.9979131123698</v>
       </c>
       <c r="D122" t="n">
-        <v>-0.0177783553764303</v>
+        <v>-14.3764159181384</v>
       </c>
       <c r="E122" t="n">
-        <v>67.06880000000001</v>
+        <v>2791.0139</v>
       </c>
       <c r="F122" t="n">
-        <v>0</v>
+        <v>8.679600000000001</v>
       </c>
       <c r="G122" t="n">
-        <v>11.31666666666667</v>
+        <v>1.166666666666666</v>
       </c>
       <c r="H122" t="n">
-        <v>12.75</v>
+        <v>2.550000000000001</v>
       </c>
       <c r="I122" t="n">
-        <v>11.31666666666667</v>
+        <v>1.166666666666666</v>
       </c>
       <c r="J122" t="n">
-        <v>12.75</v>
+        <v>2.550000000000001</v>
       </c>
       <c r="K122" t="n">
-        <v>11.31666666666667</v>
+        <v>1.166666666666666</v>
       </c>
       <c r="L122" t="n">
-        <v>12.75</v>
+        <v>2.550000000000001</v>
       </c>
       <c r="M122" t="n">
         <v>0.3333333333333333</v>
@@ -5817,37 +5817,37 @@
         <v>121</v>
       </c>
       <c r="B123" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C123" t="n">
-        <v>3.34995943599543</v>
+        <v>15.2856210779678</v>
       </c>
       <c r="D123" t="n">
-        <v>31.3048933804785</v>
+        <v>-28.0053274336459</v>
       </c>
       <c r="E123" t="n">
-        <v>2725.3232</v>
+        <v>2860.4382</v>
       </c>
       <c r="F123" t="n">
-        <v>7.50056</v>
+        <v>8.924939999999999</v>
       </c>
       <c r="G123" t="n">
-        <v>11.21666666666667</v>
+        <v>10.86666666666667</v>
       </c>
       <c r="H123" t="n">
-        <v>12.58333333333333</v>
+        <v>12.26666666666667</v>
       </c>
       <c r="I123" t="n">
-        <v>11.21666666666667</v>
+        <v>10.86666666666667</v>
       </c>
       <c r="J123" t="n">
-        <v>12.58333333333333</v>
+        <v>12.26666666666667</v>
       </c>
       <c r="K123" t="n">
-        <v>11.21666666666667</v>
+        <v>10.86666666666667</v>
       </c>
       <c r="L123" t="n">
-        <v>12.58333333333333</v>
+        <v>12.26666666666667</v>
       </c>
       <c r="M123" t="n">
         <v>0.3333333333333333</v>
@@ -5861,37 +5861,37 @@
         <v>122</v>
       </c>
       <c r="B124" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C124" t="n">
-        <v>-19.079563342021</v>
+        <v>-6.89120148830592</v>
       </c>
       <c r="D124" t="n">
-        <v>3.11570859008743</v>
+        <v>36.8225598526382</v>
       </c>
       <c r="E124" t="n">
-        <v>2996.466</v>
+        <v>2471.662466666667</v>
       </c>
       <c r="F124" t="n">
-        <v>7.5462</v>
+        <v>5.810966666666666</v>
       </c>
       <c r="G124" t="n">
-        <v>5.366666666666667</v>
+        <v>10.51666666666667</v>
       </c>
       <c r="H124" t="n">
-        <v>6.283333333333333</v>
+        <v>11.8</v>
       </c>
       <c r="I124" t="n">
-        <v>5.366666666666667</v>
+        <v>10.51666666666667</v>
       </c>
       <c r="J124" t="n">
-        <v>6.283333333333333</v>
+        <v>11.8</v>
       </c>
       <c r="K124" t="n">
-        <v>5.366666666666667</v>
+        <v>10.51666666666667</v>
       </c>
       <c r="L124" t="n">
-        <v>6.283333333333333</v>
+        <v>11.8</v>
       </c>
       <c r="M124" t="n">
         <v>0.3333333333333333</v>
@@ -5905,37 +5905,37 @@
         <v>123</v>
       </c>
       <c r="B125" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C125" t="n">
-        <v>-14.4202892616212</v>
+        <v>-6.89120148830592</v>
       </c>
       <c r="D125" t="n">
-        <v>0.438615616091085</v>
+        <v>36.8225598526382</v>
       </c>
       <c r="E125" t="n">
-        <v>3000</v>
+        <v>2471.662466666667</v>
       </c>
       <c r="F125" t="n">
-        <v>10.93872</v>
+        <v>5.810966666666666</v>
       </c>
       <c r="G125" t="n">
-        <v>5.183333333333334</v>
+        <v>10.51666666666667</v>
       </c>
       <c r="H125" t="n">
-        <v>6.166666666666666</v>
+        <v>11.8</v>
       </c>
       <c r="I125" t="n">
-        <v>5.183333333333334</v>
+        <v>10.51666666666667</v>
       </c>
       <c r="J125" t="n">
-        <v>6.166666666666666</v>
+        <v>11.8</v>
       </c>
       <c r="K125" t="n">
-        <v>5.183333333333334</v>
+        <v>10.51666666666667</v>
       </c>
       <c r="L125" t="n">
-        <v>6.166666666666666</v>
+        <v>11.8</v>
       </c>
       <c r="M125" t="n">
         <v>0.3333333333333333</v>
@@ -5949,37 +5949,37 @@
         <v>124</v>
       </c>
       <c r="B126" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C126" t="n">
-        <v>-14.4202892616212</v>
+        <v>-6.89120148830592</v>
       </c>
       <c r="D126" t="n">
-        <v>0.438615616091085</v>
+        <v>36.8225598526382</v>
       </c>
       <c r="E126" t="n">
-        <v>725.9722000000002</v>
+        <v>2471.662466666667</v>
       </c>
       <c r="F126" t="n">
-        <v>0</v>
+        <v>5.810966666666666</v>
       </c>
       <c r="G126" t="n">
-        <v>5.183333333333334</v>
+        <v>10.51666666666667</v>
       </c>
       <c r="H126" t="n">
-        <v>6.166666666666666</v>
+        <v>11.8</v>
       </c>
       <c r="I126" t="n">
-        <v>5.183333333333334</v>
+        <v>10.51666666666667</v>
       </c>
       <c r="J126" t="n">
-        <v>6.166666666666666</v>
+        <v>11.8</v>
       </c>
       <c r="K126" t="n">
-        <v>5.183333333333334</v>
+        <v>10.51666666666667</v>
       </c>
       <c r="L126" t="n">
-        <v>6.166666666666666</v>
+        <v>11.8</v>
       </c>
       <c r="M126" t="n">
         <v>0.3333333333333333</v>
@@ -5993,37 +5993,37 @@
         <v>125</v>
       </c>
       <c r="B127" t="n">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C127" t="n">
-        <v>17.8559660659719</v>
+        <v>-10.2808334321244</v>
       </c>
       <c r="D127" t="n">
-        <v>-34.5128170174245</v>
+        <v>29.5869615259404</v>
       </c>
       <c r="E127" t="n">
-        <v>3000</v>
+        <v>2288.8859</v>
       </c>
       <c r="F127" t="n">
-        <v>7.85752</v>
+        <v>6.06402</v>
       </c>
       <c r="G127" t="n">
-        <v>6.416666666666666</v>
+        <v>7.766666666666667</v>
       </c>
       <c r="H127" t="n">
-        <v>7.75</v>
+        <v>9.149999999999999</v>
       </c>
       <c r="I127" t="n">
-        <v>6.416666666666666</v>
+        <v>7.766666666666667</v>
       </c>
       <c r="J127" t="n">
-        <v>7.75</v>
+        <v>9.149999999999999</v>
       </c>
       <c r="K127" t="n">
-        <v>6.416666666666666</v>
+        <v>7.766666666666667</v>
       </c>
       <c r="L127" t="n">
-        <v>7.75</v>
+        <v>9.149999999999999</v>
       </c>
       <c r="M127" t="n">
         <v>0.3333333333333333</v>
@@ -6037,37 +6037,37 @@
         <v>126</v>
       </c>
       <c r="B128" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C128" t="n">
-        <v>17.8559660659719</v>
+        <v>-12.9249626484284</v>
       </c>
       <c r="D128" t="n">
-        <v>-34.5128170174245</v>
+        <v>-33.6033227158668</v>
       </c>
       <c r="E128" t="n">
-        <v>17.4405999999999</v>
+        <v>2837.3255</v>
       </c>
       <c r="F128" t="n">
-        <v>0</v>
+        <v>8.182865</v>
       </c>
       <c r="G128" t="n">
-        <v>6.416666666666666</v>
+        <v>3.6</v>
       </c>
       <c r="H128" t="n">
-        <v>7.75</v>
+        <v>4.583333333333334</v>
       </c>
       <c r="I128" t="n">
-        <v>6.416666666666666</v>
+        <v>3.6</v>
       </c>
       <c r="J128" t="n">
-        <v>7.75</v>
+        <v>4.583333333333334</v>
       </c>
       <c r="K128" t="n">
-        <v>6.416666666666666</v>
+        <v>3.6</v>
       </c>
       <c r="L128" t="n">
-        <v>7.75</v>
+        <v>4.583333333333334</v>
       </c>
       <c r="M128" t="n">
         <v>0.3333333333333333</v>
@@ -6081,37 +6081,37 @@
         <v>127</v>
       </c>
       <c r="B129" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C129" t="n">
-        <v>6.17248271231953</v>
+        <v>-12.9249626484284</v>
       </c>
       <c r="D129" t="n">
-        <v>-11.9739943806008</v>
+        <v>-33.6033227158668</v>
       </c>
       <c r="E129" t="n">
-        <v>1256.3017</v>
+        <v>2837.3255</v>
       </c>
       <c r="F129" t="n">
-        <v>3.94079</v>
+        <v>8.182865</v>
       </c>
       <c r="G129" t="n">
-        <v>1.15</v>
+        <v>3.6</v>
       </c>
       <c r="H129" t="n">
-        <v>2.416666666666666</v>
+        <v>4.583333333333334</v>
       </c>
       <c r="I129" t="n">
-        <v>1.15</v>
+        <v>3.6</v>
       </c>
       <c r="J129" t="n">
-        <v>2.416666666666666</v>
+        <v>4.583333333333334</v>
       </c>
       <c r="K129" t="n">
-        <v>1.15</v>
+        <v>3.6</v>
       </c>
       <c r="L129" t="n">
-        <v>2.416666666666666</v>
+        <v>4.583333333333334</v>
       </c>
       <c r="M129" t="n">
         <v>0.3333333333333333</v>
@@ -6125,37 +6125,37 @@
         <v>128</v>
       </c>
       <c r="B130" t="n">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C130" t="n">
-        <v>-8.90340842896458</v>
+        <v>-21.4142706428761</v>
       </c>
       <c r="D130" t="n">
-        <v>-33.0969833073601</v>
+        <v>-0.0177783553764303</v>
       </c>
       <c r="E130" t="n">
-        <v>1968.2668</v>
+        <v>1533.5344</v>
       </c>
       <c r="F130" t="n">
-        <v>5.09682</v>
+        <v>5.0218</v>
       </c>
       <c r="G130" t="n">
-        <v>10.93333333333333</v>
+        <v>11.31666666666667</v>
       </c>
       <c r="H130" t="n">
-        <v>12.28333333333333</v>
+        <v>12.75</v>
       </c>
       <c r="I130" t="n">
-        <v>10.93333333333333</v>
+        <v>11.31666666666667</v>
       </c>
       <c r="J130" t="n">
-        <v>12.28333333333333</v>
+        <v>12.75</v>
       </c>
       <c r="K130" t="n">
-        <v>10.93333333333333</v>
+        <v>11.31666666666667</v>
       </c>
       <c r="L130" t="n">
-        <v>12.28333333333333</v>
+        <v>12.75</v>
       </c>
       <c r="M130" t="n">
         <v>0.3333333333333333</v>
@@ -6169,37 +6169,37 @@
         <v>129</v>
       </c>
       <c r="B131" t="n">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C131" t="n">
-        <v>0.735897737284067</v>
+        <v>-21.4142706428761</v>
       </c>
       <c r="D131" t="n">
-        <v>-11.817830191293</v>
+        <v>-0.0177783553764303</v>
       </c>
       <c r="E131" t="n">
-        <v>1882.391</v>
+        <v>1533.5344</v>
       </c>
       <c r="F131" t="n">
-        <v>4.7241</v>
+        <v>5.0218</v>
       </c>
       <c r="G131" t="n">
-        <v>11.9</v>
+        <v>11.31666666666667</v>
       </c>
       <c r="H131" t="n">
-        <v>12.91666666666667</v>
+        <v>12.75</v>
       </c>
       <c r="I131" t="n">
-        <v>11.9</v>
+        <v>11.31666666666667</v>
       </c>
       <c r="J131" t="n">
-        <v>12.91666666666667</v>
+        <v>12.75</v>
       </c>
       <c r="K131" t="n">
-        <v>11.9</v>
+        <v>11.31666666666667</v>
       </c>
       <c r="L131" t="n">
-        <v>12.91666666666667</v>
+        <v>12.75</v>
       </c>
       <c r="M131" t="n">
         <v>0.3333333333333333</v>
@@ -6213,37 +6213,37 @@
         <v>130</v>
       </c>
       <c r="B132" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C132" t="n">
-        <v>6.48665021130649</v>
+        <v>3.34995943599543</v>
       </c>
       <c r="D132" t="n">
-        <v>-18.7369565714111</v>
+        <v>31.3048933804785</v>
       </c>
       <c r="E132" t="n">
-        <v>2315.13</v>
+        <v>2725.3232</v>
       </c>
       <c r="F132" t="n">
-        <v>7.36652</v>
+        <v>7.50056</v>
       </c>
       <c r="G132" t="n">
-        <v>1.583333333333334</v>
+        <v>11.21666666666667</v>
       </c>
       <c r="H132" t="n">
-        <v>2.75</v>
+        <v>12.58333333333333</v>
       </c>
       <c r="I132" t="n">
-        <v>1.583333333333334</v>
+        <v>11.21666666666667</v>
       </c>
       <c r="J132" t="n">
-        <v>2.75</v>
+        <v>12.58333333333333</v>
       </c>
       <c r="K132" t="n">
-        <v>1.583333333333334</v>
+        <v>11.21666666666667</v>
       </c>
       <c r="L132" t="n">
-        <v>2.75</v>
+        <v>12.58333333333333</v>
       </c>
       <c r="M132" t="n">
         <v>0.3333333333333333</v>
@@ -6257,37 +6257,37 @@
         <v>131</v>
       </c>
       <c r="B133" t="n">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C133" t="n">
-        <v>-16.1633724807616</v>
+        <v>-19.079563342021</v>
       </c>
       <c r="D133" t="n">
-        <v>17.956024307724</v>
+        <v>3.11570859008743</v>
       </c>
       <c r="E133" t="n">
-        <v>506.3405000000001</v>
+        <v>2996.466</v>
       </c>
       <c r="F133" t="n">
-        <v>1.90288</v>
+        <v>7.5462</v>
       </c>
       <c r="G133" t="n">
-        <v>9.683333333333334</v>
+        <v>5.366666666666667</v>
       </c>
       <c r="H133" t="n">
-        <v>10.56666666666667</v>
+        <v>6.283333333333333</v>
       </c>
       <c r="I133" t="n">
-        <v>9.683333333333334</v>
+        <v>5.366666666666667</v>
       </c>
       <c r="J133" t="n">
-        <v>10.56666666666667</v>
+        <v>6.283333333333333</v>
       </c>
       <c r="K133" t="n">
-        <v>9.683333333333334</v>
+        <v>5.366666666666667</v>
       </c>
       <c r="L133" t="n">
-        <v>10.56666666666667</v>
+        <v>6.283333333333333</v>
       </c>
       <c r="M133" t="n">
         <v>0.3333333333333333</v>
@@ -6301,37 +6301,37 @@
         <v>132</v>
       </c>
       <c r="B134" t="n">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C134" t="n">
-        <v>12.7485642351257</v>
+        <v>-14.4202892616212</v>
       </c>
       <c r="D134" t="n">
-        <v>-13.9951114455965</v>
+        <v>0.438615616091085</v>
       </c>
       <c r="E134" t="n">
-        <v>1343.6123</v>
+        <v>1862.9861</v>
       </c>
       <c r="F134" t="n">
-        <v>3.64803</v>
+        <v>5.46936</v>
       </c>
       <c r="G134" t="n">
-        <v>9.066666666666666</v>
+        <v>5.183333333333334</v>
       </c>
       <c r="H134" t="n">
-        <v>10.13333333333333</v>
+        <v>6.166666666666666</v>
       </c>
       <c r="I134" t="n">
-        <v>9.066666666666666</v>
+        <v>5.183333333333334</v>
       </c>
       <c r="J134" t="n">
-        <v>10.13333333333333</v>
+        <v>6.166666666666666</v>
       </c>
       <c r="K134" t="n">
-        <v>9.066666666666666</v>
+        <v>5.183333333333334</v>
       </c>
       <c r="L134" t="n">
-        <v>10.13333333333333</v>
+        <v>6.166666666666666</v>
       </c>
       <c r="M134" t="n">
         <v>0.3333333333333333</v>
@@ -6345,37 +6345,37 @@
         <v>133</v>
       </c>
       <c r="B135" t="n">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="C135" t="n">
-        <v>14.5060829317191</v>
+        <v>-14.4202892616212</v>
       </c>
       <c r="D135" t="n">
-        <v>-14.9096560728536</v>
+        <v>0.438615616091085</v>
       </c>
       <c r="E135" t="n">
-        <v>1493.082</v>
+        <v>1862.9861</v>
       </c>
       <c r="F135" t="n">
-        <v>4.67276</v>
+        <v>5.46936</v>
       </c>
       <c r="G135" t="n">
-        <v>3.683333333333334</v>
+        <v>5.183333333333334</v>
       </c>
       <c r="H135" t="n">
-        <v>5.033333333333333</v>
+        <v>6.166666666666666</v>
       </c>
       <c r="I135" t="n">
-        <v>3.683333333333334</v>
+        <v>5.183333333333334</v>
       </c>
       <c r="J135" t="n">
-        <v>5.033333333333333</v>
+        <v>6.166666666666666</v>
       </c>
       <c r="K135" t="n">
-        <v>3.683333333333334</v>
+        <v>5.183333333333334</v>
       </c>
       <c r="L135" t="n">
-        <v>5.033333333333333</v>
+        <v>6.166666666666666</v>
       </c>
       <c r="M135" t="n">
         <v>0.3333333333333333</v>
@@ -6389,37 +6389,37 @@
         <v>134</v>
       </c>
       <c r="B136" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C136" t="n">
-        <v>17.5691594969999</v>
+        <v>17.8559660659719</v>
       </c>
       <c r="D136" t="n">
-        <v>23.7073613386205</v>
+        <v>-34.5128170174245</v>
       </c>
       <c r="E136" t="n">
-        <v>926.8409</v>
+        <v>1508.7203</v>
       </c>
       <c r="F136" t="n">
-        <v>2.79316</v>
+        <v>3.92876</v>
       </c>
       <c r="G136" t="n">
-        <v>5.800000000000001</v>
+        <v>6.416666666666666</v>
       </c>
       <c r="H136" t="n">
-        <v>6.716666666666667</v>
+        <v>7.75</v>
       </c>
       <c r="I136" t="n">
-        <v>5.800000000000001</v>
+        <v>6.416666666666666</v>
       </c>
       <c r="J136" t="n">
-        <v>6.716666666666667</v>
+        <v>7.75</v>
       </c>
       <c r="K136" t="n">
-        <v>5.800000000000001</v>
+        <v>6.416666666666666</v>
       </c>
       <c r="L136" t="n">
-        <v>6.716666666666667</v>
+        <v>7.75</v>
       </c>
       <c r="M136" t="n">
         <v>0.3333333333333333</v>
@@ -6433,37 +6433,37 @@
         <v>135</v>
       </c>
       <c r="B137" t="n">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="C137" t="n">
-        <v>-32.2887483255588</v>
+        <v>17.8559660659719</v>
       </c>
       <c r="D137" t="n">
-        <v>-6.33777906329211</v>
+        <v>-34.5128170174245</v>
       </c>
       <c r="E137" t="n">
-        <v>1605.2619</v>
+        <v>1508.7203</v>
       </c>
       <c r="F137" t="n">
-        <v>4.36803</v>
+        <v>3.92876</v>
       </c>
       <c r="G137" t="n">
-        <v>8.233333333333334</v>
+        <v>6.416666666666666</v>
       </c>
       <c r="H137" t="n">
-        <v>9.149999999999999</v>
+        <v>7.75</v>
       </c>
       <c r="I137" t="n">
-        <v>8.233333333333334</v>
+        <v>6.416666666666666</v>
       </c>
       <c r="J137" t="n">
-        <v>9.149999999999999</v>
+        <v>7.75</v>
       </c>
       <c r="K137" t="n">
-        <v>8.233333333333334</v>
+        <v>6.416666666666666</v>
       </c>
       <c r="L137" t="n">
-        <v>9.149999999999999</v>
+        <v>7.75</v>
       </c>
       <c r="M137" t="n">
         <v>0.3333333333333333</v>
@@ -6477,37 +6477,37 @@
         <v>136</v>
       </c>
       <c r="B138" t="n">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="C138" t="n">
-        <v>5.2885051532574</v>
+        <v>6.17248271231953</v>
       </c>
       <c r="D138" t="n">
-        <v>-10.610672970256</v>
+        <v>-11.9739943806008</v>
       </c>
       <c r="E138" t="n">
-        <v>593.8303</v>
+        <v>1256.3017</v>
       </c>
       <c r="F138" t="n">
-        <v>1.42095</v>
+        <v>3.94079</v>
       </c>
       <c r="G138" t="n">
-        <v>1.85</v>
+        <v>1.15</v>
       </c>
       <c r="H138" t="n">
-        <v>3.033333333333333</v>
+        <v>2.416666666666666</v>
       </c>
       <c r="I138" t="n">
-        <v>1.85</v>
+        <v>1.15</v>
       </c>
       <c r="J138" t="n">
-        <v>3.033333333333333</v>
+        <v>2.416666666666666</v>
       </c>
       <c r="K138" t="n">
-        <v>1.85</v>
+        <v>1.15</v>
       </c>
       <c r="L138" t="n">
-        <v>3.033333333333333</v>
+        <v>2.416666666666666</v>
       </c>
       <c r="M138" t="n">
         <v>0.3333333333333333</v>
@@ -6521,37 +6521,37 @@
         <v>137</v>
       </c>
       <c r="B139" t="n">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="C139" t="n">
-        <v>22.2501851106262</v>
+        <v>-8.90340842896458</v>
       </c>
       <c r="D139" t="n">
-        <v>3.36277307745693</v>
+        <v>-33.0969833073601</v>
       </c>
       <c r="E139" t="n">
-        <v>532.895</v>
+        <v>1968.2668</v>
       </c>
       <c r="F139" t="n">
-        <v>2.84858</v>
+        <v>5.09682</v>
       </c>
       <c r="G139" t="n">
-        <v>2.1</v>
+        <v>10.93333333333333</v>
       </c>
       <c r="H139" t="n">
-        <v>3.583333333333334</v>
+        <v>12.28333333333333</v>
       </c>
       <c r="I139" t="n">
-        <v>2.1</v>
+        <v>10.93333333333333</v>
       </c>
       <c r="J139" t="n">
-        <v>3.583333333333334</v>
+        <v>12.28333333333333</v>
       </c>
       <c r="K139" t="n">
-        <v>2.1</v>
+        <v>10.93333333333333</v>
       </c>
       <c r="L139" t="n">
-        <v>3.583333333333334</v>
+        <v>12.28333333333333</v>
       </c>
       <c r="M139" t="n">
         <v>0.3333333333333333</v>
@@ -6565,37 +6565,37 @@
         <v>138</v>
       </c>
       <c r="B140" t="n">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="C140" t="n">
-        <v>-5.07881748714319</v>
+        <v>0.735897737284067</v>
       </c>
       <c r="D140" t="n">
-        <v>-34.9821210394225</v>
+        <v>-11.817830191293</v>
       </c>
       <c r="E140" t="n">
-        <v>180.291</v>
+        <v>1882.391</v>
       </c>
       <c r="F140" t="n">
-        <v>0.46473</v>
+        <v>4.7241</v>
       </c>
       <c r="G140" t="n">
-        <v>3.300000000000001</v>
+        <v>11.9</v>
       </c>
       <c r="H140" t="n">
-        <v>4.699999999999999</v>
+        <v>12.91666666666667</v>
       </c>
       <c r="I140" t="n">
-        <v>3.300000000000001</v>
+        <v>11.9</v>
       </c>
       <c r="J140" t="n">
-        <v>4.699999999999999</v>
+        <v>12.91666666666667</v>
       </c>
       <c r="K140" t="n">
-        <v>3.300000000000001</v>
+        <v>11.9</v>
       </c>
       <c r="L140" t="n">
-        <v>4.699999999999999</v>
+        <v>12.91666666666667</v>
       </c>
       <c r="M140" t="n">
         <v>0.3333333333333333</v>
@@ -6609,37 +6609,37 @@
         <v>139</v>
       </c>
       <c r="B141" t="n">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="C141" t="n">
-        <v>10.1634114043108</v>
+        <v>6.48665021130649</v>
       </c>
       <c r="D141" t="n">
-        <v>23.9868549043046</v>
+        <v>-18.7369565714111</v>
       </c>
       <c r="E141" t="n">
-        <v>79.6007</v>
+        <v>2315.13</v>
       </c>
       <c r="F141" t="n">
-        <v>0.5374800000000001</v>
+        <v>7.36652</v>
       </c>
       <c r="G141" t="n">
-        <v>2.066666666666666</v>
+        <v>1.583333333333334</v>
       </c>
       <c r="H141" t="n">
-        <v>3.316666666666666</v>
+        <v>2.75</v>
       </c>
       <c r="I141" t="n">
-        <v>2.066666666666666</v>
+        <v>1.583333333333334</v>
       </c>
       <c r="J141" t="n">
-        <v>3.316666666666666</v>
+        <v>2.75</v>
       </c>
       <c r="K141" t="n">
-        <v>2.066666666666666</v>
+        <v>1.583333333333334</v>
       </c>
       <c r="L141" t="n">
-        <v>3.316666666666666</v>
+        <v>2.75</v>
       </c>
       <c r="M141" t="n">
         <v>0.3333333333333333</v>
@@ -6653,37 +6653,37 @@
         <v>140</v>
       </c>
       <c r="B142" t="n">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C142" t="n">
-        <v>-25.5470740390242</v>
+        <v>-16.1633724807616</v>
       </c>
       <c r="D142" t="n">
-        <v>-15.4194000905651</v>
+        <v>17.956024307724</v>
       </c>
       <c r="E142" t="n">
-        <v>46.248</v>
+        <v>506.3405000000001</v>
       </c>
       <c r="F142" t="n">
-        <v>0.2733</v>
+        <v>1.90288</v>
       </c>
       <c r="G142" t="n">
-        <v>8.183333333333334</v>
+        <v>9.683333333333334</v>
       </c>
       <c r="H142" t="n">
-        <v>9.216666666666665</v>
+        <v>10.56666666666667</v>
       </c>
       <c r="I142" t="n">
-        <v>8.183333333333334</v>
+        <v>9.683333333333334</v>
       </c>
       <c r="J142" t="n">
-        <v>9.216666666666665</v>
+        <v>10.56666666666667</v>
       </c>
       <c r="K142" t="n">
-        <v>8.183333333333334</v>
+        <v>9.683333333333334</v>
       </c>
       <c r="L142" t="n">
-        <v>9.216666666666665</v>
+        <v>10.56666666666667</v>
       </c>
       <c r="M142" t="n">
         <v>0.3333333333333333</v>
@@ -6697,37 +6697,37 @@
         <v>141</v>
       </c>
       <c r="B143" t="n">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="C143" t="n">
-        <v>-33.6060651581938</v>
+        <v>12.7485642351257</v>
       </c>
       <c r="D143" t="n">
-        <v>2.20467172657312</v>
+        <v>-13.9951114455965</v>
       </c>
       <c r="E143" t="n">
-        <v>100.6088</v>
+        <v>1343.6123</v>
       </c>
       <c r="F143" t="n">
-        <v>0.22653</v>
+        <v>3.64803</v>
       </c>
       <c r="G143" t="n">
-        <v>5.833333333333334</v>
+        <v>9.066666666666666</v>
       </c>
       <c r="H143" t="n">
-        <v>7.15</v>
+        <v>10.13333333333333</v>
       </c>
       <c r="I143" t="n">
-        <v>5.833333333333334</v>
+        <v>9.066666666666666</v>
       </c>
       <c r="J143" t="n">
-        <v>7.15</v>
+        <v>10.13333333333333</v>
       </c>
       <c r="K143" t="n">
-        <v>5.833333333333334</v>
+        <v>9.066666666666666</v>
       </c>
       <c r="L143" t="n">
-        <v>7.15</v>
+        <v>10.13333333333333</v>
       </c>
       <c r="M143" t="n">
         <v>0.3333333333333333</v>
@@ -6741,37 +6741,37 @@
         <v>142</v>
       </c>
       <c r="B144" t="n">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="C144" t="n">
-        <v>-5.63196878175453</v>
+        <v>14.5060829317191</v>
       </c>
       <c r="D144" t="n">
-        <v>-30.3321609421464</v>
+        <v>-14.9096560728536</v>
       </c>
       <c r="E144" t="n">
-        <v>70.435</v>
+        <v>1493.082</v>
       </c>
       <c r="F144" t="n">
-        <v>0.39102</v>
+        <v>4.67276</v>
       </c>
       <c r="G144" t="n">
-        <v>8.666666666666668</v>
+        <v>3.683333333333334</v>
       </c>
       <c r="H144" t="n">
-        <v>9.983333333333334</v>
+        <v>5.033333333333333</v>
       </c>
       <c r="I144" t="n">
-        <v>8.666666666666668</v>
+        <v>3.683333333333334</v>
       </c>
       <c r="J144" t="n">
-        <v>9.983333333333334</v>
+        <v>5.033333333333333</v>
       </c>
       <c r="K144" t="n">
-        <v>8.666666666666668</v>
+        <v>3.683333333333334</v>
       </c>
       <c r="L144" t="n">
-        <v>9.983333333333334</v>
+        <v>5.033333333333333</v>
       </c>
       <c r="M144" t="n">
         <v>0.3333333333333333</v>
@@ -6785,37 +6785,37 @@
         <v>143</v>
       </c>
       <c r="B145" t="n">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C145" t="n">
-        <v>8.28368192850442</v>
+        <v>17.5691594969999</v>
       </c>
       <c r="D145" t="n">
-        <v>17.7735226449337</v>
+        <v>23.7073613386205</v>
       </c>
       <c r="E145" t="n">
-        <v>1524.5125</v>
+        <v>926.8409</v>
       </c>
       <c r="F145" t="n">
-        <v>3.82045</v>
+        <v>2.79316</v>
       </c>
       <c r="G145" t="n">
-        <v>6.783333333333333</v>
+        <v>5.800000000000001</v>
       </c>
       <c r="H145" t="n">
-        <v>8.116666666666667</v>
+        <v>6.716666666666667</v>
       </c>
       <c r="I145" t="n">
-        <v>6.783333333333333</v>
+        <v>5.800000000000001</v>
       </c>
       <c r="J145" t="n">
-        <v>8.116666666666667</v>
+        <v>6.716666666666667</v>
       </c>
       <c r="K145" t="n">
-        <v>6.783333333333333</v>
+        <v>5.800000000000001</v>
       </c>
       <c r="L145" t="n">
-        <v>8.116666666666667</v>
+        <v>6.716666666666667</v>
       </c>
       <c r="M145" t="n">
         <v>0.3333333333333333</v>
@@ -6829,37 +6829,37 @@
         <v>144</v>
       </c>
       <c r="B146" t="n">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="C146" t="n">
-        <v>0.746941949932783</v>
+        <v>-32.2887483255588</v>
       </c>
       <c r="D146" t="n">
-        <v>-28.7424167151396</v>
+        <v>-6.33777906329211</v>
       </c>
       <c r="E146" t="n">
-        <v>97.6961</v>
+        <v>1605.2619</v>
       </c>
       <c r="F146" t="n">
-        <v>0.33417</v>
+        <v>4.36803</v>
       </c>
       <c r="G146" t="n">
-        <v>4.866666666666667</v>
+        <v>8.233333333333334</v>
       </c>
       <c r="H146" t="n">
-        <v>6.233333333333333</v>
+        <v>9.149999999999999</v>
       </c>
       <c r="I146" t="n">
-        <v>4.866666666666667</v>
+        <v>8.233333333333334</v>
       </c>
       <c r="J146" t="n">
-        <v>6.233333333333333</v>
+        <v>9.149999999999999</v>
       </c>
       <c r="K146" t="n">
-        <v>4.866666666666667</v>
+        <v>8.233333333333334</v>
       </c>
       <c r="L146" t="n">
-        <v>6.233333333333333</v>
+        <v>9.149999999999999</v>
       </c>
       <c r="M146" t="n">
         <v>0.3333333333333333</v>
@@ -6873,37 +6873,37 @@
         <v>145</v>
       </c>
       <c r="B147" t="n">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C147" t="n">
-        <v>21.835155243347</v>
+        <v>5.2885051532574</v>
       </c>
       <c r="D147" t="n">
-        <v>-28.7650388212301</v>
+        <v>-10.610672970256</v>
       </c>
       <c r="E147" t="n">
-        <v>9.186</v>
+        <v>593.8303</v>
       </c>
       <c r="F147" t="n">
-        <v>0.01795</v>
+        <v>1.42095</v>
       </c>
       <c r="G147" t="n">
-        <v>4.716666666666667</v>
+        <v>1.85</v>
       </c>
       <c r="H147" t="n">
-        <v>5.949999999999999</v>
+        <v>3.033333333333333</v>
       </c>
       <c r="I147" t="n">
-        <v>4.716666666666667</v>
+        <v>1.85</v>
       </c>
       <c r="J147" t="n">
-        <v>5.949999999999999</v>
+        <v>3.033333333333333</v>
       </c>
       <c r="K147" t="n">
-        <v>4.716666666666667</v>
+        <v>1.85</v>
       </c>
       <c r="L147" t="n">
-        <v>5.949999999999999</v>
+        <v>3.033333333333333</v>
       </c>
       <c r="M147" t="n">
         <v>0.3333333333333333</v>
@@ -6917,37 +6917,37 @@
         <v>146</v>
       </c>
       <c r="B148" t="n">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="C148" t="n">
-        <v>-6.22843376493341</v>
+        <v>22.2501851106262</v>
       </c>
       <c r="D148" t="n">
-        <v>-26.8257702440231</v>
+        <v>3.36277307745693</v>
       </c>
       <c r="E148" t="n">
-        <v>109.35</v>
+        <v>532.895</v>
       </c>
       <c r="F148" t="n">
-        <v>0.29746</v>
+        <v>2.84858</v>
       </c>
       <c r="G148" t="n">
-        <v>6.416666666666666</v>
+        <v>2.1</v>
       </c>
       <c r="H148" t="n">
-        <v>7.566666666666666</v>
+        <v>3.583333333333334</v>
       </c>
       <c r="I148" t="n">
-        <v>6.416666666666666</v>
+        <v>2.1</v>
       </c>
       <c r="J148" t="n">
-        <v>7.566666666666666</v>
+        <v>3.583333333333334</v>
       </c>
       <c r="K148" t="n">
-        <v>6.416666666666666</v>
+        <v>2.1</v>
       </c>
       <c r="L148" t="n">
-        <v>7.566666666666666</v>
+        <v>3.583333333333334</v>
       </c>
       <c r="M148" t="n">
         <v>0.3333333333333333</v>
@@ -6961,37 +6961,37 @@
         <v>147</v>
       </c>
       <c r="B149" t="n">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="C149" t="n">
-        <v>7.2247850453069</v>
+        <v>-5.07881748714319</v>
       </c>
       <c r="D149" t="n">
-        <v>-12.1653024302337</v>
+        <v>-34.9821210394225</v>
       </c>
       <c r="E149" t="n">
-        <v>17.48</v>
+        <v>180.291</v>
       </c>
       <c r="F149" t="n">
-        <v>0.04201</v>
+        <v>0.46473</v>
       </c>
       <c r="G149" t="n">
-        <v>5.699999999999999</v>
+        <v>3.300000000000001</v>
       </c>
       <c r="H149" t="n">
-        <v>7.183333333333334</v>
+        <v>4.699999999999999</v>
       </c>
       <c r="I149" t="n">
-        <v>5.699999999999999</v>
+        <v>3.300000000000001</v>
       </c>
       <c r="J149" t="n">
-        <v>7.183333333333334</v>
+        <v>4.699999999999999</v>
       </c>
       <c r="K149" t="n">
-        <v>5.699999999999999</v>
+        <v>3.300000000000001</v>
       </c>
       <c r="L149" t="n">
-        <v>7.183333333333334</v>
+        <v>4.699999999999999</v>
       </c>
       <c r="M149" t="n">
         <v>0.3333333333333333</v>
@@ -7005,42 +7005,482 @@
         <v>148</v>
       </c>
       <c r="B150" t="n">
+        <v>88</v>
+      </c>
+      <c r="C150" t="n">
+        <v>10.1634114043108</v>
+      </c>
+      <c r="D150" t="n">
+        <v>23.9868549043046</v>
+      </c>
+      <c r="E150" t="n">
+        <v>79.6007</v>
+      </c>
+      <c r="F150" t="n">
+        <v>0.5374800000000001</v>
+      </c>
+      <c r="G150" t="n">
+        <v>2.066666666666666</v>
+      </c>
+      <c r="H150" t="n">
+        <v>3.316666666666666</v>
+      </c>
+      <c r="I150" t="n">
+        <v>2.066666666666666</v>
+      </c>
+      <c r="J150" t="n">
+        <v>3.316666666666666</v>
+      </c>
+      <c r="K150" t="n">
+        <v>2.066666666666666</v>
+      </c>
+      <c r="L150" t="n">
+        <v>3.316666666666666</v>
+      </c>
+      <c r="M150" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="N150" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>149</v>
+      </c>
+      <c r="B151" t="n">
+        <v>89</v>
+      </c>
+      <c r="C151" t="n">
+        <v>-25.5470740390242</v>
+      </c>
+      <c r="D151" t="n">
+        <v>-15.4194000905651</v>
+      </c>
+      <c r="E151" t="n">
+        <v>46.248</v>
+      </c>
+      <c r="F151" t="n">
+        <v>0.2733</v>
+      </c>
+      <c r="G151" t="n">
+        <v>8.183333333333334</v>
+      </c>
+      <c r="H151" t="n">
+        <v>9.216666666666665</v>
+      </c>
+      <c r="I151" t="n">
+        <v>8.183333333333334</v>
+      </c>
+      <c r="J151" t="n">
+        <v>9.216666666666665</v>
+      </c>
+      <c r="K151" t="n">
+        <v>8.183333333333334</v>
+      </c>
+      <c r="L151" t="n">
+        <v>9.216666666666665</v>
+      </c>
+      <c r="M151" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="N151" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>150</v>
+      </c>
+      <c r="B152" t="n">
+        <v>90</v>
+      </c>
+      <c r="C152" t="n">
+        <v>-33.6060651581938</v>
+      </c>
+      <c r="D152" t="n">
+        <v>2.20467172657312</v>
+      </c>
+      <c r="E152" t="n">
+        <v>100.6088</v>
+      </c>
+      <c r="F152" t="n">
+        <v>0.22653</v>
+      </c>
+      <c r="G152" t="n">
+        <v>5.833333333333334</v>
+      </c>
+      <c r="H152" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="I152" t="n">
+        <v>5.833333333333334</v>
+      </c>
+      <c r="J152" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="K152" t="n">
+        <v>5.833333333333334</v>
+      </c>
+      <c r="L152" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="M152" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="N152" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>151</v>
+      </c>
+      <c r="B153" t="n">
+        <v>91</v>
+      </c>
+      <c r="C153" t="n">
+        <v>-5.63196878175453</v>
+      </c>
+      <c r="D153" t="n">
+        <v>-30.3321609421464</v>
+      </c>
+      <c r="E153" t="n">
+        <v>70.435</v>
+      </c>
+      <c r="F153" t="n">
+        <v>0.39102</v>
+      </c>
+      <c r="G153" t="n">
+        <v>8.666666666666668</v>
+      </c>
+      <c r="H153" t="n">
+        <v>9.983333333333334</v>
+      </c>
+      <c r="I153" t="n">
+        <v>8.666666666666668</v>
+      </c>
+      <c r="J153" t="n">
+        <v>9.983333333333334</v>
+      </c>
+      <c r="K153" t="n">
+        <v>8.666666666666668</v>
+      </c>
+      <c r="L153" t="n">
+        <v>9.983333333333334</v>
+      </c>
+      <c r="M153" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="N153" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>152</v>
+      </c>
+      <c r="B154" t="n">
+        <v>92</v>
+      </c>
+      <c r="C154" t="n">
+        <v>8.28368192850442</v>
+      </c>
+      <c r="D154" t="n">
+        <v>17.7735226449337</v>
+      </c>
+      <c r="E154" t="n">
+        <v>1524.5125</v>
+      </c>
+      <c r="F154" t="n">
+        <v>3.82045</v>
+      </c>
+      <c r="G154" t="n">
+        <v>6.783333333333333</v>
+      </c>
+      <c r="H154" t="n">
+        <v>8.116666666666667</v>
+      </c>
+      <c r="I154" t="n">
+        <v>6.783333333333333</v>
+      </c>
+      <c r="J154" t="n">
+        <v>8.116666666666667</v>
+      </c>
+      <c r="K154" t="n">
+        <v>6.783333333333333</v>
+      </c>
+      <c r="L154" t="n">
+        <v>8.116666666666667</v>
+      </c>
+      <c r="M154" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="N154" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>153</v>
+      </c>
+      <c r="B155" t="n">
+        <v>93</v>
+      </c>
+      <c r="C155" t="n">
+        <v>0.746941949932783</v>
+      </c>
+      <c r="D155" t="n">
+        <v>-28.7424167151396</v>
+      </c>
+      <c r="E155" t="n">
+        <v>97.6961</v>
+      </c>
+      <c r="F155" t="n">
+        <v>0.33417</v>
+      </c>
+      <c r="G155" t="n">
+        <v>4.866666666666667</v>
+      </c>
+      <c r="H155" t="n">
+        <v>6.233333333333333</v>
+      </c>
+      <c r="I155" t="n">
+        <v>4.866666666666667</v>
+      </c>
+      <c r="J155" t="n">
+        <v>6.233333333333333</v>
+      </c>
+      <c r="K155" t="n">
+        <v>4.866666666666667</v>
+      </c>
+      <c r="L155" t="n">
+        <v>6.233333333333333</v>
+      </c>
+      <c r="M155" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="N155" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>154</v>
+      </c>
+      <c r="B156" t="n">
+        <v>94</v>
+      </c>
+      <c r="C156" t="n">
+        <v>21.835155243347</v>
+      </c>
+      <c r="D156" t="n">
+        <v>-28.7650388212301</v>
+      </c>
+      <c r="E156" t="n">
+        <v>9.186</v>
+      </c>
+      <c r="F156" t="n">
+        <v>0.01795</v>
+      </c>
+      <c r="G156" t="n">
+        <v>4.716666666666667</v>
+      </c>
+      <c r="H156" t="n">
+        <v>5.949999999999999</v>
+      </c>
+      <c r="I156" t="n">
+        <v>4.716666666666667</v>
+      </c>
+      <c r="J156" t="n">
+        <v>5.949999999999999</v>
+      </c>
+      <c r="K156" t="n">
+        <v>4.716666666666667</v>
+      </c>
+      <c r="L156" t="n">
+        <v>5.949999999999999</v>
+      </c>
+      <c r="M156" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="N156" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>155</v>
+      </c>
+      <c r="B157" t="n">
+        <v>95</v>
+      </c>
+      <c r="C157" t="n">
+        <v>-6.22843376493341</v>
+      </c>
+      <c r="D157" t="n">
+        <v>-26.8257702440231</v>
+      </c>
+      <c r="E157" t="n">
+        <v>109.35</v>
+      </c>
+      <c r="F157" t="n">
+        <v>0.29746</v>
+      </c>
+      <c r="G157" t="n">
+        <v>6.416666666666666</v>
+      </c>
+      <c r="H157" t="n">
+        <v>7.566666666666666</v>
+      </c>
+      <c r="I157" t="n">
+        <v>6.416666666666666</v>
+      </c>
+      <c r="J157" t="n">
+        <v>7.566666666666666</v>
+      </c>
+      <c r="K157" t="n">
+        <v>6.416666666666666</v>
+      </c>
+      <c r="L157" t="n">
+        <v>7.566666666666666</v>
+      </c>
+      <c r="M157" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="N157" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>156</v>
+      </c>
+      <c r="B158" t="n">
+        <v>96</v>
+      </c>
+      <c r="C158" t="n">
+        <v>-12.3209577741134</v>
+      </c>
+      <c r="D158" t="n">
+        <v>10.3641991683692</v>
+      </c>
+      <c r="E158" t="n">
+        <v>0</v>
+      </c>
+      <c r="F158" t="n">
+        <v>0</v>
+      </c>
+      <c r="G158" t="n">
+        <v>8.383333333333333</v>
+      </c>
+      <c r="H158" t="n">
+        <v>9.866666666666667</v>
+      </c>
+      <c r="I158" t="n">
+        <v>8.383333333333333</v>
+      </c>
+      <c r="J158" t="n">
+        <v>9.866666666666667</v>
+      </c>
+      <c r="K158" t="n">
+        <v>8.383333333333333</v>
+      </c>
+      <c r="L158" t="n">
+        <v>9.866666666666667</v>
+      </c>
+      <c r="M158" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="N158" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>157</v>
+      </c>
+      <c r="B159" t="n">
+        <v>97</v>
+      </c>
+      <c r="C159" t="n">
+        <v>7.2247850453069</v>
+      </c>
+      <c r="D159" t="n">
+        <v>-12.1653024302337</v>
+      </c>
+      <c r="E159" t="n">
+        <v>17.48</v>
+      </c>
+      <c r="F159" t="n">
+        <v>0.04201</v>
+      </c>
+      <c r="G159" t="n">
+        <v>5.699999999999999</v>
+      </c>
+      <c r="H159" t="n">
+        <v>7.183333333333334</v>
+      </c>
+      <c r="I159" t="n">
+        <v>5.699999999999999</v>
+      </c>
+      <c r="J159" t="n">
+        <v>7.183333333333334</v>
+      </c>
+      <c r="K159" t="n">
+        <v>5.699999999999999</v>
+      </c>
+      <c r="L159" t="n">
+        <v>7.183333333333334</v>
+      </c>
+      <c r="M159" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="N159" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>158</v>
+      </c>
+      <c r="B160" t="n">
         <v>98</v>
       </c>
-      <c r="C150" t="n">
+      <c r="C160" t="n">
         <v>-19.3415293006296</v>
       </c>
-      <c r="D150" t="n">
+      <c r="D160" t="n">
         <v>-35.0080570685232</v>
       </c>
-      <c r="E150" t="n">
+      <c r="E160" t="n">
         <v>25.5</v>
       </c>
-      <c r="F150" t="n">
+      <c r="F160" t="n">
         <v>0.0646</v>
       </c>
-      <c r="G150" t="n">
+      <c r="G160" t="n">
         <v>11.3</v>
       </c>
-      <c r="H150" t="n">
+      <c r="H160" t="n">
         <v>12.68333333333333</v>
       </c>
-      <c r="I150" t="n">
+      <c r="I160" t="n">
         <v>11.3</v>
       </c>
-      <c r="J150" t="n">
+      <c r="J160" t="n">
         <v>12.68333333333333</v>
       </c>
-      <c r="K150" t="n">
+      <c r="K160" t="n">
         <v>11.3</v>
       </c>
-      <c r="L150" t="n">
+      <c r="L160" t="n">
         <v>12.68333333333333</v>
       </c>
-      <c r="M150" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="N150" t="b">
+      <c r="M160" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="N160" t="b">
         <v>0</v>
       </c>
     </row>

--- a/cleaned_data_p2.xlsx
+++ b/cleaned_data_p2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="cleaned_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cleaned_data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,76 +425,76 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N160"/>
+  <dimension ref="A1:N150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>node_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>original_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>y</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>demand_weight_kg</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>demand_volume_m3</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ready_time_rel8</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>due_time_rel8</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>tw_fuel_ready</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>tw_fuel_due</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>tw_elec_ready</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tw_elec_due</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>service_time_h</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>is_green_zone</t>
         </is>
@@ -537,37 +549,37 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7459619830659699</v>
+        <v>3.49201994126609</v>
       </c>
       <c r="D3" t="n">
-        <v>6.12744724329777</v>
+        <v>-2.09987360600907</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>14.89</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>0.04317</v>
       </c>
       <c r="G3" t="n">
-        <v>3.550000000000001</v>
+        <v>9.883333333333333</v>
       </c>
       <c r="H3" t="n">
-        <v>4.366666666666667</v>
+        <v>10.81666666666667</v>
       </c>
       <c r="I3" t="n">
-        <v>-1</v>
+        <v>9.883333333333333</v>
       </c>
       <c r="J3" t="n">
-        <v>-1</v>
+        <v>10.81666666666667</v>
       </c>
       <c r="K3" t="n">
-        <v>3.550000000000001</v>
+        <v>9.883333333333333</v>
       </c>
       <c r="L3" t="n">
-        <v>4.366666666666667</v>
+        <v>10.81666666666667</v>
       </c>
       <c r="M3" t="n">
         <v>0.3333333333333333</v>
@@ -581,37 +593,37 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>3.49201994126609</v>
+        <v>-2.7926750198023</v>
       </c>
       <c r="D4" t="n">
-        <v>-2.09987360600907</v>
+        <v>-7.07070496926335</v>
       </c>
       <c r="E4" t="n">
-        <v>14.89</v>
+        <v>235.0181</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04317</v>
+        <v>0.70348</v>
       </c>
       <c r="G4" t="n">
-        <v>9.883333333333333</v>
+        <v>6.550000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>10.81666666666667</v>
+        <v>7.35</v>
       </c>
       <c r="I4" t="n">
-        <v>9.883333333333333</v>
+        <v>-1</v>
       </c>
       <c r="J4" t="n">
-        <v>10.81666666666667</v>
+        <v>-1</v>
       </c>
       <c r="K4" t="n">
-        <v>9.883333333333333</v>
+        <v>6.550000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>10.81666666666667</v>
+        <v>7.35</v>
       </c>
       <c r="M4" t="n">
         <v>0.3333333333333333</v>
@@ -625,37 +637,37 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>-2.7926750198023</v>
+        <v>-5.53320102964836</v>
       </c>
       <c r="D5" t="n">
-        <v>-7.07070496926335</v>
+        <v>4.96886646380205</v>
       </c>
       <c r="E5" t="n">
-        <v>235.0181</v>
+        <v>1443.5621</v>
       </c>
       <c r="F5" t="n">
-        <v>0.70348</v>
+        <v>3.40848</v>
       </c>
       <c r="G5" t="n">
-        <v>6.550000000000001</v>
+        <v>11.48333333333333</v>
       </c>
       <c r="H5" t="n">
-        <v>7.35</v>
+        <v>12.61666666666667</v>
       </c>
       <c r="I5" t="n">
-        <v>-1</v>
+        <v>11.48333333333333</v>
       </c>
       <c r="J5" t="n">
-        <v>-1</v>
+        <v>12.61666666666667</v>
       </c>
       <c r="K5" t="n">
-        <v>6.550000000000001</v>
+        <v>11.48333333333333</v>
       </c>
       <c r="L5" t="n">
-        <v>7.35</v>
+        <v>12.61666666666667</v>
       </c>
       <c r="M5" t="n">
         <v>0.3333333333333333</v>
@@ -669,37 +681,37 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>-5.53320102964836</v>
+        <v>-7.58608040355909</v>
       </c>
       <c r="D6" t="n">
-        <v>4.96886646380205</v>
+        <v>-3.95143072486639</v>
       </c>
       <c r="E6" t="n">
-        <v>1443.5621</v>
+        <v>731.6005</v>
       </c>
       <c r="F6" t="n">
-        <v>3.40848</v>
+        <v>2.31239</v>
       </c>
       <c r="G6" t="n">
-        <v>11.48333333333333</v>
+        <v>11.46666666666667</v>
       </c>
       <c r="H6" t="n">
-        <v>12.61666666666667</v>
+        <v>12.43333333333333</v>
       </c>
       <c r="I6" t="n">
-        <v>11.48333333333333</v>
+        <v>11.46666666666667</v>
       </c>
       <c r="J6" t="n">
-        <v>12.61666666666667</v>
+        <v>12.43333333333333</v>
       </c>
       <c r="K6" t="n">
-        <v>11.48333333333333</v>
+        <v>11.46666666666667</v>
       </c>
       <c r="L6" t="n">
-        <v>12.61666666666667</v>
+        <v>12.43333333333333</v>
       </c>
       <c r="M6" t="n">
         <v>0.3333333333333333</v>
@@ -713,37 +725,37 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>-7.58608040355909</v>
+        <v>-4.66159864091412</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.95143072486639</v>
+        <v>-7.50935781984783</v>
       </c>
       <c r="E7" t="n">
-        <v>731.6005</v>
+        <v>2236.8216</v>
       </c>
       <c r="F7" t="n">
-        <v>2.31239</v>
+        <v>5.991599999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>11.46666666666667</v>
+        <v>3.766666666666667</v>
       </c>
       <c r="H7" t="n">
-        <v>12.43333333333333</v>
+        <v>4.983333333333333</v>
       </c>
       <c r="I7" t="n">
-        <v>11.46666666666667</v>
+        <v>-1</v>
       </c>
       <c r="J7" t="n">
-        <v>12.43333333333333</v>
+        <v>-1</v>
       </c>
       <c r="K7" t="n">
-        <v>11.46666666666667</v>
+        <v>3.766666666666667</v>
       </c>
       <c r="L7" t="n">
-        <v>12.43333333333333</v>
+        <v>4.983333333333333</v>
       </c>
       <c r="M7" t="n">
         <v>0.3333333333333333</v>
@@ -801,25 +813,25 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>-4.66159864091412</v>
+        <v>-8.50508883064982</v>
       </c>
       <c r="D9" t="n">
-        <v>-7.50935781984783</v>
+        <v>3.40488850459411</v>
       </c>
       <c r="E9" t="n">
-        <v>2236.8216</v>
+        <v>2487.744266666667</v>
       </c>
       <c r="F9" t="n">
-        <v>5.991599999999999</v>
+        <v>6.078013333333334</v>
       </c>
       <c r="G9" t="n">
-        <v>3.766666666666667</v>
+        <v>4.683333333333334</v>
       </c>
       <c r="H9" t="n">
-        <v>4.983333333333333</v>
+        <v>6.133333333333333</v>
       </c>
       <c r="I9" t="n">
         <v>-1</v>
@@ -828,10 +840,10 @@
         <v>-1</v>
       </c>
       <c r="K9" t="n">
-        <v>3.766666666666667</v>
+        <v>4.683333333333334</v>
       </c>
       <c r="L9" t="n">
-        <v>4.983333333333333</v>
+        <v>6.133333333333333</v>
       </c>
       <c r="M9" t="n">
         <v>0.3333333333333333</v>
@@ -933,25 +945,25 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C12" t="n">
-        <v>-8.50508883064982</v>
+        <v>2.31778195492727</v>
       </c>
       <c r="D12" t="n">
-        <v>3.40488850459411</v>
+        <v>3.18321046881879</v>
       </c>
       <c r="E12" t="n">
-        <v>2487.744266666667</v>
+        <v>2937.388405</v>
       </c>
       <c r="F12" t="n">
-        <v>6.078013333333334</v>
+        <v>9.006755</v>
       </c>
       <c r="G12" t="n">
-        <v>4.683333333333334</v>
+        <v>2.816666666666666</v>
       </c>
       <c r="H12" t="n">
-        <v>6.133333333333333</v>
+        <v>3.783333333333333</v>
       </c>
       <c r="I12" t="n">
         <v>-1</v>
@@ -960,10 +972,10 @@
         <v>-1</v>
       </c>
       <c r="K12" t="n">
-        <v>4.683333333333334</v>
+        <v>2.816666666666666</v>
       </c>
       <c r="L12" t="n">
-        <v>6.133333333333333</v>
+        <v>3.783333333333333</v>
       </c>
       <c r="M12" t="n">
         <v>0.3333333333333333</v>
@@ -1109,25 +1121,25 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>2.31778195492727</v>
+        <v>4.21284964345134</v>
       </c>
       <c r="D16" t="n">
-        <v>3.18321046881879</v>
+        <v>7.3870741887538</v>
       </c>
       <c r="E16" t="n">
-        <v>2937.388405</v>
+        <v>2506.7093</v>
       </c>
       <c r="F16" t="n">
-        <v>9.006755</v>
+        <v>6.65072</v>
       </c>
       <c r="G16" t="n">
-        <v>2.816666666666666</v>
+        <v>2.1</v>
       </c>
       <c r="H16" t="n">
-        <v>3.783333333333333</v>
+        <v>3.533333333333333</v>
       </c>
       <c r="I16" t="n">
         <v>-1</v>
@@ -1136,10 +1148,10 @@
         <v>-1</v>
       </c>
       <c r="K16" t="n">
-        <v>2.816666666666666</v>
+        <v>2.1</v>
       </c>
       <c r="L16" t="n">
-        <v>3.783333333333333</v>
+        <v>3.533333333333333</v>
       </c>
       <c r="M16" t="n">
         <v>0.3333333333333333</v>
@@ -1153,37 +1165,37 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>4.21284964345134</v>
+        <v>-5.87115512935265</v>
       </c>
       <c r="D17" t="n">
-        <v>7.3870741887538</v>
+        <v>-5.56732049906664</v>
       </c>
       <c r="E17" t="n">
-        <v>2506.7093</v>
+        <v>1879.9925</v>
       </c>
       <c r="F17" t="n">
-        <v>6.65072</v>
+        <v>7.278745</v>
       </c>
       <c r="G17" t="n">
-        <v>2.1</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="H17" t="n">
-        <v>3.533333333333333</v>
+        <v>12.48333333333333</v>
       </c>
       <c r="I17" t="n">
-        <v>-1</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="J17" t="n">
-        <v>-1</v>
+        <v>12.48333333333333</v>
       </c>
       <c r="K17" t="n">
-        <v>2.1</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="L17" t="n">
-        <v>3.533333333333333</v>
+        <v>12.48333333333333</v>
       </c>
       <c r="M17" t="n">
         <v>0.3333333333333333</v>
@@ -1241,37 +1253,37 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C19" t="n">
-        <v>-5.87115512935265</v>
+        <v>0.52184375622088</v>
       </c>
       <c r="D19" t="n">
-        <v>-5.56732049906664</v>
+        <v>-2.3827701607119</v>
       </c>
       <c r="E19" t="n">
-        <v>1879.9925</v>
+        <v>1325.5301</v>
       </c>
       <c r="F19" t="n">
-        <v>7.278745</v>
+        <v>4.36316</v>
       </c>
       <c r="G19" t="n">
-        <v>11.66666666666667</v>
+        <v>3.483333333333333</v>
       </c>
       <c r="H19" t="n">
-        <v>12.48333333333333</v>
+        <v>4.833333333333334</v>
       </c>
       <c r="I19" t="n">
-        <v>11.66666666666667</v>
+        <v>-1</v>
       </c>
       <c r="J19" t="n">
-        <v>12.48333333333333</v>
+        <v>-1</v>
       </c>
       <c r="K19" t="n">
-        <v>11.66666666666667</v>
+        <v>3.483333333333333</v>
       </c>
       <c r="L19" t="n">
-        <v>12.48333333333333</v>
+        <v>4.833333333333334</v>
       </c>
       <c r="M19" t="n">
         <v>0.3333333333333333</v>
@@ -1285,25 +1297,25 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C20" t="n">
-        <v>0.52184375622088</v>
+        <v>1.21755848144176</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3827701607119</v>
+        <v>-1.34839674138507</v>
       </c>
       <c r="E20" t="n">
-        <v>1325.5301</v>
+        <v>1726.8416</v>
       </c>
       <c r="F20" t="n">
-        <v>4.36316</v>
+        <v>4.399550000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>3.483333333333333</v>
+        <v>6.916666666666666</v>
       </c>
       <c r="H20" t="n">
-        <v>4.833333333333334</v>
+        <v>7.833333333333334</v>
       </c>
       <c r="I20" t="n">
         <v>-1</v>
@@ -1312,10 +1324,10 @@
         <v>-1</v>
       </c>
       <c r="K20" t="n">
-        <v>3.483333333333333</v>
+        <v>6.916666666666666</v>
       </c>
       <c r="L20" t="n">
-        <v>4.833333333333334</v>
+        <v>7.833333333333334</v>
       </c>
       <c r="M20" t="n">
         <v>0.3333333333333333</v>
@@ -1329,25 +1341,25 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C21" t="n">
-        <v>1.21755848144176</v>
+        <v>1.95141807684275</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.34839674138507</v>
+        <v>8.96083447171654</v>
       </c>
       <c r="E21" t="n">
-        <v>1726.8416</v>
+        <v>540.0867999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>4.399550000000001</v>
+        <v>1.27918</v>
       </c>
       <c r="G21" t="n">
-        <v>6.916666666666666</v>
+        <v>4.166666666666666</v>
       </c>
       <c r="H21" t="n">
-        <v>7.833333333333334</v>
+        <v>5.1</v>
       </c>
       <c r="I21" t="n">
         <v>-1</v>
@@ -1356,10 +1368,10 @@
         <v>-1</v>
       </c>
       <c r="K21" t="n">
-        <v>6.916666666666666</v>
+        <v>4.166666666666666</v>
       </c>
       <c r="L21" t="n">
-        <v>7.833333333333334</v>
+        <v>5.1</v>
       </c>
       <c r="M21" t="n">
         <v>0.3333333333333333</v>
@@ -1373,43 +1385,43 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C22" t="n">
-        <v>1.95141807684275</v>
+        <v>14.450550964877</v>
       </c>
       <c r="D22" t="n">
-        <v>8.96083447171654</v>
+        <v>-8.765440295958079</v>
       </c>
       <c r="E22" t="n">
-        <v>540.0867999999999</v>
+        <v>85.19999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>1.27918</v>
+        <v>0.1931</v>
       </c>
       <c r="G22" t="n">
-        <v>4.166666666666666</v>
+        <v>1.283333333333333</v>
       </c>
       <c r="H22" t="n">
-        <v>5.1</v>
+        <v>2.683333333333334</v>
       </c>
       <c r="I22" t="n">
-        <v>-1</v>
+        <v>1.283333333333333</v>
       </c>
       <c r="J22" t="n">
-        <v>-1</v>
+        <v>2.683333333333334</v>
       </c>
       <c r="K22" t="n">
-        <v>4.166666666666666</v>
+        <v>1.283333333333333</v>
       </c>
       <c r="L22" t="n">
-        <v>5.1</v>
+        <v>2.683333333333334</v>
       </c>
       <c r="M22" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="N22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1417,43 +1429,43 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.943660216384455</v>
+        <v>-24.9556659958338</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.4695515770045</v>
+        <v>-20.1758424030975</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>9.372199999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>0.07403</v>
       </c>
       <c r="G23" t="n">
-        <v>7.699999999999999</v>
+        <v>11.25</v>
       </c>
       <c r="H23" t="n">
-        <v>9.083333333333332</v>
+        <v>12.46666666666667</v>
       </c>
       <c r="I23" t="n">
-        <v>8</v>
+        <v>11.25</v>
       </c>
       <c r="J23" t="n">
-        <v>9.083333333333332</v>
+        <v>12.46666666666667</v>
       </c>
       <c r="K23" t="n">
-        <v>7.699999999999999</v>
+        <v>11.25</v>
       </c>
       <c r="L23" t="n">
-        <v>9.083333333333332</v>
+        <v>12.46666666666667</v>
       </c>
       <c r="M23" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="N23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1461,43 +1473,43 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C24" t="n">
-        <v>-1.70421069554743</v>
+        <v>-22.8798563925078</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.09774834490506</v>
+        <v>17.78788893064</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>1262.1673</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>2.95599</v>
       </c>
       <c r="G24" t="n">
-        <v>7</v>
+        <v>8.850000000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>8.399999999999999</v>
+        <v>10.26666666666667</v>
       </c>
       <c r="I24" t="n">
-        <v>8</v>
+        <v>8.850000000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>8.399999999999999</v>
+        <v>10.26666666666667</v>
       </c>
       <c r="K24" t="n">
-        <v>7</v>
+        <v>8.850000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>8.399999999999999</v>
+        <v>10.26666666666667</v>
       </c>
       <c r="M24" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="N24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1505,37 +1517,37 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C25" t="n">
-        <v>14.450550964877</v>
+        <v>7.61494129207758</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.765440295958079</v>
+        <v>8.631907896864689</v>
       </c>
       <c r="E25" t="n">
-        <v>85.19999999999999</v>
+        <v>2528.1351</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1931</v>
+        <v>5.33839</v>
       </c>
       <c r="G25" t="n">
-        <v>1.283333333333333</v>
+        <v>8.316666666666666</v>
       </c>
       <c r="H25" t="n">
-        <v>2.683333333333334</v>
+        <v>9.483333333333334</v>
       </c>
       <c r="I25" t="n">
-        <v>1.283333333333333</v>
+        <v>8.316666666666666</v>
       </c>
       <c r="J25" t="n">
-        <v>2.683333333333334</v>
+        <v>9.483333333333334</v>
       </c>
       <c r="K25" t="n">
-        <v>1.283333333333333</v>
+        <v>8.316666666666666</v>
       </c>
       <c r="L25" t="n">
-        <v>2.683333333333334</v>
+        <v>9.483333333333334</v>
       </c>
       <c r="M25" t="n">
         <v>0.3333333333333333</v>
@@ -1549,37 +1561,37 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="C26" t="n">
-        <v>33.3988623061578</v>
+        <v>-3.82996615152896</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.21820637223678</v>
+        <v>-27.8021080833649</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>45.81319999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>0.1362</v>
       </c>
       <c r="G26" t="n">
-        <v>4.866666666666667</v>
+        <v>7.833333333333334</v>
       </c>
       <c r="H26" t="n">
-        <v>6.266666666666667</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>4.866666666666667</v>
+        <v>7.833333333333334</v>
       </c>
       <c r="J26" t="n">
-        <v>6.266666666666667</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>4.866666666666667</v>
+        <v>7.833333333333334</v>
       </c>
       <c r="L26" t="n">
-        <v>6.266666666666667</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M26" t="n">
         <v>0.3333333333333333</v>
@@ -1593,37 +1605,37 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C27" t="n">
-        <v>-5.54863118490896</v>
+        <v>-0.948882982472617</v>
       </c>
       <c r="D27" t="n">
-        <v>12.227305144567</v>
+        <v>-27.1587227180418</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>1616.80205</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>3.819855</v>
       </c>
       <c r="G27" t="n">
-        <v>7.233333333333333</v>
+        <v>9.850000000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>8.199999999999999</v>
+        <v>11.11666666666667</v>
       </c>
       <c r="I27" t="n">
-        <v>7.233333333333333</v>
+        <v>9.850000000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>8.199999999999999</v>
+        <v>11.11666666666667</v>
       </c>
       <c r="K27" t="n">
-        <v>7.233333333333333</v>
+        <v>9.850000000000001</v>
       </c>
       <c r="L27" t="n">
-        <v>8.199999999999999</v>
+        <v>11.11666666666667</v>
       </c>
       <c r="M27" t="n">
         <v>0.3333333333333333</v>
@@ -1637,37 +1649,37 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>-24.9556659958338</v>
+        <v>-0.948882982472617</v>
       </c>
       <c r="D28" t="n">
-        <v>-20.1758424030975</v>
+        <v>-27.1587227180418</v>
       </c>
       <c r="E28" t="n">
-        <v>9.372199999999999</v>
+        <v>1616.80205</v>
       </c>
       <c r="F28" t="n">
-        <v>0.07403</v>
+        <v>3.819855</v>
       </c>
       <c r="G28" t="n">
-        <v>11.25</v>
+        <v>9.850000000000001</v>
       </c>
       <c r="H28" t="n">
-        <v>12.46666666666667</v>
+        <v>11.11666666666667</v>
       </c>
       <c r="I28" t="n">
-        <v>11.25</v>
+        <v>9.850000000000001</v>
       </c>
       <c r="J28" t="n">
-        <v>12.46666666666667</v>
+        <v>11.11666666666667</v>
       </c>
       <c r="K28" t="n">
-        <v>11.25</v>
+        <v>9.850000000000001</v>
       </c>
       <c r="L28" t="n">
-        <v>12.46666666666667</v>
+        <v>11.11666666666667</v>
       </c>
       <c r="M28" t="n">
         <v>0.3333333333333333</v>
@@ -1681,37 +1693,37 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>14.7106222334661</v>
+        <v>22.0320436347622</v>
       </c>
       <c r="D29" t="n">
-        <v>-12.5193153454242</v>
+        <v>-20.5978136037632</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>1628.65575</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>3.98015</v>
       </c>
       <c r="G29" t="n">
-        <v>2.616666666666667</v>
+        <v>11.45</v>
       </c>
       <c r="H29" t="n">
-        <v>4.016666666666667</v>
+        <v>12.58333333333333</v>
       </c>
       <c r="I29" t="n">
-        <v>2.616666666666667</v>
+        <v>11.45</v>
       </c>
       <c r="J29" t="n">
-        <v>4.016666666666667</v>
+        <v>12.58333333333333</v>
       </c>
       <c r="K29" t="n">
-        <v>2.616666666666667</v>
+        <v>11.45</v>
       </c>
       <c r="L29" t="n">
-        <v>4.016666666666667</v>
+        <v>12.58333333333333</v>
       </c>
       <c r="M29" t="n">
         <v>0.3333333333333333</v>
@@ -1725,37 +1737,37 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="C30" t="n">
-        <v>-11.7497074626045</v>
+        <v>22.0320436347622</v>
       </c>
       <c r="D30" t="n">
-        <v>35.0960881663225</v>
+        <v>-20.5978136037632</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>1628.65575</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>3.98015</v>
       </c>
       <c r="G30" t="n">
-        <v>1.583333333333334</v>
+        <v>11.45</v>
       </c>
       <c r="H30" t="n">
-        <v>2.383333333333333</v>
+        <v>12.58333333333333</v>
       </c>
       <c r="I30" t="n">
-        <v>1.583333333333334</v>
+        <v>11.45</v>
       </c>
       <c r="J30" t="n">
-        <v>2.383333333333333</v>
+        <v>12.58333333333333</v>
       </c>
       <c r="K30" t="n">
-        <v>1.583333333333334</v>
+        <v>11.45</v>
       </c>
       <c r="L30" t="n">
-        <v>2.383333333333333</v>
+        <v>12.58333333333333</v>
       </c>
       <c r="M30" t="n">
         <v>0.3333333333333333</v>
@@ -1769,37 +1781,37 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C31" t="n">
-        <v>-8.831732975604879</v>
+        <v>-14.3588031854593</v>
       </c>
       <c r="D31" t="n">
-        <v>-15.519725753721</v>
+        <v>29.6057903264111</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>873.9449999999999</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>2.04764</v>
       </c>
       <c r="G31" t="n">
-        <v>5.85</v>
+        <v>9.633333333333333</v>
       </c>
       <c r="H31" t="n">
-        <v>7.283333333333333</v>
+        <v>11.05</v>
       </c>
       <c r="I31" t="n">
-        <v>5.85</v>
+        <v>9.633333333333333</v>
       </c>
       <c r="J31" t="n">
-        <v>7.283333333333333</v>
+        <v>11.05</v>
       </c>
       <c r="K31" t="n">
-        <v>5.85</v>
+        <v>9.633333333333333</v>
       </c>
       <c r="L31" t="n">
-        <v>7.283333333333333</v>
+        <v>11.05</v>
       </c>
       <c r="M31" t="n">
         <v>0.3333333333333333</v>
@@ -1813,37 +1825,37 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C32" t="n">
-        <v>-13.8099790627706</v>
+        <v>16.0800764301466</v>
       </c>
       <c r="D32" t="n">
-        <v>-22.8050691954668</v>
+        <v>7.04621833529546</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>334.852</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>0.73178</v>
       </c>
       <c r="G32" t="n">
-        <v>4.166666666666666</v>
+        <v>3.533333333333333</v>
       </c>
       <c r="H32" t="n">
-        <v>5.25</v>
+        <v>5.033333333333333</v>
       </c>
       <c r="I32" t="n">
-        <v>4.166666666666666</v>
+        <v>3.533333333333333</v>
       </c>
       <c r="J32" t="n">
-        <v>5.25</v>
+        <v>5.033333333333333</v>
       </c>
       <c r="K32" t="n">
-        <v>4.166666666666666</v>
+        <v>3.533333333333333</v>
       </c>
       <c r="L32" t="n">
-        <v>5.25</v>
+        <v>5.033333333333333</v>
       </c>
       <c r="M32" t="n">
         <v>0.3333333333333333</v>
@@ -1857,37 +1869,37 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C33" t="n">
-        <v>-22.8798563925078</v>
+        <v>8.198403697413969</v>
       </c>
       <c r="D33" t="n">
-        <v>17.78788893064</v>
+        <v>-9.60107559004272</v>
       </c>
       <c r="E33" t="n">
-        <v>1262.1673</v>
+        <v>2257.206933333333</v>
       </c>
       <c r="F33" t="n">
-        <v>2.95599</v>
+        <v>5.148423333333334</v>
       </c>
       <c r="G33" t="n">
-        <v>8.850000000000001</v>
+        <v>8.816666666666666</v>
       </c>
       <c r="H33" t="n">
-        <v>10.26666666666667</v>
+        <v>9.766666666666666</v>
       </c>
       <c r="I33" t="n">
-        <v>8.850000000000001</v>
+        <v>8.816666666666666</v>
       </c>
       <c r="J33" t="n">
-        <v>10.26666666666667</v>
+        <v>9.766666666666666</v>
       </c>
       <c r="K33" t="n">
-        <v>8.850000000000001</v>
+        <v>8.816666666666666</v>
       </c>
       <c r="L33" t="n">
-        <v>10.26666666666667</v>
+        <v>9.766666666666666</v>
       </c>
       <c r="M33" t="n">
         <v>0.3333333333333333</v>
@@ -1901,37 +1913,37 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C34" t="n">
-        <v>7.61494129207758</v>
+        <v>8.198403697413969</v>
       </c>
       <c r="D34" t="n">
-        <v>8.631907896864689</v>
+        <v>-9.60107559004272</v>
       </c>
       <c r="E34" t="n">
-        <v>2528.1351</v>
+        <v>2257.206933333333</v>
       </c>
       <c r="F34" t="n">
-        <v>5.33839</v>
+        <v>5.148423333333334</v>
       </c>
       <c r="G34" t="n">
-        <v>8.316666666666666</v>
+        <v>8.816666666666666</v>
       </c>
       <c r="H34" t="n">
-        <v>9.483333333333334</v>
+        <v>9.766666666666666</v>
       </c>
       <c r="I34" t="n">
-        <v>8.316666666666666</v>
+        <v>8.816666666666666</v>
       </c>
       <c r="J34" t="n">
-        <v>9.483333333333334</v>
+        <v>9.766666666666666</v>
       </c>
       <c r="K34" t="n">
-        <v>8.316666666666666</v>
+        <v>8.816666666666666</v>
       </c>
       <c r="L34" t="n">
-        <v>9.483333333333334</v>
+        <v>9.766666666666666</v>
       </c>
       <c r="M34" t="n">
         <v>0.3333333333333333</v>
@@ -1945,37 +1957,37 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C35" t="n">
-        <v>-3.82996615152896</v>
+        <v>8.198403697413969</v>
       </c>
       <c r="D35" t="n">
-        <v>-27.8021080833649</v>
+        <v>-9.60107559004272</v>
       </c>
       <c r="E35" t="n">
-        <v>45.81319999999999</v>
+        <v>2257.206933333333</v>
       </c>
       <c r="F35" t="n">
-        <v>0.1362</v>
+        <v>5.148423333333334</v>
       </c>
       <c r="G35" t="n">
-        <v>7.833333333333334</v>
+        <v>8.816666666666666</v>
       </c>
       <c r="H35" t="n">
-        <v>9.199999999999999</v>
+        <v>9.766666666666666</v>
       </c>
       <c r="I35" t="n">
-        <v>7.833333333333334</v>
+        <v>8.816666666666666</v>
       </c>
       <c r="J35" t="n">
-        <v>9.199999999999999</v>
+        <v>9.766666666666666</v>
       </c>
       <c r="K35" t="n">
-        <v>7.833333333333334</v>
+        <v>8.816666666666666</v>
       </c>
       <c r="L35" t="n">
-        <v>9.199999999999999</v>
+        <v>9.766666666666666</v>
       </c>
       <c r="M35" t="n">
         <v>0.3333333333333333</v>
@@ -1989,37 +2001,37 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.948882982472617</v>
+        <v>0.323325874270734</v>
       </c>
       <c r="D36" t="n">
-        <v>-27.1587227180418</v>
+        <v>-37.5736956858047</v>
       </c>
       <c r="E36" t="n">
-        <v>1616.80205</v>
+        <v>442.3342</v>
       </c>
       <c r="F36" t="n">
-        <v>3.819855</v>
+        <v>1.12524</v>
       </c>
       <c r="G36" t="n">
-        <v>9.850000000000001</v>
+        <v>5.133333333333333</v>
       </c>
       <c r="H36" t="n">
-        <v>11.11666666666667</v>
+        <v>6.4</v>
       </c>
       <c r="I36" t="n">
-        <v>9.850000000000001</v>
+        <v>5.133333333333333</v>
       </c>
       <c r="J36" t="n">
-        <v>11.11666666666667</v>
+        <v>6.4</v>
       </c>
       <c r="K36" t="n">
-        <v>9.850000000000001</v>
+        <v>5.133333333333333</v>
       </c>
       <c r="L36" t="n">
-        <v>11.11666666666667</v>
+        <v>6.4</v>
       </c>
       <c r="M36" t="n">
         <v>0.3333333333333333</v>
@@ -2033,37 +2045,37 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.948882982472617</v>
+        <v>-8.662441945648929</v>
       </c>
       <c r="D37" t="n">
-        <v>-27.1587227180418</v>
+        <v>-13.7461263895102</v>
       </c>
       <c r="E37" t="n">
-        <v>1616.80205</v>
+        <v>527.2666</v>
       </c>
       <c r="F37" t="n">
-        <v>3.819855</v>
+        <v>1.37982</v>
       </c>
       <c r="G37" t="n">
-        <v>9.850000000000001</v>
+        <v>2.766666666666667</v>
       </c>
       <c r="H37" t="n">
-        <v>11.11666666666667</v>
+        <v>4.183333333333334</v>
       </c>
       <c r="I37" t="n">
-        <v>9.850000000000001</v>
+        <v>2.766666666666667</v>
       </c>
       <c r="J37" t="n">
-        <v>11.11666666666667</v>
+        <v>4.183333333333334</v>
       </c>
       <c r="K37" t="n">
-        <v>9.850000000000001</v>
+        <v>2.766666666666667</v>
       </c>
       <c r="L37" t="n">
-        <v>11.11666666666667</v>
+        <v>4.183333333333334</v>
       </c>
       <c r="M37" t="n">
         <v>0.3333333333333333</v>
@@ -2077,37 +2089,37 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C38" t="n">
-        <v>22.0320436347622</v>
+        <v>13.090888292642</v>
       </c>
       <c r="D38" t="n">
-        <v>-20.5978136037632</v>
+        <v>-10.9595442953867</v>
       </c>
       <c r="E38" t="n">
-        <v>1628.65575</v>
+        <v>364.0498</v>
       </c>
       <c r="F38" t="n">
-        <v>3.98015</v>
+        <v>1.5211</v>
       </c>
       <c r="G38" t="n">
-        <v>11.45</v>
+        <v>10.91666666666667</v>
       </c>
       <c r="H38" t="n">
-        <v>12.58333333333333</v>
+        <v>12.13333333333333</v>
       </c>
       <c r="I38" t="n">
-        <v>11.45</v>
+        <v>10.91666666666667</v>
       </c>
       <c r="J38" t="n">
-        <v>12.58333333333333</v>
+        <v>12.13333333333333</v>
       </c>
       <c r="K38" t="n">
-        <v>11.45</v>
+        <v>10.91666666666667</v>
       </c>
       <c r="L38" t="n">
-        <v>12.58333333333333</v>
+        <v>12.13333333333333</v>
       </c>
       <c r="M38" t="n">
         <v>0.3333333333333333</v>
@@ -2121,37 +2133,37 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C39" t="n">
-        <v>22.0320436347622</v>
+        <v>-0.079057338447202</v>
       </c>
       <c r="D39" t="n">
-        <v>-20.5978136037632</v>
+        <v>-32.911273246347</v>
       </c>
       <c r="E39" t="n">
-        <v>1628.65575</v>
+        <v>1692.5786</v>
       </c>
       <c r="F39" t="n">
-        <v>3.98015</v>
+        <v>3.88436</v>
       </c>
       <c r="G39" t="n">
-        <v>11.45</v>
+        <v>1.483333333333333</v>
       </c>
       <c r="H39" t="n">
-        <v>12.58333333333333</v>
+        <v>2.866666666666667</v>
       </c>
       <c r="I39" t="n">
-        <v>11.45</v>
+        <v>1.483333333333333</v>
       </c>
       <c r="J39" t="n">
-        <v>12.58333333333333</v>
+        <v>2.866666666666667</v>
       </c>
       <c r="K39" t="n">
-        <v>11.45</v>
+        <v>1.483333333333333</v>
       </c>
       <c r="L39" t="n">
-        <v>12.58333333333333</v>
+        <v>2.866666666666667</v>
       </c>
       <c r="M39" t="n">
         <v>0.3333333333333333</v>
@@ -2165,37 +2177,37 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C40" t="n">
-        <v>-14.3588031854593</v>
+        <v>-27.7413684328977</v>
       </c>
       <c r="D40" t="n">
-        <v>29.6057903264111</v>
+        <v>15.6205382398009</v>
       </c>
       <c r="E40" t="n">
-        <v>873.9449999999999</v>
+        <v>1654.62735</v>
       </c>
       <c r="F40" t="n">
-        <v>2.04764</v>
+        <v>5.15388</v>
       </c>
       <c r="G40" t="n">
-        <v>9.633333333333333</v>
+        <v>7.266666666666667</v>
       </c>
       <c r="H40" t="n">
-        <v>11.05</v>
+        <v>8.350000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>9.633333333333333</v>
+        <v>7.266666666666667</v>
       </c>
       <c r="J40" t="n">
-        <v>11.05</v>
+        <v>8.350000000000001</v>
       </c>
       <c r="K40" t="n">
-        <v>9.633333333333333</v>
+        <v>7.266666666666667</v>
       </c>
       <c r="L40" t="n">
-        <v>11.05</v>
+        <v>8.350000000000001</v>
       </c>
       <c r="M40" t="n">
         <v>0.3333333333333333</v>
@@ -2209,37 +2221,37 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C41" t="n">
-        <v>16.0800764301466</v>
+        <v>-27.7413684328977</v>
       </c>
       <c r="D41" t="n">
-        <v>7.04621833529546</v>
+        <v>15.6205382398009</v>
       </c>
       <c r="E41" t="n">
-        <v>334.852</v>
+        <v>1654.62735</v>
       </c>
       <c r="F41" t="n">
-        <v>0.73178</v>
+        <v>5.15388</v>
       </c>
       <c r="G41" t="n">
-        <v>3.533333333333333</v>
+        <v>7.266666666666667</v>
       </c>
       <c r="H41" t="n">
-        <v>5.033333333333333</v>
+        <v>8.350000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>3.533333333333333</v>
+        <v>7.266666666666667</v>
       </c>
       <c r="J41" t="n">
-        <v>5.033333333333333</v>
+        <v>8.350000000000001</v>
       </c>
       <c r="K41" t="n">
-        <v>3.533333333333333</v>
+        <v>7.266666666666667</v>
       </c>
       <c r="L41" t="n">
-        <v>5.033333333333333</v>
+        <v>8.350000000000001</v>
       </c>
       <c r="M41" t="n">
         <v>0.3333333333333333</v>
@@ -2253,37 +2265,37 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C42" t="n">
-        <v>8.198403697413969</v>
+        <v>35.9798551608321</v>
       </c>
       <c r="D42" t="n">
-        <v>-9.60107559004272</v>
+        <v>-8.834846436336671</v>
       </c>
       <c r="E42" t="n">
-        <v>2257.206933333333</v>
+        <v>564.949</v>
       </c>
       <c r="F42" t="n">
-        <v>5.148423333333334</v>
+        <v>1.8194</v>
       </c>
       <c r="G42" t="n">
-        <v>8.816666666666666</v>
+        <v>1.416666666666666</v>
       </c>
       <c r="H42" t="n">
-        <v>9.766666666666666</v>
+        <v>2.716666666666667</v>
       </c>
       <c r="I42" t="n">
-        <v>8.816666666666666</v>
+        <v>1.416666666666666</v>
       </c>
       <c r="J42" t="n">
-        <v>9.766666666666666</v>
+        <v>2.716666666666667</v>
       </c>
       <c r="K42" t="n">
-        <v>8.816666666666666</v>
+        <v>1.416666666666666</v>
       </c>
       <c r="L42" t="n">
-        <v>9.766666666666666</v>
+        <v>2.716666666666667</v>
       </c>
       <c r="M42" t="n">
         <v>0.3333333333333333</v>
@@ -2297,37 +2309,37 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C43" t="n">
-        <v>8.198403697413969</v>
+        <v>-19.8657669761891</v>
       </c>
       <c r="D43" t="n">
-        <v>-9.60107559004272</v>
+        <v>8.245091757030799</v>
       </c>
       <c r="E43" t="n">
-        <v>2257.206933333333</v>
+        <v>1261.7326</v>
       </c>
       <c r="F43" t="n">
-        <v>5.148423333333334</v>
+        <v>4.06727</v>
       </c>
       <c r="G43" t="n">
-        <v>8.816666666666666</v>
+        <v>2.466666666666667</v>
       </c>
       <c r="H43" t="n">
-        <v>9.766666666666666</v>
+        <v>3.566666666666666</v>
       </c>
       <c r="I43" t="n">
-        <v>8.816666666666666</v>
+        <v>2.466666666666667</v>
       </c>
       <c r="J43" t="n">
-        <v>9.766666666666666</v>
+        <v>3.566666666666666</v>
       </c>
       <c r="K43" t="n">
-        <v>8.816666666666666</v>
+        <v>2.466666666666667</v>
       </c>
       <c r="L43" t="n">
-        <v>9.766666666666666</v>
+        <v>3.566666666666666</v>
       </c>
       <c r="M43" t="n">
         <v>0.3333333333333333</v>
@@ -2341,37 +2353,37 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C44" t="n">
-        <v>8.198403697413969</v>
+        <v>-14.7593829065892</v>
       </c>
       <c r="D44" t="n">
-        <v>-9.60107559004272</v>
+        <v>-31.3415469493066</v>
       </c>
       <c r="E44" t="n">
-        <v>2257.206933333333</v>
+        <v>2012.4458</v>
       </c>
       <c r="F44" t="n">
-        <v>5.148423333333334</v>
+        <v>5.003585</v>
       </c>
       <c r="G44" t="n">
-        <v>8.816666666666666</v>
+        <v>6.133333333333333</v>
       </c>
       <c r="H44" t="n">
-        <v>9.766666666666666</v>
+        <v>7</v>
       </c>
       <c r="I44" t="n">
-        <v>8.816666666666666</v>
+        <v>6.133333333333333</v>
       </c>
       <c r="J44" t="n">
-        <v>9.766666666666666</v>
+        <v>7</v>
       </c>
       <c r="K44" t="n">
-        <v>8.816666666666666</v>
+        <v>6.133333333333333</v>
       </c>
       <c r="L44" t="n">
-        <v>9.766666666666666</v>
+        <v>7</v>
       </c>
       <c r="M44" t="n">
         <v>0.3333333333333333</v>
@@ -2385,37 +2397,37 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C45" t="n">
-        <v>0.323325874270734</v>
+        <v>-14.7593829065892</v>
       </c>
       <c r="D45" t="n">
-        <v>-37.5736956858047</v>
+        <v>-31.3415469493066</v>
       </c>
       <c r="E45" t="n">
-        <v>442.3342</v>
+        <v>2012.4458</v>
       </c>
       <c r="F45" t="n">
-        <v>1.12524</v>
+        <v>5.003585</v>
       </c>
       <c r="G45" t="n">
-        <v>5.133333333333333</v>
+        <v>6.133333333333333</v>
       </c>
       <c r="H45" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="I45" t="n">
-        <v>5.133333333333333</v>
+        <v>6.133333333333333</v>
       </c>
       <c r="J45" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="K45" t="n">
-        <v>5.133333333333333</v>
+        <v>6.133333333333333</v>
       </c>
       <c r="L45" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="M45" t="n">
         <v>0.3333333333333333</v>
@@ -2429,37 +2441,37 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C46" t="n">
-        <v>-8.662441945648929</v>
+        <v>-25.4478796473256</v>
       </c>
       <c r="D46" t="n">
-        <v>-13.7461263895102</v>
+        <v>8.265874726389081</v>
       </c>
       <c r="E46" t="n">
-        <v>527.2666</v>
+        <v>2691.1358</v>
       </c>
       <c r="F46" t="n">
-        <v>1.37982</v>
+        <v>7.9507</v>
       </c>
       <c r="G46" t="n">
-        <v>2.766666666666667</v>
+        <v>9.866666666666667</v>
       </c>
       <c r="H46" t="n">
-        <v>4.183333333333334</v>
+        <v>11.06666666666667</v>
       </c>
       <c r="I46" t="n">
-        <v>2.766666666666667</v>
+        <v>9.866666666666667</v>
       </c>
       <c r="J46" t="n">
-        <v>4.183333333333334</v>
+        <v>11.06666666666667</v>
       </c>
       <c r="K46" t="n">
-        <v>2.766666666666667</v>
+        <v>9.866666666666667</v>
       </c>
       <c r="L46" t="n">
-        <v>4.183333333333334</v>
+        <v>11.06666666666667</v>
       </c>
       <c r="M46" t="n">
         <v>0.3333333333333333</v>
@@ -2473,37 +2485,37 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C47" t="n">
-        <v>13.090888292642</v>
+        <v>-6.39184845369064</v>
       </c>
       <c r="D47" t="n">
-        <v>-10.9595442953867</v>
+        <v>38.866308384005</v>
       </c>
       <c r="E47" t="n">
-        <v>364.0498</v>
+        <v>2786.4185</v>
       </c>
       <c r="F47" t="n">
-        <v>1.5211</v>
+        <v>7.85191</v>
       </c>
       <c r="G47" t="n">
-        <v>10.91666666666667</v>
+        <v>4.633333333333333</v>
       </c>
       <c r="H47" t="n">
-        <v>12.13333333333333</v>
+        <v>5.85</v>
       </c>
       <c r="I47" t="n">
-        <v>10.91666666666667</v>
+        <v>4.633333333333333</v>
       </c>
       <c r="J47" t="n">
-        <v>12.13333333333333</v>
+        <v>5.85</v>
       </c>
       <c r="K47" t="n">
-        <v>10.91666666666667</v>
+        <v>4.633333333333333</v>
       </c>
       <c r="L47" t="n">
-        <v>12.13333333333333</v>
+        <v>5.85</v>
       </c>
       <c r="M47" t="n">
         <v>0.3333333333333333</v>
@@ -2517,37 +2529,37 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.079057338447202</v>
+        <v>-7.97960536037818</v>
       </c>
       <c r="D48" t="n">
-        <v>-32.911273246347</v>
+        <v>-18.8049073592717</v>
       </c>
       <c r="E48" t="n">
-        <v>1692.5786</v>
+        <v>2113.933766666667</v>
       </c>
       <c r="F48" t="n">
-        <v>3.88436</v>
+        <v>5.008973333333333</v>
       </c>
       <c r="G48" t="n">
-        <v>1.483333333333333</v>
+        <v>2.233333333333333</v>
       </c>
       <c r="H48" t="n">
-        <v>2.866666666666667</v>
+        <v>3.35</v>
       </c>
       <c r="I48" t="n">
-        <v>1.483333333333333</v>
+        <v>2.233333333333333</v>
       </c>
       <c r="J48" t="n">
-        <v>2.866666666666667</v>
+        <v>3.35</v>
       </c>
       <c r="K48" t="n">
-        <v>1.483333333333333</v>
+        <v>2.233333333333333</v>
       </c>
       <c r="L48" t="n">
-        <v>2.866666666666667</v>
+        <v>3.35</v>
       </c>
       <c r="M48" t="n">
         <v>0.3333333333333333</v>
@@ -2561,37 +2573,37 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C49" t="n">
-        <v>-27.7413684328977</v>
+        <v>-7.97960536037818</v>
       </c>
       <c r="D49" t="n">
-        <v>15.6205382398009</v>
+        <v>-18.8049073592717</v>
       </c>
       <c r="E49" t="n">
-        <v>1654.62735</v>
+        <v>2113.933766666667</v>
       </c>
       <c r="F49" t="n">
-        <v>5.15388</v>
+        <v>5.008973333333333</v>
       </c>
       <c r="G49" t="n">
-        <v>7.266666666666667</v>
+        <v>2.233333333333333</v>
       </c>
       <c r="H49" t="n">
-        <v>8.350000000000001</v>
+        <v>3.35</v>
       </c>
       <c r="I49" t="n">
-        <v>7.266666666666667</v>
+        <v>2.233333333333333</v>
       </c>
       <c r="J49" t="n">
-        <v>8.350000000000001</v>
+        <v>3.35</v>
       </c>
       <c r="K49" t="n">
-        <v>7.266666666666667</v>
+        <v>2.233333333333333</v>
       </c>
       <c r="L49" t="n">
-        <v>8.350000000000001</v>
+        <v>3.35</v>
       </c>
       <c r="M49" t="n">
         <v>0.3333333333333333</v>
@@ -2605,37 +2617,37 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C50" t="n">
-        <v>-27.7413684328977</v>
+        <v>-7.97960536037818</v>
       </c>
       <c r="D50" t="n">
-        <v>15.6205382398009</v>
+        <v>-18.8049073592717</v>
       </c>
       <c r="E50" t="n">
-        <v>1654.62735</v>
+        <v>2113.933766666667</v>
       </c>
       <c r="F50" t="n">
-        <v>5.15388</v>
+        <v>5.008973333333333</v>
       </c>
       <c r="G50" t="n">
-        <v>7.266666666666667</v>
+        <v>2.233333333333333</v>
       </c>
       <c r="H50" t="n">
-        <v>8.350000000000001</v>
+        <v>3.35</v>
       </c>
       <c r="I50" t="n">
-        <v>7.266666666666667</v>
+        <v>2.233333333333333</v>
       </c>
       <c r="J50" t="n">
-        <v>8.350000000000001</v>
+        <v>3.35</v>
       </c>
       <c r="K50" t="n">
-        <v>7.266666666666667</v>
+        <v>2.233333333333333</v>
       </c>
       <c r="L50" t="n">
-        <v>8.350000000000001</v>
+        <v>3.35</v>
       </c>
       <c r="M50" t="n">
         <v>0.3333333333333333</v>
@@ -2649,37 +2661,37 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C51" t="n">
-        <v>35.9798551608321</v>
+        <v>18.151206181933</v>
       </c>
       <c r="D51" t="n">
-        <v>-8.834846436336671</v>
+        <v>-13.637299694184</v>
       </c>
       <c r="E51" t="n">
-        <v>564.949</v>
+        <v>2530.79035</v>
       </c>
       <c r="F51" t="n">
-        <v>1.8194</v>
+        <v>6.80844</v>
       </c>
       <c r="G51" t="n">
-        <v>1.416666666666666</v>
+        <v>8.883333333333333</v>
       </c>
       <c r="H51" t="n">
-        <v>2.716666666666667</v>
+        <v>10.28333333333333</v>
       </c>
       <c r="I51" t="n">
-        <v>1.416666666666666</v>
+        <v>8.883333333333333</v>
       </c>
       <c r="J51" t="n">
-        <v>2.716666666666667</v>
+        <v>10.28333333333333</v>
       </c>
       <c r="K51" t="n">
-        <v>1.416666666666666</v>
+        <v>8.883333333333333</v>
       </c>
       <c r="L51" t="n">
-        <v>2.716666666666667</v>
+        <v>10.28333333333333</v>
       </c>
       <c r="M51" t="n">
         <v>0.3333333333333333</v>
@@ -2693,37 +2705,37 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C52" t="n">
-        <v>-19.8657669761891</v>
+        <v>18.151206181933</v>
       </c>
       <c r="D52" t="n">
-        <v>8.245091757030799</v>
+        <v>-13.637299694184</v>
       </c>
       <c r="E52" t="n">
-        <v>1261.7326</v>
+        <v>2530.79035</v>
       </c>
       <c r="F52" t="n">
-        <v>4.06727</v>
+        <v>6.80844</v>
       </c>
       <c r="G52" t="n">
-        <v>2.466666666666667</v>
+        <v>8.883333333333333</v>
       </c>
       <c r="H52" t="n">
-        <v>3.566666666666666</v>
+        <v>10.28333333333333</v>
       </c>
       <c r="I52" t="n">
-        <v>2.466666666666667</v>
+        <v>8.883333333333333</v>
       </c>
       <c r="J52" t="n">
-        <v>3.566666666666666</v>
+        <v>10.28333333333333</v>
       </c>
       <c r="K52" t="n">
-        <v>2.466666666666667</v>
+        <v>8.883333333333333</v>
       </c>
       <c r="L52" t="n">
-        <v>3.566666666666666</v>
+        <v>10.28333333333333</v>
       </c>
       <c r="M52" t="n">
         <v>0.3333333333333333</v>
@@ -2737,37 +2749,37 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C53" t="n">
-        <v>-14.7593829065892</v>
+        <v>21.590843242742</v>
       </c>
       <c r="D53" t="n">
-        <v>-31.3415469493066</v>
+        <v>-11.0654463649764</v>
       </c>
       <c r="E53" t="n">
-        <v>2012.4458</v>
+        <v>2276.15445</v>
       </c>
       <c r="F53" t="n">
-        <v>5.003585</v>
+        <v>5.812015</v>
       </c>
       <c r="G53" t="n">
-        <v>6.133333333333333</v>
+        <v>9.016666666666666</v>
       </c>
       <c r="H53" t="n">
-        <v>7</v>
+        <v>10.48333333333333</v>
       </c>
       <c r="I53" t="n">
-        <v>6.133333333333333</v>
+        <v>9.016666666666666</v>
       </c>
       <c r="J53" t="n">
-        <v>7</v>
+        <v>10.48333333333333</v>
       </c>
       <c r="K53" t="n">
-        <v>6.133333333333333</v>
+        <v>9.016666666666666</v>
       </c>
       <c r="L53" t="n">
-        <v>7</v>
+        <v>10.48333333333333</v>
       </c>
       <c r="M53" t="n">
         <v>0.3333333333333333</v>
@@ -2781,37 +2793,37 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C54" t="n">
-        <v>-14.7593829065892</v>
+        <v>21.590843242742</v>
       </c>
       <c r="D54" t="n">
-        <v>-31.3415469493066</v>
+        <v>-11.0654463649764</v>
       </c>
       <c r="E54" t="n">
-        <v>2012.4458</v>
+        <v>2276.15445</v>
       </c>
       <c r="F54" t="n">
-        <v>5.003585</v>
+        <v>5.812015</v>
       </c>
       <c r="G54" t="n">
-        <v>6.133333333333333</v>
+        <v>9.016666666666666</v>
       </c>
       <c r="H54" t="n">
-        <v>7</v>
+        <v>10.48333333333333</v>
       </c>
       <c r="I54" t="n">
-        <v>6.133333333333333</v>
+        <v>9.016666666666666</v>
       </c>
       <c r="J54" t="n">
-        <v>7</v>
+        <v>10.48333333333333</v>
       </c>
       <c r="K54" t="n">
-        <v>6.133333333333333</v>
+        <v>9.016666666666666</v>
       </c>
       <c r="L54" t="n">
-        <v>7</v>
+        <v>10.48333333333333</v>
       </c>
       <c r="M54" t="n">
         <v>0.3333333333333333</v>
@@ -2825,37 +2837,37 @@
         <v>53</v>
       </c>
       <c r="B55" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C55" t="n">
-        <v>-25.4478796473256</v>
+        <v>19.4247893328668</v>
       </c>
       <c r="D55" t="n">
-        <v>8.265874726389081</v>
+        <v>-17.0996049039402</v>
       </c>
       <c r="E55" t="n">
-        <v>2691.1358</v>
+        <v>2899.9628</v>
       </c>
       <c r="F55" t="n">
-        <v>7.9507</v>
+        <v>9.206685</v>
       </c>
       <c r="G55" t="n">
-        <v>9.866666666666667</v>
+        <v>7.616666666666667</v>
       </c>
       <c r="H55" t="n">
-        <v>11.06666666666667</v>
+        <v>8.600000000000001</v>
       </c>
       <c r="I55" t="n">
-        <v>9.866666666666667</v>
+        <v>7.616666666666667</v>
       </c>
       <c r="J55" t="n">
-        <v>11.06666666666667</v>
+        <v>8.600000000000001</v>
       </c>
       <c r="K55" t="n">
-        <v>9.866666666666667</v>
+        <v>7.616666666666667</v>
       </c>
       <c r="L55" t="n">
-        <v>11.06666666666667</v>
+        <v>8.600000000000001</v>
       </c>
       <c r="M55" t="n">
         <v>0.3333333333333333</v>
@@ -2869,37 +2881,37 @@
         <v>54</v>
       </c>
       <c r="B56" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C56" t="n">
-        <v>-6.39184845369064</v>
+        <v>19.4247893328668</v>
       </c>
       <c r="D56" t="n">
-        <v>38.866308384005</v>
+        <v>-17.0996049039402</v>
       </c>
       <c r="E56" t="n">
-        <v>2786.4185</v>
+        <v>2899.9628</v>
       </c>
       <c r="F56" t="n">
-        <v>7.85191</v>
+        <v>9.206685</v>
       </c>
       <c r="G56" t="n">
-        <v>4.633333333333333</v>
+        <v>7.616666666666667</v>
       </c>
       <c r="H56" t="n">
-        <v>5.85</v>
+        <v>8.600000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>4.633333333333333</v>
+        <v>7.616666666666667</v>
       </c>
       <c r="J56" t="n">
-        <v>5.85</v>
+        <v>8.600000000000001</v>
       </c>
       <c r="K56" t="n">
-        <v>4.633333333333333</v>
+        <v>7.616666666666667</v>
       </c>
       <c r="L56" t="n">
-        <v>5.85</v>
+        <v>8.600000000000001</v>
       </c>
       <c r="M56" t="n">
         <v>0.3333333333333333</v>
@@ -2913,37 +2925,37 @@
         <v>55</v>
       </c>
       <c r="B57" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C57" t="n">
-        <v>-7.97960536037818</v>
+        <v>-3.94895297178467</v>
       </c>
       <c r="D57" t="n">
-        <v>-18.8049073592717</v>
+        <v>-34.8007269144264</v>
       </c>
       <c r="E57" t="n">
-        <v>2113.933766666667</v>
+        <v>1659.91985</v>
       </c>
       <c r="F57" t="n">
-        <v>5.008973333333333</v>
+        <v>5.44331</v>
       </c>
       <c r="G57" t="n">
-        <v>2.233333333333333</v>
+        <v>3.199999999999999</v>
       </c>
       <c r="H57" t="n">
-        <v>3.35</v>
+        <v>4.183333333333334</v>
       </c>
       <c r="I57" t="n">
-        <v>2.233333333333333</v>
+        <v>3.199999999999999</v>
       </c>
       <c r="J57" t="n">
-        <v>3.35</v>
+        <v>4.183333333333334</v>
       </c>
       <c r="K57" t="n">
-        <v>2.233333333333333</v>
+        <v>3.199999999999999</v>
       </c>
       <c r="L57" t="n">
-        <v>3.35</v>
+        <v>4.183333333333334</v>
       </c>
       <c r="M57" t="n">
         <v>0.3333333333333333</v>
@@ -2957,37 +2969,37 @@
         <v>56</v>
       </c>
       <c r="B58" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C58" t="n">
-        <v>-7.97960536037818</v>
+        <v>-3.94895297178467</v>
       </c>
       <c r="D58" t="n">
-        <v>-18.8049073592717</v>
+        <v>-34.8007269144264</v>
       </c>
       <c r="E58" t="n">
-        <v>2113.933766666667</v>
+        <v>1659.91985</v>
       </c>
       <c r="F58" t="n">
-        <v>5.008973333333333</v>
+        <v>5.44331</v>
       </c>
       <c r="G58" t="n">
-        <v>2.233333333333333</v>
+        <v>3.199999999999999</v>
       </c>
       <c r="H58" t="n">
-        <v>3.35</v>
+        <v>4.183333333333334</v>
       </c>
       <c r="I58" t="n">
-        <v>2.233333333333333</v>
+        <v>3.199999999999999</v>
       </c>
       <c r="J58" t="n">
-        <v>3.35</v>
+        <v>4.183333333333334</v>
       </c>
       <c r="K58" t="n">
-        <v>2.233333333333333</v>
+        <v>3.199999999999999</v>
       </c>
       <c r="L58" t="n">
-        <v>3.35</v>
+        <v>4.183333333333334</v>
       </c>
       <c r="M58" t="n">
         <v>0.3333333333333333</v>
@@ -3001,37 +3013,37 @@
         <v>57</v>
       </c>
       <c r="B59" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C59" t="n">
-        <v>-7.97960536037818</v>
+        <v>10.5334022336896</v>
       </c>
       <c r="D59" t="n">
-        <v>-18.8049073592717</v>
+        <v>17.621635259999</v>
       </c>
       <c r="E59" t="n">
-        <v>2113.933766666667</v>
+        <v>2784.5018</v>
       </c>
       <c r="F59" t="n">
-        <v>5.008973333333333</v>
+        <v>8.09606</v>
       </c>
       <c r="G59" t="n">
-        <v>2.233333333333333</v>
+        <v>10.91666666666667</v>
       </c>
       <c r="H59" t="n">
-        <v>3.35</v>
+        <v>11.91666666666667</v>
       </c>
       <c r="I59" t="n">
-        <v>2.233333333333333</v>
+        <v>10.91666666666667</v>
       </c>
       <c r="J59" t="n">
-        <v>3.35</v>
+        <v>11.91666666666667</v>
       </c>
       <c r="K59" t="n">
-        <v>2.233333333333333</v>
+        <v>10.91666666666667</v>
       </c>
       <c r="L59" t="n">
-        <v>3.35</v>
+        <v>11.91666666666667</v>
       </c>
       <c r="M59" t="n">
         <v>0.3333333333333333</v>
@@ -3045,37 +3057,37 @@
         <v>58</v>
       </c>
       <c r="B60" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C60" t="n">
-        <v>18.151206181933</v>
+        <v>5.11105840595424</v>
       </c>
       <c r="D60" t="n">
-        <v>-13.637299694184</v>
+        <v>10.9732978458469</v>
       </c>
       <c r="E60" t="n">
-        <v>2530.79035</v>
+        <v>2866.242533333334</v>
       </c>
       <c r="F60" t="n">
-        <v>6.80844</v>
+        <v>6.516393333333333</v>
       </c>
       <c r="G60" t="n">
-        <v>8.883333333333333</v>
+        <v>8.100000000000001</v>
       </c>
       <c r="H60" t="n">
-        <v>10.28333333333333</v>
+        <v>9.466666666666665</v>
       </c>
       <c r="I60" t="n">
-        <v>8.883333333333333</v>
+        <v>8.100000000000001</v>
       </c>
       <c r="J60" t="n">
-        <v>10.28333333333333</v>
+        <v>9.466666666666665</v>
       </c>
       <c r="K60" t="n">
-        <v>8.883333333333333</v>
+        <v>8.100000000000001</v>
       </c>
       <c r="L60" t="n">
-        <v>10.28333333333333</v>
+        <v>9.466666666666665</v>
       </c>
       <c r="M60" t="n">
         <v>0.3333333333333333</v>
@@ -3089,37 +3101,37 @@
         <v>59</v>
       </c>
       <c r="B61" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C61" t="n">
-        <v>18.151206181933</v>
+        <v>5.11105840595424</v>
       </c>
       <c r="D61" t="n">
-        <v>-13.637299694184</v>
+        <v>10.9732978458469</v>
       </c>
       <c r="E61" t="n">
-        <v>2530.79035</v>
+        <v>2866.242533333334</v>
       </c>
       <c r="F61" t="n">
-        <v>6.80844</v>
+        <v>6.516393333333333</v>
       </c>
       <c r="G61" t="n">
-        <v>8.883333333333333</v>
+        <v>8.100000000000001</v>
       </c>
       <c r="H61" t="n">
-        <v>10.28333333333333</v>
+        <v>9.466666666666665</v>
       </c>
       <c r="I61" t="n">
-        <v>8.883333333333333</v>
+        <v>8.100000000000001</v>
       </c>
       <c r="J61" t="n">
-        <v>10.28333333333333</v>
+        <v>9.466666666666665</v>
       </c>
       <c r="K61" t="n">
-        <v>8.883333333333333</v>
+        <v>8.100000000000001</v>
       </c>
       <c r="L61" t="n">
-        <v>10.28333333333333</v>
+        <v>9.466666666666665</v>
       </c>
       <c r="M61" t="n">
         <v>0.3333333333333333</v>
@@ -3133,37 +3145,37 @@
         <v>60</v>
       </c>
       <c r="B62" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C62" t="n">
-        <v>21.590843242742</v>
+        <v>5.11105840595424</v>
       </c>
       <c r="D62" t="n">
-        <v>-11.0654463649764</v>
+        <v>10.9732978458469</v>
       </c>
       <c r="E62" t="n">
-        <v>2276.15445</v>
+        <v>2866.242533333334</v>
       </c>
       <c r="F62" t="n">
-        <v>5.812015</v>
+        <v>6.516393333333333</v>
       </c>
       <c r="G62" t="n">
-        <v>9.016666666666666</v>
+        <v>8.100000000000001</v>
       </c>
       <c r="H62" t="n">
-        <v>10.48333333333333</v>
+        <v>9.466666666666665</v>
       </c>
       <c r="I62" t="n">
-        <v>9.016666666666666</v>
+        <v>8.100000000000001</v>
       </c>
       <c r="J62" t="n">
-        <v>10.48333333333333</v>
+        <v>9.466666666666665</v>
       </c>
       <c r="K62" t="n">
-        <v>9.016666666666666</v>
+        <v>8.100000000000001</v>
       </c>
       <c r="L62" t="n">
-        <v>10.48333333333333</v>
+        <v>9.466666666666665</v>
       </c>
       <c r="M62" t="n">
         <v>0.3333333333333333</v>
@@ -3177,37 +3189,37 @@
         <v>61</v>
       </c>
       <c r="B63" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C63" t="n">
-        <v>21.590843242742</v>
+        <v>30.4883697362318</v>
       </c>
       <c r="D63" t="n">
-        <v>-11.0654463649764</v>
+        <v>13.04953073461</v>
       </c>
       <c r="E63" t="n">
-        <v>2276.15445</v>
+        <v>2243.418</v>
       </c>
       <c r="F63" t="n">
-        <v>5.812015</v>
+        <v>6.769475</v>
       </c>
       <c r="G63" t="n">
-        <v>9.016666666666666</v>
+        <v>5.1</v>
       </c>
       <c r="H63" t="n">
-        <v>10.48333333333333</v>
+        <v>6.033333333333333</v>
       </c>
       <c r="I63" t="n">
-        <v>9.016666666666666</v>
+        <v>5.1</v>
       </c>
       <c r="J63" t="n">
-        <v>10.48333333333333</v>
+        <v>6.033333333333333</v>
       </c>
       <c r="K63" t="n">
-        <v>9.016666666666666</v>
+        <v>5.1</v>
       </c>
       <c r="L63" t="n">
-        <v>10.48333333333333</v>
+        <v>6.033333333333333</v>
       </c>
       <c r="M63" t="n">
         <v>0.3333333333333333</v>
@@ -3221,37 +3233,37 @@
         <v>62</v>
       </c>
       <c r="B64" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C64" t="n">
-        <v>19.4247893328668</v>
+        <v>30.4883697362318</v>
       </c>
       <c r="D64" t="n">
-        <v>-17.0996049039402</v>
+        <v>13.04953073461</v>
       </c>
       <c r="E64" t="n">
-        <v>2899.9628</v>
+        <v>2243.418</v>
       </c>
       <c r="F64" t="n">
-        <v>9.206685</v>
+        <v>6.769475</v>
       </c>
       <c r="G64" t="n">
-        <v>7.616666666666667</v>
+        <v>5.1</v>
       </c>
       <c r="H64" t="n">
-        <v>8.600000000000001</v>
+        <v>6.033333333333333</v>
       </c>
       <c r="I64" t="n">
-        <v>7.616666666666667</v>
+        <v>5.1</v>
       </c>
       <c r="J64" t="n">
-        <v>8.600000000000001</v>
+        <v>6.033333333333333</v>
       </c>
       <c r="K64" t="n">
-        <v>7.616666666666667</v>
+        <v>5.1</v>
       </c>
       <c r="L64" t="n">
-        <v>8.600000000000001</v>
+        <v>6.033333333333333</v>
       </c>
       <c r="M64" t="n">
         <v>0.3333333333333333</v>
@@ -3265,37 +3277,37 @@
         <v>63</v>
       </c>
       <c r="B65" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C65" t="n">
-        <v>19.4247893328668</v>
+        <v>-19.4837889125212</v>
       </c>
       <c r="D65" t="n">
-        <v>-17.0996049039402</v>
+        <v>-8.728925143928519</v>
       </c>
       <c r="E65" t="n">
-        <v>2899.9628</v>
+        <v>2650.770033333333</v>
       </c>
       <c r="F65" t="n">
-        <v>9.206685</v>
+        <v>7.165916666666667</v>
       </c>
       <c r="G65" t="n">
-        <v>7.616666666666667</v>
+        <v>12.15</v>
       </c>
       <c r="H65" t="n">
-        <v>8.600000000000001</v>
+        <v>12.96666666666667</v>
       </c>
       <c r="I65" t="n">
-        <v>7.616666666666667</v>
+        <v>12.15</v>
       </c>
       <c r="J65" t="n">
-        <v>8.600000000000001</v>
+        <v>12.96666666666667</v>
       </c>
       <c r="K65" t="n">
-        <v>7.616666666666667</v>
+        <v>12.15</v>
       </c>
       <c r="L65" t="n">
-        <v>8.600000000000001</v>
+        <v>12.96666666666667</v>
       </c>
       <c r="M65" t="n">
         <v>0.3333333333333333</v>
@@ -3309,37 +3321,37 @@
         <v>64</v>
       </c>
       <c r="B66" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C66" t="n">
-        <v>-3.94895297178467</v>
+        <v>-19.4837889125212</v>
       </c>
       <c r="D66" t="n">
-        <v>-34.8007269144264</v>
+        <v>-8.728925143928519</v>
       </c>
       <c r="E66" t="n">
-        <v>1659.91985</v>
+        <v>2650.770033333333</v>
       </c>
       <c r="F66" t="n">
-        <v>5.44331</v>
+        <v>7.165916666666667</v>
       </c>
       <c r="G66" t="n">
-        <v>3.199999999999999</v>
+        <v>12.15</v>
       </c>
       <c r="H66" t="n">
-        <v>4.183333333333334</v>
+        <v>12.96666666666667</v>
       </c>
       <c r="I66" t="n">
-        <v>3.199999999999999</v>
+        <v>12.15</v>
       </c>
       <c r="J66" t="n">
-        <v>4.183333333333334</v>
+        <v>12.96666666666667</v>
       </c>
       <c r="K66" t="n">
-        <v>3.199999999999999</v>
+        <v>12.15</v>
       </c>
       <c r="L66" t="n">
-        <v>4.183333333333334</v>
+        <v>12.96666666666667</v>
       </c>
       <c r="M66" t="n">
         <v>0.3333333333333333</v>
@@ -3353,37 +3365,37 @@
         <v>65</v>
       </c>
       <c r="B67" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C67" t="n">
-        <v>-3.94895297178467</v>
+        <v>-19.4837889125212</v>
       </c>
       <c r="D67" t="n">
-        <v>-34.8007269144264</v>
+        <v>-8.728925143928519</v>
       </c>
       <c r="E67" t="n">
-        <v>1659.91985</v>
+        <v>2650.770033333333</v>
       </c>
       <c r="F67" t="n">
-        <v>5.44331</v>
+        <v>7.165916666666667</v>
       </c>
       <c r="G67" t="n">
-        <v>3.199999999999999</v>
+        <v>12.15</v>
       </c>
       <c r="H67" t="n">
-        <v>4.183333333333334</v>
+        <v>12.96666666666667</v>
       </c>
       <c r="I67" t="n">
-        <v>3.199999999999999</v>
+        <v>12.15</v>
       </c>
       <c r="J67" t="n">
-        <v>4.183333333333334</v>
+        <v>12.96666666666667</v>
       </c>
       <c r="K67" t="n">
-        <v>3.199999999999999</v>
+        <v>12.15</v>
       </c>
       <c r="L67" t="n">
-        <v>4.183333333333334</v>
+        <v>12.96666666666667</v>
       </c>
       <c r="M67" t="n">
         <v>0.3333333333333333</v>
@@ -3397,37 +3409,37 @@
         <v>66</v>
       </c>
       <c r="B68" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C68" t="n">
-        <v>10.5334022336896</v>
+        <v>-8.69400896691041</v>
       </c>
       <c r="D68" t="n">
-        <v>17.621635259999</v>
+        <v>16.0355565510262</v>
       </c>
       <c r="E68" t="n">
-        <v>2784.5018</v>
+        <v>1704.19215</v>
       </c>
       <c r="F68" t="n">
-        <v>8.09606</v>
+        <v>4.879655</v>
       </c>
       <c r="G68" t="n">
-        <v>10.91666666666667</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="H68" t="n">
-        <v>11.91666666666667</v>
+        <v>10.65</v>
       </c>
       <c r="I68" t="n">
-        <v>10.91666666666667</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="J68" t="n">
-        <v>11.91666666666667</v>
+        <v>10.65</v>
       </c>
       <c r="K68" t="n">
-        <v>10.91666666666667</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="L68" t="n">
-        <v>11.91666666666667</v>
+        <v>10.65</v>
       </c>
       <c r="M68" t="n">
         <v>0.3333333333333333</v>
@@ -3441,37 +3453,37 @@
         <v>67</v>
       </c>
       <c r="B69" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C69" t="n">
-        <v>5.11105840595424</v>
+        <v>-8.69400896691041</v>
       </c>
       <c r="D69" t="n">
-        <v>10.9732978458469</v>
+        <v>16.0355565510262</v>
       </c>
       <c r="E69" t="n">
-        <v>2866.242533333334</v>
+        <v>1704.19215</v>
       </c>
       <c r="F69" t="n">
-        <v>6.516393333333333</v>
+        <v>4.879655</v>
       </c>
       <c r="G69" t="n">
-        <v>8.100000000000001</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="H69" t="n">
-        <v>9.466666666666665</v>
+        <v>10.65</v>
       </c>
       <c r="I69" t="n">
-        <v>8.100000000000001</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="J69" t="n">
-        <v>9.466666666666665</v>
+        <v>10.65</v>
       </c>
       <c r="K69" t="n">
-        <v>8.100000000000001</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="L69" t="n">
-        <v>9.466666666666665</v>
+        <v>10.65</v>
       </c>
       <c r="M69" t="n">
         <v>0.3333333333333333</v>
@@ -3485,37 +3497,37 @@
         <v>68</v>
       </c>
       <c r="B70" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C70" t="n">
-        <v>5.11105840595424</v>
+        <v>-9.42229186702531</v>
       </c>
       <c r="D70" t="n">
-        <v>10.9732978458469</v>
+        <v>-18.809064939498</v>
       </c>
       <c r="E70" t="n">
-        <v>2866.242533333334</v>
+        <v>2238.462733333333</v>
       </c>
       <c r="F70" t="n">
-        <v>6.516393333333333</v>
+        <v>5.696406666666667</v>
       </c>
       <c r="G70" t="n">
-        <v>8.100000000000001</v>
+        <v>7.083333333333334</v>
       </c>
       <c r="H70" t="n">
-        <v>9.466666666666665</v>
+        <v>8.533333333333335</v>
       </c>
       <c r="I70" t="n">
-        <v>8.100000000000001</v>
+        <v>7.083333333333334</v>
       </c>
       <c r="J70" t="n">
-        <v>9.466666666666665</v>
+        <v>8.533333333333335</v>
       </c>
       <c r="K70" t="n">
-        <v>8.100000000000001</v>
+        <v>7.083333333333334</v>
       </c>
       <c r="L70" t="n">
-        <v>9.466666666666665</v>
+        <v>8.533333333333335</v>
       </c>
       <c r="M70" t="n">
         <v>0.3333333333333333</v>
@@ -3529,37 +3541,37 @@
         <v>69</v>
       </c>
       <c r="B71" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C71" t="n">
-        <v>5.11105840595424</v>
+        <v>-9.42229186702531</v>
       </c>
       <c r="D71" t="n">
-        <v>10.9732978458469</v>
+        <v>-18.809064939498</v>
       </c>
       <c r="E71" t="n">
-        <v>2866.242533333334</v>
+        <v>2238.462733333333</v>
       </c>
       <c r="F71" t="n">
-        <v>6.516393333333333</v>
+        <v>5.696406666666667</v>
       </c>
       <c r="G71" t="n">
-        <v>8.100000000000001</v>
+        <v>7.083333333333334</v>
       </c>
       <c r="H71" t="n">
-        <v>9.466666666666665</v>
+        <v>8.533333333333335</v>
       </c>
       <c r="I71" t="n">
-        <v>8.100000000000001</v>
+        <v>7.083333333333334</v>
       </c>
       <c r="J71" t="n">
-        <v>9.466666666666665</v>
+        <v>8.533333333333335</v>
       </c>
       <c r="K71" t="n">
-        <v>8.100000000000001</v>
+        <v>7.083333333333334</v>
       </c>
       <c r="L71" t="n">
-        <v>9.466666666666665</v>
+        <v>8.533333333333335</v>
       </c>
       <c r="M71" t="n">
         <v>0.3333333333333333</v>
@@ -3573,37 +3585,37 @@
         <v>70</v>
       </c>
       <c r="B72" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C72" t="n">
-        <v>30.4883697362318</v>
+        <v>-9.42229186702531</v>
       </c>
       <c r="D72" t="n">
-        <v>13.04953073461</v>
+        <v>-18.809064939498</v>
       </c>
       <c r="E72" t="n">
-        <v>2243.418</v>
+        <v>2238.462733333333</v>
       </c>
       <c r="F72" t="n">
-        <v>6.769475</v>
+        <v>5.696406666666667</v>
       </c>
       <c r="G72" t="n">
-        <v>5.1</v>
+        <v>7.083333333333334</v>
       </c>
       <c r="H72" t="n">
-        <v>6.033333333333333</v>
+        <v>8.533333333333335</v>
       </c>
       <c r="I72" t="n">
-        <v>5.1</v>
+        <v>7.083333333333334</v>
       </c>
       <c r="J72" t="n">
-        <v>6.033333333333333</v>
+        <v>8.533333333333335</v>
       </c>
       <c r="K72" t="n">
-        <v>5.1</v>
+        <v>7.083333333333334</v>
       </c>
       <c r="L72" t="n">
-        <v>6.033333333333333</v>
+        <v>8.533333333333335</v>
       </c>
       <c r="M72" t="n">
         <v>0.3333333333333333</v>
@@ -3617,37 +3629,37 @@
         <v>71</v>
       </c>
       <c r="B73" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C73" t="n">
-        <v>30.4883697362318</v>
+        <v>16.6645391539304</v>
       </c>
       <c r="D73" t="n">
-        <v>13.04953073461</v>
+        <v>-0.259417867939575</v>
       </c>
       <c r="E73" t="n">
-        <v>2243.418</v>
+        <v>2321.281966666667</v>
       </c>
       <c r="F73" t="n">
-        <v>6.769475</v>
+        <v>6.252913333333333</v>
       </c>
       <c r="G73" t="n">
-        <v>5.1</v>
+        <v>9.983333333333334</v>
       </c>
       <c r="H73" t="n">
-        <v>6.033333333333333</v>
+        <v>10.86666666666667</v>
       </c>
       <c r="I73" t="n">
-        <v>5.1</v>
+        <v>9.983333333333334</v>
       </c>
       <c r="J73" t="n">
-        <v>6.033333333333333</v>
+        <v>10.86666666666667</v>
       </c>
       <c r="K73" t="n">
-        <v>5.1</v>
+        <v>9.983333333333334</v>
       </c>
       <c r="L73" t="n">
-        <v>6.033333333333333</v>
+        <v>10.86666666666667</v>
       </c>
       <c r="M73" t="n">
         <v>0.3333333333333333</v>
@@ -3661,37 +3673,37 @@
         <v>72</v>
       </c>
       <c r="B74" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C74" t="n">
-        <v>-19.4837889125212</v>
+        <v>16.6645391539304</v>
       </c>
       <c r="D74" t="n">
-        <v>-8.728925143928519</v>
+        <v>-0.259417867939575</v>
       </c>
       <c r="E74" t="n">
-        <v>2650.770033333333</v>
+        <v>2321.281966666667</v>
       </c>
       <c r="F74" t="n">
-        <v>7.165916666666667</v>
+        <v>6.252913333333333</v>
       </c>
       <c r="G74" t="n">
-        <v>12.15</v>
+        <v>9.983333333333334</v>
       </c>
       <c r="H74" t="n">
-        <v>12.96666666666667</v>
+        <v>10.86666666666667</v>
       </c>
       <c r="I74" t="n">
-        <v>12.15</v>
+        <v>9.983333333333334</v>
       </c>
       <c r="J74" t="n">
-        <v>12.96666666666667</v>
+        <v>10.86666666666667</v>
       </c>
       <c r="K74" t="n">
-        <v>12.15</v>
+        <v>9.983333333333334</v>
       </c>
       <c r="L74" t="n">
-        <v>12.96666666666667</v>
+        <v>10.86666666666667</v>
       </c>
       <c r="M74" t="n">
         <v>0.3333333333333333</v>
@@ -3705,37 +3717,37 @@
         <v>73</v>
       </c>
       <c r="B75" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C75" t="n">
-        <v>-19.4837889125212</v>
+        <v>16.6645391539304</v>
       </c>
       <c r="D75" t="n">
-        <v>-8.728925143928519</v>
+        <v>-0.259417867939575</v>
       </c>
       <c r="E75" t="n">
-        <v>2650.770033333333</v>
+        <v>2321.281966666667</v>
       </c>
       <c r="F75" t="n">
-        <v>7.165916666666667</v>
+        <v>6.252913333333333</v>
       </c>
       <c r="G75" t="n">
-        <v>12.15</v>
+        <v>9.983333333333334</v>
       </c>
       <c r="H75" t="n">
-        <v>12.96666666666667</v>
+        <v>10.86666666666667</v>
       </c>
       <c r="I75" t="n">
-        <v>12.15</v>
+        <v>9.983333333333334</v>
       </c>
       <c r="J75" t="n">
-        <v>12.96666666666667</v>
+        <v>10.86666666666667</v>
       </c>
       <c r="K75" t="n">
-        <v>12.15</v>
+        <v>9.983333333333334</v>
       </c>
       <c r="L75" t="n">
-        <v>12.96666666666667</v>
+        <v>10.86666666666667</v>
       </c>
       <c r="M75" t="n">
         <v>0.3333333333333333</v>
@@ -3749,37 +3761,37 @@
         <v>74</v>
       </c>
       <c r="B76" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C76" t="n">
-        <v>-19.4837889125212</v>
+        <v>-7.26957106603941</v>
       </c>
       <c r="D76" t="n">
-        <v>-8.728925143928519</v>
+        <v>-30.7450666987351</v>
       </c>
       <c r="E76" t="n">
-        <v>2650.770033333333</v>
+        <v>2472.8861</v>
       </c>
       <c r="F76" t="n">
-        <v>7.165916666666667</v>
+        <v>6.55764</v>
       </c>
       <c r="G76" t="n">
-        <v>12.15</v>
+        <v>9.333333333333332</v>
       </c>
       <c r="H76" t="n">
-        <v>12.96666666666667</v>
+        <v>10.73333333333333</v>
       </c>
       <c r="I76" t="n">
-        <v>12.15</v>
+        <v>9.333333333333332</v>
       </c>
       <c r="J76" t="n">
-        <v>12.96666666666667</v>
+        <v>10.73333333333333</v>
       </c>
       <c r="K76" t="n">
-        <v>12.15</v>
+        <v>9.333333333333332</v>
       </c>
       <c r="L76" t="n">
-        <v>12.96666666666667</v>
+        <v>10.73333333333333</v>
       </c>
       <c r="M76" t="n">
         <v>0.3333333333333333</v>
@@ -3793,37 +3805,37 @@
         <v>75</v>
       </c>
       <c r="B77" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C77" t="n">
-        <v>-8.69400896691041</v>
+        <v>-7.26957106603941</v>
       </c>
       <c r="D77" t="n">
-        <v>16.0355565510262</v>
+        <v>-30.7450666987351</v>
       </c>
       <c r="E77" t="n">
-        <v>1704.19215</v>
+        <v>2472.8861</v>
       </c>
       <c r="F77" t="n">
-        <v>4.879655</v>
+        <v>6.55764</v>
       </c>
       <c r="G77" t="n">
-        <v>9.550000000000001</v>
+        <v>9.333333333333332</v>
       </c>
       <c r="H77" t="n">
-        <v>10.65</v>
+        <v>10.73333333333333</v>
       </c>
       <c r="I77" t="n">
-        <v>9.550000000000001</v>
+        <v>9.333333333333332</v>
       </c>
       <c r="J77" t="n">
-        <v>10.65</v>
+        <v>10.73333333333333</v>
       </c>
       <c r="K77" t="n">
-        <v>9.550000000000001</v>
+        <v>9.333333333333332</v>
       </c>
       <c r="L77" t="n">
-        <v>10.65</v>
+        <v>10.73333333333333</v>
       </c>
       <c r="M77" t="n">
         <v>0.3333333333333333</v>
@@ -3837,37 +3849,37 @@
         <v>76</v>
       </c>
       <c r="B78" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C78" t="n">
-        <v>-8.69400896691041</v>
+        <v>-7.26957106603941</v>
       </c>
       <c r="D78" t="n">
-        <v>16.0355565510262</v>
+        <v>-30.7450666987351</v>
       </c>
       <c r="E78" t="n">
-        <v>1704.19215</v>
+        <v>2472.8861</v>
       </c>
       <c r="F78" t="n">
-        <v>4.879655</v>
+        <v>6.55764</v>
       </c>
       <c r="G78" t="n">
-        <v>9.550000000000001</v>
+        <v>9.333333333333332</v>
       </c>
       <c r="H78" t="n">
-        <v>10.65</v>
+        <v>10.73333333333333</v>
       </c>
       <c r="I78" t="n">
-        <v>9.550000000000001</v>
+        <v>9.333333333333332</v>
       </c>
       <c r="J78" t="n">
-        <v>10.65</v>
+        <v>10.73333333333333</v>
       </c>
       <c r="K78" t="n">
-        <v>9.550000000000001</v>
+        <v>9.333333333333332</v>
       </c>
       <c r="L78" t="n">
-        <v>10.65</v>
+        <v>10.73333333333333</v>
       </c>
       <c r="M78" t="n">
         <v>0.3333333333333333</v>
@@ -3881,37 +3893,37 @@
         <v>77</v>
       </c>
       <c r="B79" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C79" t="n">
-        <v>-9.42229186702531</v>
+        <v>-30.4738708628108</v>
       </c>
       <c r="D79" t="n">
-        <v>-18.809064939498</v>
+        <v>0.417718230968227</v>
       </c>
       <c r="E79" t="n">
-        <v>2238.462733333333</v>
+        <v>2439.52946</v>
       </c>
       <c r="F79" t="n">
-        <v>5.696406666666667</v>
+        <v>6.159698000000001</v>
       </c>
       <c r="G79" t="n">
-        <v>7.083333333333334</v>
+        <v>9.916666666666668</v>
       </c>
       <c r="H79" t="n">
-        <v>8.533333333333335</v>
+        <v>11.2</v>
       </c>
       <c r="I79" t="n">
-        <v>7.083333333333334</v>
+        <v>9.916666666666668</v>
       </c>
       <c r="J79" t="n">
-        <v>8.533333333333335</v>
+        <v>11.2</v>
       </c>
       <c r="K79" t="n">
-        <v>7.083333333333334</v>
+        <v>9.916666666666668</v>
       </c>
       <c r="L79" t="n">
-        <v>8.533333333333335</v>
+        <v>11.2</v>
       </c>
       <c r="M79" t="n">
         <v>0.3333333333333333</v>
@@ -3925,37 +3937,37 @@
         <v>78</v>
       </c>
       <c r="B80" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C80" t="n">
-        <v>-9.42229186702531</v>
+        <v>-30.4738708628108</v>
       </c>
       <c r="D80" t="n">
-        <v>-18.809064939498</v>
+        <v>0.417718230968227</v>
       </c>
       <c r="E80" t="n">
-        <v>2238.462733333333</v>
+        <v>2439.52946</v>
       </c>
       <c r="F80" t="n">
-        <v>5.696406666666667</v>
+        <v>6.159698000000001</v>
       </c>
       <c r="G80" t="n">
-        <v>7.083333333333334</v>
+        <v>9.916666666666668</v>
       </c>
       <c r="H80" t="n">
-        <v>8.533333333333335</v>
+        <v>11.2</v>
       </c>
       <c r="I80" t="n">
-        <v>7.083333333333334</v>
+        <v>9.916666666666668</v>
       </c>
       <c r="J80" t="n">
-        <v>8.533333333333335</v>
+        <v>11.2</v>
       </c>
       <c r="K80" t="n">
-        <v>7.083333333333334</v>
+        <v>9.916666666666668</v>
       </c>
       <c r="L80" t="n">
-        <v>8.533333333333335</v>
+        <v>11.2</v>
       </c>
       <c r="M80" t="n">
         <v>0.3333333333333333</v>
@@ -3969,37 +3981,37 @@
         <v>79</v>
       </c>
       <c r="B81" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C81" t="n">
-        <v>-9.42229186702531</v>
+        <v>-30.4738708628108</v>
       </c>
       <c r="D81" t="n">
-        <v>-18.809064939498</v>
+        <v>0.417718230968227</v>
       </c>
       <c r="E81" t="n">
-        <v>2238.462733333333</v>
+        <v>2439.52946</v>
       </c>
       <c r="F81" t="n">
-        <v>5.696406666666667</v>
+        <v>6.159698000000001</v>
       </c>
       <c r="G81" t="n">
-        <v>7.083333333333334</v>
+        <v>9.916666666666668</v>
       </c>
       <c r="H81" t="n">
-        <v>8.533333333333335</v>
+        <v>11.2</v>
       </c>
       <c r="I81" t="n">
-        <v>7.083333333333334</v>
+        <v>9.916666666666668</v>
       </c>
       <c r="J81" t="n">
-        <v>8.533333333333335</v>
+        <v>11.2</v>
       </c>
       <c r="K81" t="n">
-        <v>7.083333333333334</v>
+        <v>9.916666666666668</v>
       </c>
       <c r="L81" t="n">
-        <v>8.533333333333335</v>
+        <v>11.2</v>
       </c>
       <c r="M81" t="n">
         <v>0.3333333333333333</v>
@@ -4013,37 +4025,37 @@
         <v>80</v>
       </c>
       <c r="B82" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C82" t="n">
-        <v>16.6645391539304</v>
+        <v>-30.4738708628108</v>
       </c>
       <c r="D82" t="n">
-        <v>-0.259417867939575</v>
+        <v>0.417718230968227</v>
       </c>
       <c r="E82" t="n">
-        <v>2321.281966666667</v>
+        <v>2439.52946</v>
       </c>
       <c r="F82" t="n">
-        <v>6.252913333333333</v>
+        <v>6.159698000000001</v>
       </c>
       <c r="G82" t="n">
-        <v>9.983333333333334</v>
+        <v>9.916666666666668</v>
       </c>
       <c r="H82" t="n">
-        <v>10.86666666666667</v>
+        <v>11.2</v>
       </c>
       <c r="I82" t="n">
-        <v>9.983333333333334</v>
+        <v>9.916666666666668</v>
       </c>
       <c r="J82" t="n">
-        <v>10.86666666666667</v>
+        <v>11.2</v>
       </c>
       <c r="K82" t="n">
-        <v>9.983333333333334</v>
+        <v>9.916666666666668</v>
       </c>
       <c r="L82" t="n">
-        <v>10.86666666666667</v>
+        <v>11.2</v>
       </c>
       <c r="M82" t="n">
         <v>0.3333333333333333</v>
@@ -4057,37 +4069,37 @@
         <v>81</v>
       </c>
       <c r="B83" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C83" t="n">
-        <v>16.6645391539304</v>
+        <v>-30.4738708628108</v>
       </c>
       <c r="D83" t="n">
-        <v>-0.259417867939575</v>
+        <v>0.417718230968227</v>
       </c>
       <c r="E83" t="n">
-        <v>2321.281966666667</v>
+        <v>2439.52946</v>
       </c>
       <c r="F83" t="n">
-        <v>6.252913333333333</v>
+        <v>6.159698000000001</v>
       </c>
       <c r="G83" t="n">
-        <v>9.983333333333334</v>
+        <v>9.916666666666668</v>
       </c>
       <c r="H83" t="n">
-        <v>10.86666666666667</v>
+        <v>11.2</v>
       </c>
       <c r="I83" t="n">
-        <v>9.983333333333334</v>
+        <v>9.916666666666668</v>
       </c>
       <c r="J83" t="n">
-        <v>10.86666666666667</v>
+        <v>11.2</v>
       </c>
       <c r="K83" t="n">
-        <v>9.983333333333334</v>
+        <v>9.916666666666668</v>
       </c>
       <c r="L83" t="n">
-        <v>10.86666666666667</v>
+        <v>11.2</v>
       </c>
       <c r="M83" t="n">
         <v>0.3333333333333333</v>
@@ -4101,37 +4113,37 @@
         <v>82</v>
       </c>
       <c r="B84" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C84" t="n">
-        <v>16.6645391539304</v>
+        <v>30.9734492073973</v>
       </c>
       <c r="D84" t="n">
-        <v>-0.259417867939575</v>
+        <v>-24.4269327966448</v>
       </c>
       <c r="E84" t="n">
-        <v>2321.281966666667</v>
+        <v>2355.053633333333</v>
       </c>
       <c r="F84" t="n">
-        <v>6.252913333333333</v>
+        <v>5.909806666666667</v>
       </c>
       <c r="G84" t="n">
-        <v>9.983333333333334</v>
+        <v>5.833333333333334</v>
       </c>
       <c r="H84" t="n">
-        <v>10.86666666666667</v>
+        <v>7.15</v>
       </c>
       <c r="I84" t="n">
-        <v>9.983333333333334</v>
+        <v>5.833333333333334</v>
       </c>
       <c r="J84" t="n">
-        <v>10.86666666666667</v>
+        <v>7.15</v>
       </c>
       <c r="K84" t="n">
-        <v>9.983333333333334</v>
+        <v>5.833333333333334</v>
       </c>
       <c r="L84" t="n">
-        <v>10.86666666666667</v>
+        <v>7.15</v>
       </c>
       <c r="M84" t="n">
         <v>0.3333333333333333</v>
@@ -4145,37 +4157,37 @@
         <v>83</v>
       </c>
       <c r="B85" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C85" t="n">
-        <v>-7.26957106603941</v>
+        <v>30.9734492073973</v>
       </c>
       <c r="D85" t="n">
-        <v>-30.7450666987351</v>
+        <v>-24.4269327966448</v>
       </c>
       <c r="E85" t="n">
-        <v>2472.8861</v>
+        <v>2355.053633333333</v>
       </c>
       <c r="F85" t="n">
-        <v>6.55764</v>
+        <v>5.909806666666667</v>
       </c>
       <c r="G85" t="n">
-        <v>9.333333333333332</v>
+        <v>5.833333333333334</v>
       </c>
       <c r="H85" t="n">
-        <v>10.73333333333333</v>
+        <v>7.15</v>
       </c>
       <c r="I85" t="n">
-        <v>9.333333333333332</v>
+        <v>5.833333333333334</v>
       </c>
       <c r="J85" t="n">
-        <v>10.73333333333333</v>
+        <v>7.15</v>
       </c>
       <c r="K85" t="n">
-        <v>9.333333333333332</v>
+        <v>5.833333333333334</v>
       </c>
       <c r="L85" t="n">
-        <v>10.73333333333333</v>
+        <v>7.15</v>
       </c>
       <c r="M85" t="n">
         <v>0.3333333333333333</v>
@@ -4189,37 +4201,37 @@
         <v>84</v>
       </c>
       <c r="B86" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C86" t="n">
-        <v>-7.26957106603941</v>
+        <v>30.9734492073973</v>
       </c>
       <c r="D86" t="n">
-        <v>-30.7450666987351</v>
+        <v>-24.4269327966448</v>
       </c>
       <c r="E86" t="n">
-        <v>2472.8861</v>
+        <v>2355.053633333333</v>
       </c>
       <c r="F86" t="n">
-        <v>6.55764</v>
+        <v>5.909806666666667</v>
       </c>
       <c r="G86" t="n">
-        <v>9.333333333333332</v>
+        <v>5.833333333333334</v>
       </c>
       <c r="H86" t="n">
-        <v>10.73333333333333</v>
+        <v>7.15</v>
       </c>
       <c r="I86" t="n">
-        <v>9.333333333333332</v>
+        <v>5.833333333333334</v>
       </c>
       <c r="J86" t="n">
-        <v>10.73333333333333</v>
+        <v>7.15</v>
       </c>
       <c r="K86" t="n">
-        <v>9.333333333333332</v>
+        <v>5.833333333333334</v>
       </c>
       <c r="L86" t="n">
-        <v>10.73333333333333</v>
+        <v>7.15</v>
       </c>
       <c r="M86" t="n">
         <v>0.3333333333333333</v>
@@ -4233,37 +4245,37 @@
         <v>85</v>
       </c>
       <c r="B87" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C87" t="n">
-        <v>-7.26957106603941</v>
+        <v>35.8691630924626</v>
       </c>
       <c r="D87" t="n">
-        <v>-30.7450666987351</v>
+        <v>6.80594557114049</v>
       </c>
       <c r="E87" t="n">
-        <v>2472.8861</v>
+        <v>2203.217666666667</v>
       </c>
       <c r="F87" t="n">
-        <v>6.55764</v>
+        <v>5.638176666666666</v>
       </c>
       <c r="G87" t="n">
-        <v>9.333333333333332</v>
+        <v>6.633333333333333</v>
       </c>
       <c r="H87" t="n">
-        <v>10.73333333333333</v>
+        <v>7.983333333333333</v>
       </c>
       <c r="I87" t="n">
-        <v>9.333333333333332</v>
+        <v>6.633333333333333</v>
       </c>
       <c r="J87" t="n">
-        <v>10.73333333333333</v>
+        <v>7.983333333333333</v>
       </c>
       <c r="K87" t="n">
-        <v>9.333333333333332</v>
+        <v>6.633333333333333</v>
       </c>
       <c r="L87" t="n">
-        <v>10.73333333333333</v>
+        <v>7.983333333333333</v>
       </c>
       <c r="M87" t="n">
         <v>0.3333333333333333</v>
@@ -4277,37 +4289,37 @@
         <v>86</v>
       </c>
       <c r="B88" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C88" t="n">
-        <v>-30.4738708628108</v>
+        <v>35.8691630924626</v>
       </c>
       <c r="D88" t="n">
-        <v>0.417718230968227</v>
+        <v>6.80594557114049</v>
       </c>
       <c r="E88" t="n">
-        <v>2439.52946</v>
+        <v>2203.217666666667</v>
       </c>
       <c r="F88" t="n">
-        <v>6.159698000000001</v>
+        <v>5.638176666666666</v>
       </c>
       <c r="G88" t="n">
-        <v>9.916666666666668</v>
+        <v>6.633333333333333</v>
       </c>
       <c r="H88" t="n">
-        <v>11.2</v>
+        <v>7.983333333333333</v>
       </c>
       <c r="I88" t="n">
-        <v>9.916666666666668</v>
+        <v>6.633333333333333</v>
       </c>
       <c r="J88" t="n">
-        <v>11.2</v>
+        <v>7.983333333333333</v>
       </c>
       <c r="K88" t="n">
-        <v>9.916666666666668</v>
+        <v>6.633333333333333</v>
       </c>
       <c r="L88" t="n">
-        <v>11.2</v>
+        <v>7.983333333333333</v>
       </c>
       <c r="M88" t="n">
         <v>0.3333333333333333</v>
@@ -4321,37 +4333,37 @@
         <v>87</v>
       </c>
       <c r="B89" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C89" t="n">
-        <v>-30.4738708628108</v>
+        <v>35.8691630924626</v>
       </c>
       <c r="D89" t="n">
-        <v>0.417718230968227</v>
+        <v>6.80594557114049</v>
       </c>
       <c r="E89" t="n">
-        <v>2439.52946</v>
+        <v>2203.217666666667</v>
       </c>
       <c r="F89" t="n">
-        <v>6.159698000000001</v>
+        <v>5.638176666666666</v>
       </c>
       <c r="G89" t="n">
-        <v>9.916666666666668</v>
+        <v>6.633333333333333</v>
       </c>
       <c r="H89" t="n">
-        <v>11.2</v>
+        <v>7.983333333333333</v>
       </c>
       <c r="I89" t="n">
-        <v>9.916666666666668</v>
+        <v>6.633333333333333</v>
       </c>
       <c r="J89" t="n">
-        <v>11.2</v>
+        <v>7.983333333333333</v>
       </c>
       <c r="K89" t="n">
-        <v>9.916666666666668</v>
+        <v>6.633333333333333</v>
       </c>
       <c r="L89" t="n">
-        <v>11.2</v>
+        <v>7.983333333333333</v>
       </c>
       <c r="M89" t="n">
         <v>0.3333333333333333</v>
@@ -4365,37 +4377,37 @@
         <v>88</v>
       </c>
       <c r="B90" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C90" t="n">
-        <v>-30.4738708628108</v>
+        <v>29.2918813421379</v>
       </c>
       <c r="D90" t="n">
-        <v>0.417718230968227</v>
+        <v>-11.2363981231824</v>
       </c>
       <c r="E90" t="n">
-        <v>2439.52946</v>
+        <v>2933.964</v>
       </c>
       <c r="F90" t="n">
-        <v>6.159698000000001</v>
+        <v>9.727729999999999</v>
       </c>
       <c r="G90" t="n">
-        <v>9.916666666666668</v>
+        <v>6.300000000000001</v>
       </c>
       <c r="H90" t="n">
-        <v>11.2</v>
+        <v>7.383333333333333</v>
       </c>
       <c r="I90" t="n">
-        <v>9.916666666666668</v>
+        <v>6.300000000000001</v>
       </c>
       <c r="J90" t="n">
-        <v>11.2</v>
+        <v>7.383333333333333</v>
       </c>
       <c r="K90" t="n">
-        <v>9.916666666666668</v>
+        <v>6.300000000000001</v>
       </c>
       <c r="L90" t="n">
-        <v>11.2</v>
+        <v>7.383333333333333</v>
       </c>
       <c r="M90" t="n">
         <v>0.3333333333333333</v>
@@ -4409,37 +4421,37 @@
         <v>89</v>
       </c>
       <c r="B91" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C91" t="n">
-        <v>-30.4738708628108</v>
+        <v>-32.4103858046121</v>
       </c>
       <c r="D91" t="n">
-        <v>0.417718230968227</v>
+        <v>-2.65068011202597</v>
       </c>
       <c r="E91" t="n">
-        <v>2439.52946</v>
+        <v>2935.7956</v>
       </c>
       <c r="F91" t="n">
-        <v>6.159698000000001</v>
+        <v>7.748356666666667</v>
       </c>
       <c r="G91" t="n">
-        <v>9.916666666666668</v>
+        <v>3.25</v>
       </c>
       <c r="H91" t="n">
-        <v>11.2</v>
+        <v>4.65</v>
       </c>
       <c r="I91" t="n">
-        <v>9.916666666666668</v>
+        <v>3.25</v>
       </c>
       <c r="J91" t="n">
-        <v>11.2</v>
+        <v>4.65</v>
       </c>
       <c r="K91" t="n">
-        <v>9.916666666666668</v>
+        <v>3.25</v>
       </c>
       <c r="L91" t="n">
-        <v>11.2</v>
+        <v>4.65</v>
       </c>
       <c r="M91" t="n">
         <v>0.3333333333333333</v>
@@ -4453,37 +4465,37 @@
         <v>90</v>
       </c>
       <c r="B92" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C92" t="n">
-        <v>-30.4738708628108</v>
+        <v>-32.4103858046121</v>
       </c>
       <c r="D92" t="n">
-        <v>0.417718230968227</v>
+        <v>-2.65068011202597</v>
       </c>
       <c r="E92" t="n">
-        <v>2439.52946</v>
+        <v>2935.7956</v>
       </c>
       <c r="F92" t="n">
-        <v>6.159698000000001</v>
+        <v>7.748356666666667</v>
       </c>
       <c r="G92" t="n">
-        <v>9.916666666666668</v>
+        <v>3.25</v>
       </c>
       <c r="H92" t="n">
-        <v>11.2</v>
+        <v>4.65</v>
       </c>
       <c r="I92" t="n">
-        <v>9.916666666666668</v>
+        <v>3.25</v>
       </c>
       <c r="J92" t="n">
-        <v>11.2</v>
+        <v>4.65</v>
       </c>
       <c r="K92" t="n">
-        <v>9.916666666666668</v>
+        <v>3.25</v>
       </c>
       <c r="L92" t="n">
-        <v>11.2</v>
+        <v>4.65</v>
       </c>
       <c r="M92" t="n">
         <v>0.3333333333333333</v>
@@ -4497,37 +4509,37 @@
         <v>91</v>
       </c>
       <c r="B93" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C93" t="n">
-        <v>30.9734492073973</v>
+        <v>-32.4103858046121</v>
       </c>
       <c r="D93" t="n">
-        <v>-24.4269327966448</v>
+        <v>-2.65068011202597</v>
       </c>
       <c r="E93" t="n">
-        <v>2355.053633333333</v>
+        <v>2935.7956</v>
       </c>
       <c r="F93" t="n">
-        <v>5.909806666666667</v>
+        <v>7.748356666666667</v>
       </c>
       <c r="G93" t="n">
-        <v>5.833333333333334</v>
+        <v>3.25</v>
       </c>
       <c r="H93" t="n">
-        <v>7.15</v>
+        <v>4.65</v>
       </c>
       <c r="I93" t="n">
-        <v>5.833333333333334</v>
+        <v>3.25</v>
       </c>
       <c r="J93" t="n">
-        <v>7.15</v>
+        <v>4.65</v>
       </c>
       <c r="K93" t="n">
-        <v>5.833333333333334</v>
+        <v>3.25</v>
       </c>
       <c r="L93" t="n">
-        <v>7.15</v>
+        <v>4.65</v>
       </c>
       <c r="M93" t="n">
         <v>0.3333333333333333</v>
@@ -4541,37 +4553,37 @@
         <v>92</v>
       </c>
       <c r="B94" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C94" t="n">
-        <v>30.9734492073973</v>
+        <v>14.512163776104</v>
       </c>
       <c r="D94" t="n">
-        <v>-24.4269327966448</v>
+        <v>29.3929978248616</v>
       </c>
       <c r="E94" t="n">
-        <v>2355.053633333333</v>
+        <v>2476.6573</v>
       </c>
       <c r="F94" t="n">
-        <v>5.909806666666667</v>
+        <v>6.5043975</v>
       </c>
       <c r="G94" t="n">
-        <v>5.833333333333334</v>
+        <v>2.383333333333333</v>
       </c>
       <c r="H94" t="n">
-        <v>7.15</v>
+        <v>3.6</v>
       </c>
       <c r="I94" t="n">
-        <v>5.833333333333334</v>
+        <v>2.383333333333333</v>
       </c>
       <c r="J94" t="n">
-        <v>7.15</v>
+        <v>3.6</v>
       </c>
       <c r="K94" t="n">
-        <v>5.833333333333334</v>
+        <v>2.383333333333333</v>
       </c>
       <c r="L94" t="n">
-        <v>7.15</v>
+        <v>3.6</v>
       </c>
       <c r="M94" t="n">
         <v>0.3333333333333333</v>
@@ -4585,37 +4597,37 @@
         <v>93</v>
       </c>
       <c r="B95" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C95" t="n">
-        <v>30.9734492073973</v>
+        <v>14.512163776104</v>
       </c>
       <c r="D95" t="n">
-        <v>-24.4269327966448</v>
+        <v>29.3929978248616</v>
       </c>
       <c r="E95" t="n">
-        <v>2355.053633333333</v>
+        <v>2476.6573</v>
       </c>
       <c r="F95" t="n">
-        <v>5.909806666666667</v>
+        <v>6.5043975</v>
       </c>
       <c r="G95" t="n">
-        <v>5.833333333333334</v>
+        <v>2.383333333333333</v>
       </c>
       <c r="H95" t="n">
-        <v>7.15</v>
+        <v>3.6</v>
       </c>
       <c r="I95" t="n">
-        <v>5.833333333333334</v>
+        <v>2.383333333333333</v>
       </c>
       <c r="J95" t="n">
-        <v>7.15</v>
+        <v>3.6</v>
       </c>
       <c r="K95" t="n">
-        <v>5.833333333333334</v>
+        <v>2.383333333333333</v>
       </c>
       <c r="L95" t="n">
-        <v>7.15</v>
+        <v>3.6</v>
       </c>
       <c r="M95" t="n">
         <v>0.3333333333333333</v>
@@ -4629,37 +4641,37 @@
         <v>94</v>
       </c>
       <c r="B96" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C96" t="n">
-        <v>35.8691630924626</v>
+        <v>14.512163776104</v>
       </c>
       <c r="D96" t="n">
-        <v>6.80594557114049</v>
+        <v>29.3929978248616</v>
       </c>
       <c r="E96" t="n">
-        <v>2203.217666666667</v>
+        <v>2476.6573</v>
       </c>
       <c r="F96" t="n">
-        <v>5.638176666666666</v>
+        <v>6.5043975</v>
       </c>
       <c r="G96" t="n">
-        <v>6.633333333333333</v>
+        <v>2.383333333333333</v>
       </c>
       <c r="H96" t="n">
-        <v>7.983333333333333</v>
+        <v>3.6</v>
       </c>
       <c r="I96" t="n">
-        <v>6.633333333333333</v>
+        <v>2.383333333333333</v>
       </c>
       <c r="J96" t="n">
-        <v>7.983333333333333</v>
+        <v>3.6</v>
       </c>
       <c r="K96" t="n">
-        <v>6.633333333333333</v>
+        <v>2.383333333333333</v>
       </c>
       <c r="L96" t="n">
-        <v>7.983333333333333</v>
+        <v>3.6</v>
       </c>
       <c r="M96" t="n">
         <v>0.3333333333333333</v>
@@ -4673,37 +4685,37 @@
         <v>95</v>
       </c>
       <c r="B97" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C97" t="n">
-        <v>35.8691630924626</v>
+        <v>14.512163776104</v>
       </c>
       <c r="D97" t="n">
-        <v>6.80594557114049</v>
+        <v>29.3929978248616</v>
       </c>
       <c r="E97" t="n">
-        <v>2203.217666666667</v>
+        <v>2476.6573</v>
       </c>
       <c r="F97" t="n">
-        <v>5.638176666666666</v>
+        <v>6.5043975</v>
       </c>
       <c r="G97" t="n">
-        <v>6.633333333333333</v>
+        <v>2.383333333333333</v>
       </c>
       <c r="H97" t="n">
-        <v>7.983333333333333</v>
+        <v>3.6</v>
       </c>
       <c r="I97" t="n">
-        <v>6.633333333333333</v>
+        <v>2.383333333333333</v>
       </c>
       <c r="J97" t="n">
-        <v>7.983333333333333</v>
+        <v>3.6</v>
       </c>
       <c r="K97" t="n">
-        <v>6.633333333333333</v>
+        <v>2.383333333333333</v>
       </c>
       <c r="L97" t="n">
-        <v>7.983333333333333</v>
+        <v>3.6</v>
       </c>
       <c r="M97" t="n">
         <v>0.3333333333333333</v>
@@ -4717,37 +4729,37 @@
         <v>96</v>
       </c>
       <c r="B98" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C98" t="n">
-        <v>35.8691630924626</v>
+        <v>7.25597388908157</v>
       </c>
       <c r="D98" t="n">
-        <v>6.80594557114049</v>
+        <v>-33.7475199378438</v>
       </c>
       <c r="E98" t="n">
-        <v>2203.217666666667</v>
+        <v>2004.6885</v>
       </c>
       <c r="F98" t="n">
-        <v>5.638176666666666</v>
+        <v>6.13507</v>
       </c>
       <c r="G98" t="n">
-        <v>6.633333333333333</v>
+        <v>4.283333333333333</v>
       </c>
       <c r="H98" t="n">
-        <v>7.983333333333333</v>
+        <v>5.716666666666667</v>
       </c>
       <c r="I98" t="n">
-        <v>6.633333333333333</v>
+        <v>4.283333333333333</v>
       </c>
       <c r="J98" t="n">
-        <v>7.983333333333333</v>
+        <v>5.716666666666667</v>
       </c>
       <c r="K98" t="n">
-        <v>6.633333333333333</v>
+        <v>4.283333333333333</v>
       </c>
       <c r="L98" t="n">
-        <v>7.983333333333333</v>
+        <v>5.716666666666667</v>
       </c>
       <c r="M98" t="n">
         <v>0.3333333333333333</v>
@@ -4761,37 +4773,37 @@
         <v>97</v>
       </c>
       <c r="B99" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C99" t="n">
-        <v>29.2918813421379</v>
+        <v>7.25597388908157</v>
       </c>
       <c r="D99" t="n">
-        <v>-11.2363981231824</v>
+        <v>-33.7475199378438</v>
       </c>
       <c r="E99" t="n">
-        <v>2933.964</v>
+        <v>2004.6885</v>
       </c>
       <c r="F99" t="n">
-        <v>9.727729999999999</v>
+        <v>6.13507</v>
       </c>
       <c r="G99" t="n">
-        <v>6.300000000000001</v>
+        <v>4.283333333333333</v>
       </c>
       <c r="H99" t="n">
-        <v>7.383333333333333</v>
+        <v>5.716666666666667</v>
       </c>
       <c r="I99" t="n">
-        <v>6.300000000000001</v>
+        <v>4.283333333333333</v>
       </c>
       <c r="J99" t="n">
-        <v>7.383333333333333</v>
+        <v>5.716666666666667</v>
       </c>
       <c r="K99" t="n">
-        <v>6.300000000000001</v>
+        <v>4.283333333333333</v>
       </c>
       <c r="L99" t="n">
-        <v>7.383333333333333</v>
+        <v>5.716666666666667</v>
       </c>
       <c r="M99" t="n">
         <v>0.3333333333333333</v>
@@ -4805,37 +4817,37 @@
         <v>98</v>
       </c>
       <c r="B100" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C100" t="n">
-        <v>-32.4103858046121</v>
+        <v>7.25597388908157</v>
       </c>
       <c r="D100" t="n">
-        <v>-2.65068011202597</v>
+        <v>-33.7475199378438</v>
       </c>
       <c r="E100" t="n">
-        <v>2935.7956</v>
+        <v>2004.6885</v>
       </c>
       <c r="F100" t="n">
-        <v>7.748356666666667</v>
+        <v>6.13507</v>
       </c>
       <c r="G100" t="n">
-        <v>3.25</v>
+        <v>4.283333333333333</v>
       </c>
       <c r="H100" t="n">
-        <v>4.65</v>
+        <v>5.716666666666667</v>
       </c>
       <c r="I100" t="n">
-        <v>3.25</v>
+        <v>4.283333333333333</v>
       </c>
       <c r="J100" t="n">
-        <v>4.65</v>
+        <v>5.716666666666667</v>
       </c>
       <c r="K100" t="n">
-        <v>3.25</v>
+        <v>4.283333333333333</v>
       </c>
       <c r="L100" t="n">
-        <v>4.65</v>
+        <v>5.716666666666667</v>
       </c>
       <c r="M100" t="n">
         <v>0.3333333333333333</v>
@@ -4849,37 +4861,37 @@
         <v>99</v>
       </c>
       <c r="B101" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C101" t="n">
-        <v>-32.4103858046121</v>
+        <v>-14.3803349502555</v>
       </c>
       <c r="D101" t="n">
-        <v>-2.65068011202597</v>
+        <v>-0.886084812651717</v>
       </c>
       <c r="E101" t="n">
-        <v>2935.7956</v>
+        <v>2934.7648</v>
       </c>
       <c r="F101" t="n">
-        <v>7.748356666666667</v>
+        <v>8.376146666666667</v>
       </c>
       <c r="G101" t="n">
-        <v>3.25</v>
+        <v>11.18333333333333</v>
       </c>
       <c r="H101" t="n">
-        <v>4.65</v>
+        <v>12.01666666666667</v>
       </c>
       <c r="I101" t="n">
-        <v>3.25</v>
+        <v>11.18333333333333</v>
       </c>
       <c r="J101" t="n">
-        <v>4.65</v>
+        <v>12.01666666666667</v>
       </c>
       <c r="K101" t="n">
-        <v>3.25</v>
+        <v>11.18333333333333</v>
       </c>
       <c r="L101" t="n">
-        <v>4.65</v>
+        <v>12.01666666666667</v>
       </c>
       <c r="M101" t="n">
         <v>0.3333333333333333</v>
@@ -4893,37 +4905,37 @@
         <v>100</v>
       </c>
       <c r="B102" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C102" t="n">
-        <v>-32.4103858046121</v>
+        <v>-14.3803349502555</v>
       </c>
       <c r="D102" t="n">
-        <v>-2.65068011202597</v>
+        <v>-0.886084812651717</v>
       </c>
       <c r="E102" t="n">
-        <v>2935.7956</v>
+        <v>2934.7648</v>
       </c>
       <c r="F102" t="n">
-        <v>7.748356666666667</v>
+        <v>8.376146666666667</v>
       </c>
       <c r="G102" t="n">
-        <v>3.25</v>
+        <v>11.18333333333333</v>
       </c>
       <c r="H102" t="n">
-        <v>4.65</v>
+        <v>12.01666666666667</v>
       </c>
       <c r="I102" t="n">
-        <v>3.25</v>
+        <v>11.18333333333333</v>
       </c>
       <c r="J102" t="n">
-        <v>4.65</v>
+        <v>12.01666666666667</v>
       </c>
       <c r="K102" t="n">
-        <v>3.25</v>
+        <v>11.18333333333333</v>
       </c>
       <c r="L102" t="n">
-        <v>4.65</v>
+        <v>12.01666666666667</v>
       </c>
       <c r="M102" t="n">
         <v>0.3333333333333333</v>
@@ -4937,37 +4949,37 @@
         <v>101</v>
       </c>
       <c r="B103" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C103" t="n">
-        <v>14.512163776104</v>
+        <v>-14.3803349502555</v>
       </c>
       <c r="D103" t="n">
-        <v>29.3929978248616</v>
+        <v>-0.886084812651717</v>
       </c>
       <c r="E103" t="n">
-        <v>2476.6573</v>
+        <v>2934.7648</v>
       </c>
       <c r="F103" t="n">
-        <v>6.5043975</v>
+        <v>8.376146666666667</v>
       </c>
       <c r="G103" t="n">
-        <v>2.383333333333333</v>
+        <v>11.18333333333333</v>
       </c>
       <c r="H103" t="n">
-        <v>3.6</v>
+        <v>12.01666666666667</v>
       </c>
       <c r="I103" t="n">
-        <v>2.383333333333333</v>
+        <v>11.18333333333333</v>
       </c>
       <c r="J103" t="n">
-        <v>3.6</v>
+        <v>12.01666666666667</v>
       </c>
       <c r="K103" t="n">
-        <v>2.383333333333333</v>
+        <v>11.18333333333333</v>
       </c>
       <c r="L103" t="n">
-        <v>3.6</v>
+        <v>12.01666666666667</v>
       </c>
       <c r="M103" t="n">
         <v>0.3333333333333333</v>
@@ -4981,37 +4993,37 @@
         <v>102</v>
       </c>
       <c r="B104" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C104" t="n">
-        <v>14.512163776104</v>
+        <v>-18.8423929163792</v>
       </c>
       <c r="D104" t="n">
-        <v>29.3929978248616</v>
+        <v>25.2549085872536</v>
       </c>
       <c r="E104" t="n">
-        <v>2476.6573</v>
+        <v>2897.663333333333</v>
       </c>
       <c r="F104" t="n">
-        <v>6.5043975</v>
+        <v>7.92595</v>
       </c>
       <c r="G104" t="n">
-        <v>2.383333333333333</v>
+        <v>7.866666666666667</v>
       </c>
       <c r="H104" t="n">
-        <v>3.6</v>
+        <v>9.233333333333334</v>
       </c>
       <c r="I104" t="n">
-        <v>2.383333333333333</v>
+        <v>7.866666666666667</v>
       </c>
       <c r="J104" t="n">
-        <v>3.6</v>
+        <v>9.233333333333334</v>
       </c>
       <c r="K104" t="n">
-        <v>2.383333333333333</v>
+        <v>7.866666666666667</v>
       </c>
       <c r="L104" t="n">
-        <v>3.6</v>
+        <v>9.233333333333334</v>
       </c>
       <c r="M104" t="n">
         <v>0.3333333333333333</v>
@@ -5025,37 +5037,37 @@
         <v>103</v>
       </c>
       <c r="B105" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C105" t="n">
-        <v>14.512163776104</v>
+        <v>-18.8423929163792</v>
       </c>
       <c r="D105" t="n">
-        <v>29.3929978248616</v>
+        <v>25.2549085872536</v>
       </c>
       <c r="E105" t="n">
-        <v>2476.6573</v>
+        <v>2897.663333333333</v>
       </c>
       <c r="F105" t="n">
-        <v>6.5043975</v>
+        <v>7.92595</v>
       </c>
       <c r="G105" t="n">
-        <v>2.383333333333333</v>
+        <v>7.866666666666667</v>
       </c>
       <c r="H105" t="n">
-        <v>3.6</v>
+        <v>9.233333333333334</v>
       </c>
       <c r="I105" t="n">
-        <v>2.383333333333333</v>
+        <v>7.866666666666667</v>
       </c>
       <c r="J105" t="n">
-        <v>3.6</v>
+        <v>9.233333333333334</v>
       </c>
       <c r="K105" t="n">
-        <v>2.383333333333333</v>
+        <v>7.866666666666667</v>
       </c>
       <c r="L105" t="n">
-        <v>3.6</v>
+        <v>9.233333333333334</v>
       </c>
       <c r="M105" t="n">
         <v>0.3333333333333333</v>
@@ -5069,37 +5081,37 @@
         <v>104</v>
       </c>
       <c r="B106" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C106" t="n">
-        <v>14.512163776104</v>
+        <v>-18.8423929163792</v>
       </c>
       <c r="D106" t="n">
-        <v>29.3929978248616</v>
+        <v>25.2549085872536</v>
       </c>
       <c r="E106" t="n">
-        <v>2476.6573</v>
+        <v>2897.663333333333</v>
       </c>
       <c r="F106" t="n">
-        <v>6.5043975</v>
+        <v>7.92595</v>
       </c>
       <c r="G106" t="n">
-        <v>2.383333333333333</v>
+        <v>7.866666666666667</v>
       </c>
       <c r="H106" t="n">
-        <v>3.6</v>
+        <v>9.233333333333334</v>
       </c>
       <c r="I106" t="n">
-        <v>2.383333333333333</v>
+        <v>7.866666666666667</v>
       </c>
       <c r="J106" t="n">
-        <v>3.6</v>
+        <v>9.233333333333334</v>
       </c>
       <c r="K106" t="n">
-        <v>2.383333333333333</v>
+        <v>7.866666666666667</v>
       </c>
       <c r="L106" t="n">
-        <v>3.6</v>
+        <v>9.233333333333334</v>
       </c>
       <c r="M106" t="n">
         <v>0.3333333333333333</v>
@@ -5113,37 +5125,37 @@
         <v>105</v>
       </c>
       <c r="B107" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C107" t="n">
-        <v>7.25597388908157</v>
+        <v>29.553914624618</v>
       </c>
       <c r="D107" t="n">
-        <v>-33.7475199378438</v>
+        <v>-15.7832896589862</v>
       </c>
       <c r="E107" t="n">
-        <v>2004.6885</v>
+        <v>2949.9224</v>
       </c>
       <c r="F107" t="n">
-        <v>6.13507</v>
+        <v>7.129093333333334</v>
       </c>
       <c r="G107" t="n">
-        <v>4.283333333333333</v>
+        <v>6.15</v>
       </c>
       <c r="H107" t="n">
-        <v>5.716666666666667</v>
+        <v>7.083333333333334</v>
       </c>
       <c r="I107" t="n">
-        <v>4.283333333333333</v>
+        <v>6.15</v>
       </c>
       <c r="J107" t="n">
-        <v>5.716666666666667</v>
+        <v>7.083333333333334</v>
       </c>
       <c r="K107" t="n">
-        <v>4.283333333333333</v>
+        <v>6.15</v>
       </c>
       <c r="L107" t="n">
-        <v>5.716666666666667</v>
+        <v>7.083333333333334</v>
       </c>
       <c r="M107" t="n">
         <v>0.3333333333333333</v>
@@ -5157,37 +5169,37 @@
         <v>106</v>
       </c>
       <c r="B108" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C108" t="n">
-        <v>7.25597388908157</v>
+        <v>29.553914624618</v>
       </c>
       <c r="D108" t="n">
-        <v>-33.7475199378438</v>
+        <v>-15.7832896589862</v>
       </c>
       <c r="E108" t="n">
-        <v>2004.6885</v>
+        <v>2949.9224</v>
       </c>
       <c r="F108" t="n">
-        <v>6.13507</v>
+        <v>7.129093333333334</v>
       </c>
       <c r="G108" t="n">
-        <v>4.283333333333333</v>
+        <v>6.15</v>
       </c>
       <c r="H108" t="n">
-        <v>5.716666666666667</v>
+        <v>7.083333333333334</v>
       </c>
       <c r="I108" t="n">
-        <v>4.283333333333333</v>
+        <v>6.15</v>
       </c>
       <c r="J108" t="n">
-        <v>5.716666666666667</v>
+        <v>7.083333333333334</v>
       </c>
       <c r="K108" t="n">
-        <v>4.283333333333333</v>
+        <v>6.15</v>
       </c>
       <c r="L108" t="n">
-        <v>5.716666666666667</v>
+        <v>7.083333333333334</v>
       </c>
       <c r="M108" t="n">
         <v>0.3333333333333333</v>
@@ -5201,37 +5213,37 @@
         <v>107</v>
       </c>
       <c r="B109" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C109" t="n">
-        <v>7.25597388908157</v>
+        <v>29.553914624618</v>
       </c>
       <c r="D109" t="n">
-        <v>-33.7475199378438</v>
+        <v>-15.7832896589862</v>
       </c>
       <c r="E109" t="n">
-        <v>2004.6885</v>
+        <v>2949.9224</v>
       </c>
       <c r="F109" t="n">
-        <v>6.13507</v>
+        <v>7.129093333333334</v>
       </c>
       <c r="G109" t="n">
-        <v>4.283333333333333</v>
+        <v>6.15</v>
       </c>
       <c r="H109" t="n">
-        <v>5.716666666666667</v>
+        <v>7.083333333333334</v>
       </c>
       <c r="I109" t="n">
-        <v>4.283333333333333</v>
+        <v>6.15</v>
       </c>
       <c r="J109" t="n">
-        <v>5.716666666666667</v>
+        <v>7.083333333333334</v>
       </c>
       <c r="K109" t="n">
-        <v>4.283333333333333</v>
+        <v>6.15</v>
       </c>
       <c r="L109" t="n">
-        <v>5.716666666666667</v>
+        <v>7.083333333333334</v>
       </c>
       <c r="M109" t="n">
         <v>0.3333333333333333</v>
@@ -5245,37 +5257,37 @@
         <v>108</v>
       </c>
       <c r="B110" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C110" t="n">
-        <v>-14.3803349502555</v>
+        <v>-13.5633988058324</v>
       </c>
       <c r="D110" t="n">
-        <v>-0.886084812651717</v>
+        <v>35.7117550694904</v>
       </c>
       <c r="E110" t="n">
-        <v>2934.7648</v>
+        <v>2184.195566666667</v>
       </c>
       <c r="F110" t="n">
-        <v>8.376146666666667</v>
+        <v>4.921436666666667</v>
       </c>
       <c r="G110" t="n">
-        <v>11.18333333333333</v>
+        <v>7.949999999999999</v>
       </c>
       <c r="H110" t="n">
-        <v>12.01666666666667</v>
+        <v>9.383333333333333</v>
       </c>
       <c r="I110" t="n">
-        <v>11.18333333333333</v>
+        <v>7.949999999999999</v>
       </c>
       <c r="J110" t="n">
-        <v>12.01666666666667</v>
+        <v>9.383333333333333</v>
       </c>
       <c r="K110" t="n">
-        <v>11.18333333333333</v>
+        <v>7.949999999999999</v>
       </c>
       <c r="L110" t="n">
-        <v>12.01666666666667</v>
+        <v>9.383333333333333</v>
       </c>
       <c r="M110" t="n">
         <v>0.3333333333333333</v>
@@ -5289,37 +5301,37 @@
         <v>109</v>
       </c>
       <c r="B111" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C111" t="n">
-        <v>-14.3803349502555</v>
+        <v>-13.5633988058324</v>
       </c>
       <c r="D111" t="n">
-        <v>-0.886084812651717</v>
+        <v>35.7117550694904</v>
       </c>
       <c r="E111" t="n">
-        <v>2934.7648</v>
+        <v>2184.195566666667</v>
       </c>
       <c r="F111" t="n">
-        <v>8.376146666666667</v>
+        <v>4.921436666666667</v>
       </c>
       <c r="G111" t="n">
-        <v>11.18333333333333</v>
+        <v>7.949999999999999</v>
       </c>
       <c r="H111" t="n">
-        <v>12.01666666666667</v>
+        <v>9.383333333333333</v>
       </c>
       <c r="I111" t="n">
-        <v>11.18333333333333</v>
+        <v>7.949999999999999</v>
       </c>
       <c r="J111" t="n">
-        <v>12.01666666666667</v>
+        <v>9.383333333333333</v>
       </c>
       <c r="K111" t="n">
-        <v>11.18333333333333</v>
+        <v>7.949999999999999</v>
       </c>
       <c r="L111" t="n">
-        <v>12.01666666666667</v>
+        <v>9.383333333333333</v>
       </c>
       <c r="M111" t="n">
         <v>0.3333333333333333</v>
@@ -5333,37 +5345,37 @@
         <v>110</v>
       </c>
       <c r="B112" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C112" t="n">
-        <v>-14.3803349502555</v>
+        <v>-13.5633988058324</v>
       </c>
       <c r="D112" t="n">
-        <v>-0.886084812651717</v>
+        <v>35.7117550694904</v>
       </c>
       <c r="E112" t="n">
-        <v>2934.7648</v>
+        <v>2184.195566666667</v>
       </c>
       <c r="F112" t="n">
-        <v>8.376146666666667</v>
+        <v>4.921436666666667</v>
       </c>
       <c r="G112" t="n">
-        <v>11.18333333333333</v>
+        <v>7.949999999999999</v>
       </c>
       <c r="H112" t="n">
-        <v>12.01666666666667</v>
+        <v>9.383333333333333</v>
       </c>
       <c r="I112" t="n">
-        <v>11.18333333333333</v>
+        <v>7.949999999999999</v>
       </c>
       <c r="J112" t="n">
-        <v>12.01666666666667</v>
+        <v>9.383333333333333</v>
       </c>
       <c r="K112" t="n">
-        <v>11.18333333333333</v>
+        <v>7.949999999999999</v>
       </c>
       <c r="L112" t="n">
-        <v>12.01666666666667</v>
+        <v>9.383333333333333</v>
       </c>
       <c r="M112" t="n">
         <v>0.3333333333333333</v>
@@ -5377,37 +5389,37 @@
         <v>111</v>
       </c>
       <c r="B113" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C113" t="n">
-        <v>-18.8423929163792</v>
+        <v>10.9979131123698</v>
       </c>
       <c r="D113" t="n">
-        <v>25.2549085872536</v>
+        <v>-14.3764159181384</v>
       </c>
       <c r="E113" t="n">
-        <v>2897.663333333333</v>
+        <v>2791.0139</v>
       </c>
       <c r="F113" t="n">
-        <v>7.92595</v>
+        <v>8.679600000000001</v>
       </c>
       <c r="G113" t="n">
-        <v>7.866666666666667</v>
+        <v>1.166666666666666</v>
       </c>
       <c r="H113" t="n">
-        <v>9.233333333333334</v>
+        <v>2.550000000000001</v>
       </c>
       <c r="I113" t="n">
-        <v>7.866666666666667</v>
+        <v>1.166666666666666</v>
       </c>
       <c r="J113" t="n">
-        <v>9.233333333333334</v>
+        <v>2.550000000000001</v>
       </c>
       <c r="K113" t="n">
-        <v>7.866666666666667</v>
+        <v>1.166666666666666</v>
       </c>
       <c r="L113" t="n">
-        <v>9.233333333333334</v>
+        <v>2.550000000000001</v>
       </c>
       <c r="M113" t="n">
         <v>0.3333333333333333</v>
@@ -5421,37 +5433,37 @@
         <v>112</v>
       </c>
       <c r="B114" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C114" t="n">
-        <v>-18.8423929163792</v>
+        <v>15.2856210779678</v>
       </c>
       <c r="D114" t="n">
-        <v>25.2549085872536</v>
+        <v>-28.0053274336459</v>
       </c>
       <c r="E114" t="n">
-        <v>2897.663333333333</v>
+        <v>2860.4382</v>
       </c>
       <c r="F114" t="n">
-        <v>7.92595</v>
+        <v>8.924939999999999</v>
       </c>
       <c r="G114" t="n">
-        <v>7.866666666666667</v>
+        <v>10.86666666666667</v>
       </c>
       <c r="H114" t="n">
-        <v>9.233333333333334</v>
+        <v>12.26666666666667</v>
       </c>
       <c r="I114" t="n">
-        <v>7.866666666666667</v>
+        <v>10.86666666666667</v>
       </c>
       <c r="J114" t="n">
-        <v>9.233333333333334</v>
+        <v>12.26666666666667</v>
       </c>
       <c r="K114" t="n">
-        <v>7.866666666666667</v>
+        <v>10.86666666666667</v>
       </c>
       <c r="L114" t="n">
-        <v>9.233333333333334</v>
+        <v>12.26666666666667</v>
       </c>
       <c r="M114" t="n">
         <v>0.3333333333333333</v>
@@ -5465,37 +5477,37 @@
         <v>113</v>
       </c>
       <c r="B115" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C115" t="n">
-        <v>-18.8423929163792</v>
+        <v>-6.89120148830592</v>
       </c>
       <c r="D115" t="n">
-        <v>25.2549085872536</v>
+        <v>36.8225598526382</v>
       </c>
       <c r="E115" t="n">
-        <v>2897.663333333333</v>
+        <v>2471.662466666667</v>
       </c>
       <c r="F115" t="n">
-        <v>7.92595</v>
+        <v>5.810966666666666</v>
       </c>
       <c r="G115" t="n">
-        <v>7.866666666666667</v>
+        <v>10.51666666666667</v>
       </c>
       <c r="H115" t="n">
-        <v>9.233333333333334</v>
+        <v>11.8</v>
       </c>
       <c r="I115" t="n">
-        <v>7.866666666666667</v>
+        <v>10.51666666666667</v>
       </c>
       <c r="J115" t="n">
-        <v>9.233333333333334</v>
+        <v>11.8</v>
       </c>
       <c r="K115" t="n">
-        <v>7.866666666666667</v>
+        <v>10.51666666666667</v>
       </c>
       <c r="L115" t="n">
-        <v>9.233333333333334</v>
+        <v>11.8</v>
       </c>
       <c r="M115" t="n">
         <v>0.3333333333333333</v>
@@ -5509,37 +5521,37 @@
         <v>114</v>
       </c>
       <c r="B116" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C116" t="n">
-        <v>29.553914624618</v>
+        <v>-6.89120148830592</v>
       </c>
       <c r="D116" t="n">
-        <v>-15.7832896589862</v>
+        <v>36.8225598526382</v>
       </c>
       <c r="E116" t="n">
-        <v>2949.9224</v>
+        <v>2471.662466666667</v>
       </c>
       <c r="F116" t="n">
-        <v>7.129093333333334</v>
+        <v>5.810966666666666</v>
       </c>
       <c r="G116" t="n">
-        <v>6.15</v>
+        <v>10.51666666666667</v>
       </c>
       <c r="H116" t="n">
-        <v>7.083333333333334</v>
+        <v>11.8</v>
       </c>
       <c r="I116" t="n">
-        <v>6.15</v>
+        <v>10.51666666666667</v>
       </c>
       <c r="J116" t="n">
-        <v>7.083333333333334</v>
+        <v>11.8</v>
       </c>
       <c r="K116" t="n">
-        <v>6.15</v>
+        <v>10.51666666666667</v>
       </c>
       <c r="L116" t="n">
-        <v>7.083333333333334</v>
+        <v>11.8</v>
       </c>
       <c r="M116" t="n">
         <v>0.3333333333333333</v>
@@ -5553,37 +5565,37 @@
         <v>115</v>
       </c>
       <c r="B117" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C117" t="n">
-        <v>29.553914624618</v>
+        <v>-6.89120148830592</v>
       </c>
       <c r="D117" t="n">
-        <v>-15.7832896589862</v>
+        <v>36.8225598526382</v>
       </c>
       <c r="E117" t="n">
-        <v>2949.9224</v>
+        <v>2471.662466666667</v>
       </c>
       <c r="F117" t="n">
-        <v>7.129093333333334</v>
+        <v>5.810966666666666</v>
       </c>
       <c r="G117" t="n">
-        <v>6.15</v>
+        <v>10.51666666666667</v>
       </c>
       <c r="H117" t="n">
-        <v>7.083333333333334</v>
+        <v>11.8</v>
       </c>
       <c r="I117" t="n">
-        <v>6.15</v>
+        <v>10.51666666666667</v>
       </c>
       <c r="J117" t="n">
-        <v>7.083333333333334</v>
+        <v>11.8</v>
       </c>
       <c r="K117" t="n">
-        <v>6.15</v>
+        <v>10.51666666666667</v>
       </c>
       <c r="L117" t="n">
-        <v>7.083333333333334</v>
+        <v>11.8</v>
       </c>
       <c r="M117" t="n">
         <v>0.3333333333333333</v>
@@ -5597,37 +5609,37 @@
         <v>116</v>
       </c>
       <c r="B118" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C118" t="n">
-        <v>29.553914624618</v>
+        <v>-10.2808334321244</v>
       </c>
       <c r="D118" t="n">
-        <v>-15.7832896589862</v>
+        <v>29.5869615259404</v>
       </c>
       <c r="E118" t="n">
-        <v>2949.9224</v>
+        <v>2288.8859</v>
       </c>
       <c r="F118" t="n">
-        <v>7.129093333333334</v>
+        <v>6.06402</v>
       </c>
       <c r="G118" t="n">
-        <v>6.15</v>
+        <v>7.766666666666667</v>
       </c>
       <c r="H118" t="n">
-        <v>7.083333333333334</v>
+        <v>9.149999999999999</v>
       </c>
       <c r="I118" t="n">
-        <v>6.15</v>
+        <v>7.766666666666667</v>
       </c>
       <c r="J118" t="n">
-        <v>7.083333333333334</v>
+        <v>9.149999999999999</v>
       </c>
       <c r="K118" t="n">
-        <v>6.15</v>
+        <v>7.766666666666667</v>
       </c>
       <c r="L118" t="n">
-        <v>7.083333333333334</v>
+        <v>9.149999999999999</v>
       </c>
       <c r="M118" t="n">
         <v>0.3333333333333333</v>
@@ -5641,37 +5653,37 @@
         <v>117</v>
       </c>
       <c r="B119" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C119" t="n">
-        <v>-13.5633988058324</v>
+        <v>-12.9249626484284</v>
       </c>
       <c r="D119" t="n">
-        <v>35.7117550694904</v>
+        <v>-33.6033227158668</v>
       </c>
       <c r="E119" t="n">
-        <v>2184.195566666667</v>
+        <v>2837.3255</v>
       </c>
       <c r="F119" t="n">
-        <v>4.921436666666667</v>
+        <v>8.182865</v>
       </c>
       <c r="G119" t="n">
-        <v>7.949999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="H119" t="n">
-        <v>9.383333333333333</v>
+        <v>4.583333333333334</v>
       </c>
       <c r="I119" t="n">
-        <v>7.949999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="J119" t="n">
-        <v>9.383333333333333</v>
+        <v>4.583333333333334</v>
       </c>
       <c r="K119" t="n">
-        <v>7.949999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="L119" t="n">
-        <v>9.383333333333333</v>
+        <v>4.583333333333334</v>
       </c>
       <c r="M119" t="n">
         <v>0.3333333333333333</v>
@@ -5685,37 +5697,37 @@
         <v>118</v>
       </c>
       <c r="B120" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C120" t="n">
-        <v>-13.5633988058324</v>
+        <v>-12.9249626484284</v>
       </c>
       <c r="D120" t="n">
-        <v>35.7117550694904</v>
+        <v>-33.6033227158668</v>
       </c>
       <c r="E120" t="n">
-        <v>2184.195566666667</v>
+        <v>2837.3255</v>
       </c>
       <c r="F120" t="n">
-        <v>4.921436666666667</v>
+        <v>8.182865</v>
       </c>
       <c r="G120" t="n">
-        <v>7.949999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="H120" t="n">
-        <v>9.383333333333333</v>
+        <v>4.583333333333334</v>
       </c>
       <c r="I120" t="n">
-        <v>7.949999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="J120" t="n">
-        <v>9.383333333333333</v>
+        <v>4.583333333333334</v>
       </c>
       <c r="K120" t="n">
-        <v>7.949999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="L120" t="n">
-        <v>9.383333333333333</v>
+        <v>4.583333333333334</v>
       </c>
       <c r="M120" t="n">
         <v>0.3333333333333333</v>
@@ -5729,37 +5741,37 @@
         <v>119</v>
       </c>
       <c r="B121" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C121" t="n">
-        <v>-13.5633988058324</v>
+        <v>-21.4142706428761</v>
       </c>
       <c r="D121" t="n">
-        <v>35.7117550694904</v>
+        <v>-0.0177783553764303</v>
       </c>
       <c r="E121" t="n">
-        <v>2184.195566666667</v>
+        <v>1533.5344</v>
       </c>
       <c r="F121" t="n">
-        <v>4.921436666666667</v>
+        <v>5.0218</v>
       </c>
       <c r="G121" t="n">
-        <v>7.949999999999999</v>
+        <v>11.31666666666667</v>
       </c>
       <c r="H121" t="n">
-        <v>9.383333333333333</v>
+        <v>12.75</v>
       </c>
       <c r="I121" t="n">
-        <v>7.949999999999999</v>
+        <v>11.31666666666667</v>
       </c>
       <c r="J121" t="n">
-        <v>9.383333333333333</v>
+        <v>12.75</v>
       </c>
       <c r="K121" t="n">
-        <v>7.949999999999999</v>
+        <v>11.31666666666667</v>
       </c>
       <c r="L121" t="n">
-        <v>9.383333333333333</v>
+        <v>12.75</v>
       </c>
       <c r="M121" t="n">
         <v>0.3333333333333333</v>
@@ -5773,37 +5785,37 @@
         <v>120</v>
       </c>
       <c r="B122" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C122" t="n">
-        <v>10.9979131123698</v>
+        <v>-21.4142706428761</v>
       </c>
       <c r="D122" t="n">
-        <v>-14.3764159181384</v>
+        <v>-0.0177783553764303</v>
       </c>
       <c r="E122" t="n">
-        <v>2791.0139</v>
+        <v>1533.5344</v>
       </c>
       <c r="F122" t="n">
-        <v>8.679600000000001</v>
+        <v>5.0218</v>
       </c>
       <c r="G122" t="n">
-        <v>1.166666666666666</v>
+        <v>11.31666666666667</v>
       </c>
       <c r="H122" t="n">
-        <v>2.550000000000001</v>
+        <v>12.75</v>
       </c>
       <c r="I122" t="n">
-        <v>1.166666666666666</v>
+        <v>11.31666666666667</v>
       </c>
       <c r="J122" t="n">
-        <v>2.550000000000001</v>
+        <v>12.75</v>
       </c>
       <c r="K122" t="n">
-        <v>1.166666666666666</v>
+        <v>11.31666666666667</v>
       </c>
       <c r="L122" t="n">
-        <v>2.550000000000001</v>
+        <v>12.75</v>
       </c>
       <c r="M122" t="n">
         <v>0.3333333333333333</v>
@@ -5817,37 +5829,37 @@
         <v>121</v>
       </c>
       <c r="B123" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C123" t="n">
-        <v>15.2856210779678</v>
+        <v>3.34995943599543</v>
       </c>
       <c r="D123" t="n">
-        <v>-28.0053274336459</v>
+        <v>31.3048933804785</v>
       </c>
       <c r="E123" t="n">
-        <v>2860.4382</v>
+        <v>2725.3232</v>
       </c>
       <c r="F123" t="n">
-        <v>8.924939999999999</v>
+        <v>7.50056</v>
       </c>
       <c r="G123" t="n">
-        <v>10.86666666666667</v>
+        <v>11.21666666666667</v>
       </c>
       <c r="H123" t="n">
-        <v>12.26666666666667</v>
+        <v>12.58333333333333</v>
       </c>
       <c r="I123" t="n">
-        <v>10.86666666666667</v>
+        <v>11.21666666666667</v>
       </c>
       <c r="J123" t="n">
-        <v>12.26666666666667</v>
+        <v>12.58333333333333</v>
       </c>
       <c r="K123" t="n">
-        <v>10.86666666666667</v>
+        <v>11.21666666666667</v>
       </c>
       <c r="L123" t="n">
-        <v>12.26666666666667</v>
+        <v>12.58333333333333</v>
       </c>
       <c r="M123" t="n">
         <v>0.3333333333333333</v>
@@ -5861,37 +5873,37 @@
         <v>122</v>
       </c>
       <c r="B124" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C124" t="n">
-        <v>-6.89120148830592</v>
+        <v>-19.079563342021</v>
       </c>
       <c r="D124" t="n">
-        <v>36.8225598526382</v>
+        <v>3.11570859008743</v>
       </c>
       <c r="E124" t="n">
-        <v>2471.662466666667</v>
+        <v>2996.466</v>
       </c>
       <c r="F124" t="n">
-        <v>5.810966666666666</v>
+        <v>7.5462</v>
       </c>
       <c r="G124" t="n">
-        <v>10.51666666666667</v>
+        <v>5.366666666666667</v>
       </c>
       <c r="H124" t="n">
-        <v>11.8</v>
+        <v>6.283333333333333</v>
       </c>
       <c r="I124" t="n">
-        <v>10.51666666666667</v>
+        <v>5.366666666666667</v>
       </c>
       <c r="J124" t="n">
-        <v>11.8</v>
+        <v>6.283333333333333</v>
       </c>
       <c r="K124" t="n">
-        <v>10.51666666666667</v>
+        <v>5.366666666666667</v>
       </c>
       <c r="L124" t="n">
-        <v>11.8</v>
+        <v>6.283333333333333</v>
       </c>
       <c r="M124" t="n">
         <v>0.3333333333333333</v>
@@ -5905,37 +5917,37 @@
         <v>123</v>
       </c>
       <c r="B125" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C125" t="n">
-        <v>-6.89120148830592</v>
+        <v>-14.4202892616212</v>
       </c>
       <c r="D125" t="n">
-        <v>36.8225598526382</v>
+        <v>0.438615616091085</v>
       </c>
       <c r="E125" t="n">
-        <v>2471.662466666667</v>
+        <v>1862.9861</v>
       </c>
       <c r="F125" t="n">
-        <v>5.810966666666666</v>
+        <v>5.46936</v>
       </c>
       <c r="G125" t="n">
-        <v>10.51666666666667</v>
+        <v>5.183333333333334</v>
       </c>
       <c r="H125" t="n">
-        <v>11.8</v>
+        <v>6.166666666666666</v>
       </c>
       <c r="I125" t="n">
-        <v>10.51666666666667</v>
+        <v>5.183333333333334</v>
       </c>
       <c r="J125" t="n">
-        <v>11.8</v>
+        <v>6.166666666666666</v>
       </c>
       <c r="K125" t="n">
-        <v>10.51666666666667</v>
+        <v>5.183333333333334</v>
       </c>
       <c r="L125" t="n">
-        <v>11.8</v>
+        <v>6.166666666666666</v>
       </c>
       <c r="M125" t="n">
         <v>0.3333333333333333</v>
@@ -5949,37 +5961,37 @@
         <v>124</v>
       </c>
       <c r="B126" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C126" t="n">
-        <v>-6.89120148830592</v>
+        <v>-14.4202892616212</v>
       </c>
       <c r="D126" t="n">
-        <v>36.8225598526382</v>
+        <v>0.438615616091085</v>
       </c>
       <c r="E126" t="n">
-        <v>2471.662466666667</v>
+        <v>1862.9861</v>
       </c>
       <c r="F126" t="n">
-        <v>5.810966666666666</v>
+        <v>5.46936</v>
       </c>
       <c r="G126" t="n">
-        <v>10.51666666666667</v>
+        <v>5.183333333333334</v>
       </c>
       <c r="H126" t="n">
-        <v>11.8</v>
+        <v>6.166666666666666</v>
       </c>
       <c r="I126" t="n">
-        <v>10.51666666666667</v>
+        <v>5.183333333333334</v>
       </c>
       <c r="J126" t="n">
-        <v>11.8</v>
+        <v>6.166666666666666</v>
       </c>
       <c r="K126" t="n">
-        <v>10.51666666666667</v>
+        <v>5.183333333333334</v>
       </c>
       <c r="L126" t="n">
-        <v>11.8</v>
+        <v>6.166666666666666</v>
       </c>
       <c r="M126" t="n">
         <v>0.3333333333333333</v>
@@ -5993,37 +6005,37 @@
         <v>125</v>
       </c>
       <c r="B127" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C127" t="n">
-        <v>-10.2808334321244</v>
+        <v>17.8559660659719</v>
       </c>
       <c r="D127" t="n">
-        <v>29.5869615259404</v>
+        <v>-34.5128170174245</v>
       </c>
       <c r="E127" t="n">
-        <v>2288.8859</v>
+        <v>1508.7203</v>
       </c>
       <c r="F127" t="n">
-        <v>6.06402</v>
+        <v>3.92876</v>
       </c>
       <c r="G127" t="n">
-        <v>7.766666666666667</v>
+        <v>6.416666666666666</v>
       </c>
       <c r="H127" t="n">
-        <v>9.149999999999999</v>
+        <v>7.75</v>
       </c>
       <c r="I127" t="n">
-        <v>7.766666666666667</v>
+        <v>6.416666666666666</v>
       </c>
       <c r="J127" t="n">
-        <v>9.149999999999999</v>
+        <v>7.75</v>
       </c>
       <c r="K127" t="n">
-        <v>7.766666666666667</v>
+        <v>6.416666666666666</v>
       </c>
       <c r="L127" t="n">
-        <v>9.149999999999999</v>
+        <v>7.75</v>
       </c>
       <c r="M127" t="n">
         <v>0.3333333333333333</v>
@@ -6037,37 +6049,37 @@
         <v>126</v>
       </c>
       <c r="B128" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C128" t="n">
-        <v>-12.9249626484284</v>
+        <v>17.8559660659719</v>
       </c>
       <c r="D128" t="n">
-        <v>-33.6033227158668</v>
+        <v>-34.5128170174245</v>
       </c>
       <c r="E128" t="n">
-        <v>2837.3255</v>
+        <v>1508.7203</v>
       </c>
       <c r="F128" t="n">
-        <v>8.182865</v>
+        <v>3.92876</v>
       </c>
       <c r="G128" t="n">
-        <v>3.6</v>
+        <v>6.416666666666666</v>
       </c>
       <c r="H128" t="n">
-        <v>4.583333333333334</v>
+        <v>7.75</v>
       </c>
       <c r="I128" t="n">
-        <v>3.6</v>
+        <v>6.416666666666666</v>
       </c>
       <c r="J128" t="n">
-        <v>4.583333333333334</v>
+        <v>7.75</v>
       </c>
       <c r="K128" t="n">
-        <v>3.6</v>
+        <v>6.416666666666666</v>
       </c>
       <c r="L128" t="n">
-        <v>4.583333333333334</v>
+        <v>7.75</v>
       </c>
       <c r="M128" t="n">
         <v>0.3333333333333333</v>
@@ -6081,37 +6093,37 @@
         <v>127</v>
       </c>
       <c r="B129" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C129" t="n">
-        <v>-12.9249626484284</v>
+        <v>6.17248271231953</v>
       </c>
       <c r="D129" t="n">
-        <v>-33.6033227158668</v>
+        <v>-11.9739943806008</v>
       </c>
       <c r="E129" t="n">
-        <v>2837.3255</v>
+        <v>1256.3017</v>
       </c>
       <c r="F129" t="n">
-        <v>8.182865</v>
+        <v>3.94079</v>
       </c>
       <c r="G129" t="n">
-        <v>3.6</v>
+        <v>1.15</v>
       </c>
       <c r="H129" t="n">
-        <v>4.583333333333334</v>
+        <v>2.416666666666666</v>
       </c>
       <c r="I129" t="n">
-        <v>3.6</v>
+        <v>1.15</v>
       </c>
       <c r="J129" t="n">
-        <v>4.583333333333334</v>
+        <v>2.416666666666666</v>
       </c>
       <c r="K129" t="n">
-        <v>3.6</v>
+        <v>1.15</v>
       </c>
       <c r="L129" t="n">
-        <v>4.583333333333334</v>
+        <v>2.416666666666666</v>
       </c>
       <c r="M129" t="n">
         <v>0.3333333333333333</v>
@@ -6125,37 +6137,37 @@
         <v>128</v>
       </c>
       <c r="B130" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C130" t="n">
-        <v>-21.4142706428761</v>
+        <v>-8.90340842896458</v>
       </c>
       <c r="D130" t="n">
-        <v>-0.0177783553764303</v>
+        <v>-33.0969833073601</v>
       </c>
       <c r="E130" t="n">
-        <v>1533.5344</v>
+        <v>1968.2668</v>
       </c>
       <c r="F130" t="n">
-        <v>5.0218</v>
+        <v>5.09682</v>
       </c>
       <c r="G130" t="n">
-        <v>11.31666666666667</v>
+        <v>10.93333333333333</v>
       </c>
       <c r="H130" t="n">
-        <v>12.75</v>
+        <v>12.28333333333333</v>
       </c>
       <c r="I130" t="n">
-        <v>11.31666666666667</v>
+        <v>10.93333333333333</v>
       </c>
       <c r="J130" t="n">
-        <v>12.75</v>
+        <v>12.28333333333333</v>
       </c>
       <c r="K130" t="n">
-        <v>11.31666666666667</v>
+        <v>10.93333333333333</v>
       </c>
       <c r="L130" t="n">
-        <v>12.75</v>
+        <v>12.28333333333333</v>
       </c>
       <c r="M130" t="n">
         <v>0.3333333333333333</v>
@@ -6169,37 +6181,37 @@
         <v>129</v>
       </c>
       <c r="B131" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="C131" t="n">
-        <v>-21.4142706428761</v>
+        <v>0.735897737284067</v>
       </c>
       <c r="D131" t="n">
-        <v>-0.0177783553764303</v>
+        <v>-11.817830191293</v>
       </c>
       <c r="E131" t="n">
-        <v>1533.5344</v>
+        <v>1882.391</v>
       </c>
       <c r="F131" t="n">
-        <v>5.0218</v>
+        <v>4.7241</v>
       </c>
       <c r="G131" t="n">
-        <v>11.31666666666667</v>
+        <v>11.9</v>
       </c>
       <c r="H131" t="n">
-        <v>12.75</v>
+        <v>12.91666666666667</v>
       </c>
       <c r="I131" t="n">
-        <v>11.31666666666667</v>
+        <v>11.9</v>
       </c>
       <c r="J131" t="n">
-        <v>12.75</v>
+        <v>12.91666666666667</v>
       </c>
       <c r="K131" t="n">
-        <v>11.31666666666667</v>
+        <v>11.9</v>
       </c>
       <c r="L131" t="n">
-        <v>12.75</v>
+        <v>12.91666666666667</v>
       </c>
       <c r="M131" t="n">
         <v>0.3333333333333333</v>
@@ -6213,37 +6225,37 @@
         <v>130</v>
       </c>
       <c r="B132" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C132" t="n">
-        <v>3.34995943599543</v>
+        <v>6.48665021130649</v>
       </c>
       <c r="D132" t="n">
-        <v>31.3048933804785</v>
+        <v>-18.7369565714111</v>
       </c>
       <c r="E132" t="n">
-        <v>2725.3232</v>
+        <v>2315.13</v>
       </c>
       <c r="F132" t="n">
-        <v>7.50056</v>
+        <v>7.36652</v>
       </c>
       <c r="G132" t="n">
-        <v>11.21666666666667</v>
+        <v>1.583333333333334</v>
       </c>
       <c r="H132" t="n">
-        <v>12.58333333333333</v>
+        <v>2.75</v>
       </c>
       <c r="I132" t="n">
-        <v>11.21666666666667</v>
+        <v>1.583333333333334</v>
       </c>
       <c r="J132" t="n">
-        <v>12.58333333333333</v>
+        <v>2.75</v>
       </c>
       <c r="K132" t="n">
-        <v>11.21666666666667</v>
+        <v>1.583333333333334</v>
       </c>
       <c r="L132" t="n">
-        <v>12.58333333333333</v>
+        <v>2.75</v>
       </c>
       <c r="M132" t="n">
         <v>0.3333333333333333</v>
@@ -6257,37 +6269,37 @@
         <v>131</v>
       </c>
       <c r="B133" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="C133" t="n">
-        <v>-19.079563342021</v>
+        <v>-16.1633724807616</v>
       </c>
       <c r="D133" t="n">
-        <v>3.11570859008743</v>
+        <v>17.956024307724</v>
       </c>
       <c r="E133" t="n">
-        <v>2996.466</v>
+        <v>506.3405000000001</v>
       </c>
       <c r="F133" t="n">
-        <v>7.5462</v>
+        <v>1.90288</v>
       </c>
       <c r="G133" t="n">
-        <v>5.366666666666667</v>
+        <v>9.683333333333334</v>
       </c>
       <c r="H133" t="n">
-        <v>6.283333333333333</v>
+        <v>10.56666666666667</v>
       </c>
       <c r="I133" t="n">
-        <v>5.366666666666667</v>
+        <v>9.683333333333334</v>
       </c>
       <c r="J133" t="n">
-        <v>6.283333333333333</v>
+        <v>10.56666666666667</v>
       </c>
       <c r="K133" t="n">
-        <v>5.366666666666667</v>
+        <v>9.683333333333334</v>
       </c>
       <c r="L133" t="n">
-        <v>6.283333333333333</v>
+        <v>10.56666666666667</v>
       </c>
       <c r="M133" t="n">
         <v>0.3333333333333333</v>
@@ -6301,37 +6313,37 @@
         <v>132</v>
       </c>
       <c r="B134" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="C134" t="n">
-        <v>-14.4202892616212</v>
+        <v>12.7485642351257</v>
       </c>
       <c r="D134" t="n">
-        <v>0.438615616091085</v>
+        <v>-13.9951114455965</v>
       </c>
       <c r="E134" t="n">
-        <v>1862.9861</v>
+        <v>1343.6123</v>
       </c>
       <c r="F134" t="n">
-        <v>5.46936</v>
+        <v>3.64803</v>
       </c>
       <c r="G134" t="n">
-        <v>5.183333333333334</v>
+        <v>9.066666666666666</v>
       </c>
       <c r="H134" t="n">
-        <v>6.166666666666666</v>
+        <v>10.13333333333333</v>
       </c>
       <c r="I134" t="n">
-        <v>5.183333333333334</v>
+        <v>9.066666666666666</v>
       </c>
       <c r="J134" t="n">
-        <v>6.166666666666666</v>
+        <v>10.13333333333333</v>
       </c>
       <c r="K134" t="n">
-        <v>5.183333333333334</v>
+        <v>9.066666666666666</v>
       </c>
       <c r="L134" t="n">
-        <v>6.166666666666666</v>
+        <v>10.13333333333333</v>
       </c>
       <c r="M134" t="n">
         <v>0.3333333333333333</v>
@@ -6345,37 +6357,37 @@
         <v>133</v>
       </c>
       <c r="B135" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="C135" t="n">
-        <v>-14.4202892616212</v>
+        <v>14.5060829317191</v>
       </c>
       <c r="D135" t="n">
-        <v>0.438615616091085</v>
+        <v>-14.9096560728536</v>
       </c>
       <c r="E135" t="n">
-        <v>1862.9861</v>
+        <v>1493.082</v>
       </c>
       <c r="F135" t="n">
-        <v>5.46936</v>
+        <v>4.67276</v>
       </c>
       <c r="G135" t="n">
-        <v>5.183333333333334</v>
+        <v>3.683333333333334</v>
       </c>
       <c r="H135" t="n">
-        <v>6.166666666666666</v>
+        <v>5.033333333333333</v>
       </c>
       <c r="I135" t="n">
-        <v>5.183333333333334</v>
+        <v>3.683333333333334</v>
       </c>
       <c r="J135" t="n">
-        <v>6.166666666666666</v>
+        <v>5.033333333333333</v>
       </c>
       <c r="K135" t="n">
-        <v>5.183333333333334</v>
+        <v>3.683333333333334</v>
       </c>
       <c r="L135" t="n">
-        <v>6.166666666666666</v>
+        <v>5.033333333333333</v>
       </c>
       <c r="M135" t="n">
         <v>0.3333333333333333</v>
@@ -6389,37 +6401,37 @@
         <v>134</v>
       </c>
       <c r="B136" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C136" t="n">
-        <v>17.8559660659719</v>
+        <v>17.5691594969999</v>
       </c>
       <c r="D136" t="n">
-        <v>-34.5128170174245</v>
+        <v>23.7073613386205</v>
       </c>
       <c r="E136" t="n">
-        <v>1508.7203</v>
+        <v>926.8409</v>
       </c>
       <c r="F136" t="n">
-        <v>3.92876</v>
+        <v>2.79316</v>
       </c>
       <c r="G136" t="n">
-        <v>6.416666666666666</v>
+        <v>5.800000000000001</v>
       </c>
       <c r="H136" t="n">
-        <v>7.75</v>
+        <v>6.716666666666667</v>
       </c>
       <c r="I136" t="n">
-        <v>6.416666666666666</v>
+        <v>5.800000000000001</v>
       </c>
       <c r="J136" t="n">
-        <v>7.75</v>
+        <v>6.716666666666667</v>
       </c>
       <c r="K136" t="n">
-        <v>6.416666666666666</v>
+        <v>5.800000000000001</v>
       </c>
       <c r="L136" t="n">
-        <v>7.75</v>
+        <v>6.716666666666667</v>
       </c>
       <c r="M136" t="n">
         <v>0.3333333333333333</v>
@@ -6433,37 +6445,37 @@
         <v>135</v>
       </c>
       <c r="B137" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="C137" t="n">
-        <v>17.8559660659719</v>
+        <v>-32.2887483255588</v>
       </c>
       <c r="D137" t="n">
-        <v>-34.5128170174245</v>
+        <v>-6.33777906329211</v>
       </c>
       <c r="E137" t="n">
-        <v>1508.7203</v>
+        <v>1605.2619</v>
       </c>
       <c r="F137" t="n">
-        <v>3.92876</v>
+        <v>4.36803</v>
       </c>
       <c r="G137" t="n">
-        <v>6.416666666666666</v>
+        <v>8.233333333333334</v>
       </c>
       <c r="H137" t="n">
-        <v>7.75</v>
+        <v>9.149999999999999</v>
       </c>
       <c r="I137" t="n">
-        <v>6.416666666666666</v>
+        <v>8.233333333333334</v>
       </c>
       <c r="J137" t="n">
-        <v>7.75</v>
+        <v>9.149999999999999</v>
       </c>
       <c r="K137" t="n">
-        <v>6.416666666666666</v>
+        <v>8.233333333333334</v>
       </c>
       <c r="L137" t="n">
-        <v>7.75</v>
+        <v>9.149999999999999</v>
       </c>
       <c r="M137" t="n">
         <v>0.3333333333333333</v>
@@ -6477,37 +6489,37 @@
         <v>136</v>
       </c>
       <c r="B138" t="n">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="C138" t="n">
-        <v>6.17248271231953</v>
+        <v>5.2885051532574</v>
       </c>
       <c r="D138" t="n">
-        <v>-11.9739943806008</v>
+        <v>-10.610672970256</v>
       </c>
       <c r="E138" t="n">
-        <v>1256.3017</v>
+        <v>593.8303</v>
       </c>
       <c r="F138" t="n">
-        <v>3.94079</v>
+        <v>1.42095</v>
       </c>
       <c r="G138" t="n">
-        <v>1.15</v>
+        <v>1.85</v>
       </c>
       <c r="H138" t="n">
-        <v>2.416666666666666</v>
+        <v>3.033333333333333</v>
       </c>
       <c r="I138" t="n">
-        <v>1.15</v>
+        <v>1.85</v>
       </c>
       <c r="J138" t="n">
-        <v>2.416666666666666</v>
+        <v>3.033333333333333</v>
       </c>
       <c r="K138" t="n">
-        <v>1.15</v>
+        <v>1.85</v>
       </c>
       <c r="L138" t="n">
-        <v>2.416666666666666</v>
+        <v>3.033333333333333</v>
       </c>
       <c r="M138" t="n">
         <v>0.3333333333333333</v>
@@ -6521,37 +6533,37 @@
         <v>137</v>
       </c>
       <c r="B139" t="n">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="C139" t="n">
-        <v>-8.90340842896458</v>
+        <v>22.2501851106262</v>
       </c>
       <c r="D139" t="n">
-        <v>-33.0969833073601</v>
+        <v>3.36277307745693</v>
       </c>
       <c r="E139" t="n">
-        <v>1968.2668</v>
+        <v>532.895</v>
       </c>
       <c r="F139" t="n">
-        <v>5.09682</v>
+        <v>2.84858</v>
       </c>
       <c r="G139" t="n">
-        <v>10.93333333333333</v>
+        <v>2.1</v>
       </c>
       <c r="H139" t="n">
-        <v>12.28333333333333</v>
+        <v>3.583333333333334</v>
       </c>
       <c r="I139" t="n">
-        <v>10.93333333333333</v>
+        <v>2.1</v>
       </c>
       <c r="J139" t="n">
-        <v>12.28333333333333</v>
+        <v>3.583333333333334</v>
       </c>
       <c r="K139" t="n">
-        <v>10.93333333333333</v>
+        <v>2.1</v>
       </c>
       <c r="L139" t="n">
-        <v>12.28333333333333</v>
+        <v>3.583333333333334</v>
       </c>
       <c r="M139" t="n">
         <v>0.3333333333333333</v>
@@ -6565,37 +6577,37 @@
         <v>138</v>
       </c>
       <c r="B140" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C140" t="n">
-        <v>0.735897737284067</v>
+        <v>-5.07881748714319</v>
       </c>
       <c r="D140" t="n">
-        <v>-11.817830191293</v>
+        <v>-34.9821210394225</v>
       </c>
       <c r="E140" t="n">
-        <v>1882.391</v>
+        <v>180.291</v>
       </c>
       <c r="F140" t="n">
-        <v>4.7241</v>
+        <v>0.46473</v>
       </c>
       <c r="G140" t="n">
-        <v>11.9</v>
+        <v>3.300000000000001</v>
       </c>
       <c r="H140" t="n">
-        <v>12.91666666666667</v>
+        <v>4.699999999999999</v>
       </c>
       <c r="I140" t="n">
-        <v>11.9</v>
+        <v>3.300000000000001</v>
       </c>
       <c r="J140" t="n">
-        <v>12.91666666666667</v>
+        <v>4.699999999999999</v>
       </c>
       <c r="K140" t="n">
-        <v>11.9</v>
+        <v>3.300000000000001</v>
       </c>
       <c r="L140" t="n">
-        <v>12.91666666666667</v>
+        <v>4.699999999999999</v>
       </c>
       <c r="M140" t="n">
         <v>0.3333333333333333</v>
@@ -6609,37 +6621,37 @@
         <v>139</v>
       </c>
       <c r="B141" t="n">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="C141" t="n">
-        <v>6.48665021130649</v>
+        <v>10.1634114043108</v>
       </c>
       <c r="D141" t="n">
-        <v>-18.7369565714111</v>
+        <v>23.9868549043046</v>
       </c>
       <c r="E141" t="n">
-        <v>2315.13</v>
+        <v>79.6007</v>
       </c>
       <c r="F141" t="n">
-        <v>7.36652</v>
+        <v>0.5374800000000001</v>
       </c>
       <c r="G141" t="n">
-        <v>1.583333333333334</v>
+        <v>2.066666666666666</v>
       </c>
       <c r="H141" t="n">
-        <v>2.75</v>
+        <v>3.316666666666666</v>
       </c>
       <c r="I141" t="n">
-        <v>1.583333333333334</v>
+        <v>2.066666666666666</v>
       </c>
       <c r="J141" t="n">
-        <v>2.75</v>
+        <v>3.316666666666666</v>
       </c>
       <c r="K141" t="n">
-        <v>1.583333333333334</v>
+        <v>2.066666666666666</v>
       </c>
       <c r="L141" t="n">
-        <v>2.75</v>
+        <v>3.316666666666666</v>
       </c>
       <c r="M141" t="n">
         <v>0.3333333333333333</v>
@@ -6653,37 +6665,37 @@
         <v>140</v>
       </c>
       <c r="B142" t="n">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C142" t="n">
-        <v>-16.1633724807616</v>
+        <v>-25.5470740390242</v>
       </c>
       <c r="D142" t="n">
-        <v>17.956024307724</v>
+        <v>-15.4194000905651</v>
       </c>
       <c r="E142" t="n">
-        <v>506.3405000000001</v>
+        <v>46.248</v>
       </c>
       <c r="F142" t="n">
-        <v>1.90288</v>
+        <v>0.2733</v>
       </c>
       <c r="G142" t="n">
-        <v>9.683333333333334</v>
+        <v>8.183333333333334</v>
       </c>
       <c r="H142" t="n">
-        <v>10.56666666666667</v>
+        <v>9.216666666666665</v>
       </c>
       <c r="I142" t="n">
-        <v>9.683333333333334</v>
+        <v>8.183333333333334</v>
       </c>
       <c r="J142" t="n">
-        <v>10.56666666666667</v>
+        <v>9.216666666666665</v>
       </c>
       <c r="K142" t="n">
-        <v>9.683333333333334</v>
+        <v>8.183333333333334</v>
       </c>
       <c r="L142" t="n">
-        <v>10.56666666666667</v>
+        <v>9.216666666666665</v>
       </c>
       <c r="M142" t="n">
         <v>0.3333333333333333</v>
@@ -6697,37 +6709,37 @@
         <v>141</v>
       </c>
       <c r="B143" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="C143" t="n">
-        <v>12.7485642351257</v>
+        <v>-33.6060651581938</v>
       </c>
       <c r="D143" t="n">
-        <v>-13.9951114455965</v>
+        <v>2.20467172657312</v>
       </c>
       <c r="E143" t="n">
-        <v>1343.6123</v>
+        <v>100.6088</v>
       </c>
       <c r="F143" t="n">
-        <v>3.64803</v>
+        <v>0.22653</v>
       </c>
       <c r="G143" t="n">
-        <v>9.066666666666666</v>
+        <v>5.833333333333334</v>
       </c>
       <c r="H143" t="n">
-        <v>10.13333333333333</v>
+        <v>7.15</v>
       </c>
       <c r="I143" t="n">
-        <v>9.066666666666666</v>
+        <v>5.833333333333334</v>
       </c>
       <c r="J143" t="n">
-        <v>10.13333333333333</v>
+        <v>7.15</v>
       </c>
       <c r="K143" t="n">
-        <v>9.066666666666666</v>
+        <v>5.833333333333334</v>
       </c>
       <c r="L143" t="n">
-        <v>10.13333333333333</v>
+        <v>7.15</v>
       </c>
       <c r="M143" t="n">
         <v>0.3333333333333333</v>
@@ -6741,37 +6753,37 @@
         <v>142</v>
       </c>
       <c r="B144" t="n">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="C144" t="n">
-        <v>14.5060829317191</v>
+        <v>-5.63196878175453</v>
       </c>
       <c r="D144" t="n">
-        <v>-14.9096560728536</v>
+        <v>-30.3321609421464</v>
       </c>
       <c r="E144" t="n">
-        <v>1493.082</v>
+        <v>70.435</v>
       </c>
       <c r="F144" t="n">
-        <v>4.67276</v>
+        <v>0.39102</v>
       </c>
       <c r="G144" t="n">
-        <v>3.683333333333334</v>
+        <v>8.666666666666668</v>
       </c>
       <c r="H144" t="n">
-        <v>5.033333333333333</v>
+        <v>9.983333333333334</v>
       </c>
       <c r="I144" t="n">
-        <v>3.683333333333334</v>
+        <v>8.666666666666668</v>
       </c>
       <c r="J144" t="n">
-        <v>5.033333333333333</v>
+        <v>9.983333333333334</v>
       </c>
       <c r="K144" t="n">
-        <v>3.683333333333334</v>
+        <v>8.666666666666668</v>
       </c>
       <c r="L144" t="n">
-        <v>5.033333333333333</v>
+        <v>9.983333333333334</v>
       </c>
       <c r="M144" t="n">
         <v>0.3333333333333333</v>
@@ -6785,37 +6797,37 @@
         <v>143</v>
       </c>
       <c r="B145" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="C145" t="n">
-        <v>17.5691594969999</v>
+        <v>8.28368192850442</v>
       </c>
       <c r="D145" t="n">
-        <v>23.7073613386205</v>
+        <v>17.7735226449337</v>
       </c>
       <c r="E145" t="n">
-        <v>926.8409</v>
+        <v>1524.5125</v>
       </c>
       <c r="F145" t="n">
-        <v>2.79316</v>
+        <v>3.82045</v>
       </c>
       <c r="G145" t="n">
-        <v>5.800000000000001</v>
+        <v>6.783333333333333</v>
       </c>
       <c r="H145" t="n">
-        <v>6.716666666666667</v>
+        <v>8.116666666666667</v>
       </c>
       <c r="I145" t="n">
-        <v>5.800000000000001</v>
+        <v>6.783333333333333</v>
       </c>
       <c r="J145" t="n">
-        <v>6.716666666666667</v>
+        <v>8.116666666666667</v>
       </c>
       <c r="K145" t="n">
-        <v>5.800000000000001</v>
+        <v>6.783333333333333</v>
       </c>
       <c r="L145" t="n">
-        <v>6.716666666666667</v>
+        <v>8.116666666666667</v>
       </c>
       <c r="M145" t="n">
         <v>0.3333333333333333</v>
@@ -6829,37 +6841,37 @@
         <v>144</v>
       </c>
       <c r="B146" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="C146" t="n">
-        <v>-32.2887483255588</v>
+        <v>0.746941949932783</v>
       </c>
       <c r="D146" t="n">
-        <v>-6.33777906329211</v>
+        <v>-28.7424167151396</v>
       </c>
       <c r="E146" t="n">
-        <v>1605.2619</v>
+        <v>97.6961</v>
       </c>
       <c r="F146" t="n">
-        <v>4.36803</v>
+        <v>0.33417</v>
       </c>
       <c r="G146" t="n">
-        <v>8.233333333333334</v>
+        <v>4.866666666666667</v>
       </c>
       <c r="H146" t="n">
-        <v>9.149999999999999</v>
+        <v>6.233333333333333</v>
       </c>
       <c r="I146" t="n">
-        <v>8.233333333333334</v>
+        <v>4.866666666666667</v>
       </c>
       <c r="J146" t="n">
-        <v>9.149999999999999</v>
+        <v>6.233333333333333</v>
       </c>
       <c r="K146" t="n">
-        <v>8.233333333333334</v>
+        <v>4.866666666666667</v>
       </c>
       <c r="L146" t="n">
-        <v>9.149999999999999</v>
+        <v>6.233333333333333</v>
       </c>
       <c r="M146" t="n">
         <v>0.3333333333333333</v>
@@ -6873,37 +6885,37 @@
         <v>145</v>
       </c>
       <c r="B147" t="n">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="C147" t="n">
-        <v>5.2885051532574</v>
+        <v>21.835155243347</v>
       </c>
       <c r="D147" t="n">
-        <v>-10.610672970256</v>
+        <v>-28.7650388212301</v>
       </c>
       <c r="E147" t="n">
-        <v>593.8303</v>
+        <v>9.186</v>
       </c>
       <c r="F147" t="n">
-        <v>1.42095</v>
+        <v>0.01795</v>
       </c>
       <c r="G147" t="n">
-        <v>1.85</v>
+        <v>4.716666666666667</v>
       </c>
       <c r="H147" t="n">
-        <v>3.033333333333333</v>
+        <v>5.949999999999999</v>
       </c>
       <c r="I147" t="n">
-        <v>1.85</v>
+        <v>4.716666666666667</v>
       </c>
       <c r="J147" t="n">
-        <v>3.033333333333333</v>
+        <v>5.949999999999999</v>
       </c>
       <c r="K147" t="n">
-        <v>1.85</v>
+        <v>4.716666666666667</v>
       </c>
       <c r="L147" t="n">
-        <v>3.033333333333333</v>
+        <v>5.949999999999999</v>
       </c>
       <c r="M147" t="n">
         <v>0.3333333333333333</v>
@@ -6917,37 +6929,37 @@
         <v>146</v>
       </c>
       <c r="B148" t="n">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="C148" t="n">
-        <v>22.2501851106262</v>
+        <v>-6.22843376493341</v>
       </c>
       <c r="D148" t="n">
-        <v>3.36277307745693</v>
+        <v>-26.8257702440231</v>
       </c>
       <c r="E148" t="n">
-        <v>532.895</v>
+        <v>109.35</v>
       </c>
       <c r="F148" t="n">
-        <v>2.84858</v>
+        <v>0.29746</v>
       </c>
       <c r="G148" t="n">
-        <v>2.1</v>
+        <v>6.416666666666666</v>
       </c>
       <c r="H148" t="n">
-        <v>3.583333333333334</v>
+        <v>7.566666666666666</v>
       </c>
       <c r="I148" t="n">
-        <v>2.1</v>
+        <v>6.416666666666666</v>
       </c>
       <c r="J148" t="n">
-        <v>3.583333333333334</v>
+        <v>7.566666666666666</v>
       </c>
       <c r="K148" t="n">
-        <v>2.1</v>
+        <v>6.416666666666666</v>
       </c>
       <c r="L148" t="n">
-        <v>3.583333333333334</v>
+        <v>7.566666666666666</v>
       </c>
       <c r="M148" t="n">
         <v>0.3333333333333333</v>
@@ -6961,37 +6973,37 @@
         <v>147</v>
       </c>
       <c r="B149" t="n">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="C149" t="n">
-        <v>-5.07881748714319</v>
+        <v>7.2247850453069</v>
       </c>
       <c r="D149" t="n">
-        <v>-34.9821210394225</v>
+        <v>-12.1653024302337</v>
       </c>
       <c r="E149" t="n">
-        <v>180.291</v>
+        <v>17.48</v>
       </c>
       <c r="F149" t="n">
-        <v>0.46473</v>
+        <v>0.04201</v>
       </c>
       <c r="G149" t="n">
-        <v>3.300000000000001</v>
+        <v>5.699999999999999</v>
       </c>
       <c r="H149" t="n">
-        <v>4.699999999999999</v>
+        <v>7.183333333333334</v>
       </c>
       <c r="I149" t="n">
-        <v>3.300000000000001</v>
+        <v>5.699999999999999</v>
       </c>
       <c r="J149" t="n">
-        <v>4.699999999999999</v>
+        <v>7.183333333333334</v>
       </c>
       <c r="K149" t="n">
-        <v>3.300000000000001</v>
+        <v>5.699999999999999</v>
       </c>
       <c r="L149" t="n">
-        <v>4.699999999999999</v>
+        <v>7.183333333333334</v>
       </c>
       <c r="M149" t="n">
         <v>0.3333333333333333</v>
@@ -7005,482 +7017,42 @@
         <v>148</v>
       </c>
       <c r="B150" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="C150" t="n">
-        <v>10.1634114043108</v>
+        <v>-19.3415293006296</v>
       </c>
       <c r="D150" t="n">
-        <v>23.9868549043046</v>
+        <v>-35.0080570685232</v>
       </c>
       <c r="E150" t="n">
-        <v>79.6007</v>
+        <v>25.5</v>
       </c>
       <c r="F150" t="n">
-        <v>0.5374800000000001</v>
+        <v>0.0646</v>
       </c>
       <c r="G150" t="n">
-        <v>2.066666666666666</v>
+        <v>11.3</v>
       </c>
       <c r="H150" t="n">
-        <v>3.316666666666666</v>
+        <v>12.68333333333333</v>
       </c>
       <c r="I150" t="n">
-        <v>2.066666666666666</v>
+        <v>11.3</v>
       </c>
       <c r="J150" t="n">
-        <v>3.316666666666666</v>
+        <v>12.68333333333333</v>
       </c>
       <c r="K150" t="n">
-        <v>2.066666666666666</v>
+        <v>11.3</v>
       </c>
       <c r="L150" t="n">
-        <v>3.316666666666666</v>
+        <v>12.68333333333333</v>
       </c>
       <c r="M150" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="N150" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="n">
-        <v>149</v>
-      </c>
-      <c r="B151" t="n">
-        <v>89</v>
-      </c>
-      <c r="C151" t="n">
-        <v>-25.5470740390242</v>
-      </c>
-      <c r="D151" t="n">
-        <v>-15.4194000905651</v>
-      </c>
-      <c r="E151" t="n">
-        <v>46.248</v>
-      </c>
-      <c r="F151" t="n">
-        <v>0.2733</v>
-      </c>
-      <c r="G151" t="n">
-        <v>8.183333333333334</v>
-      </c>
-      <c r="H151" t="n">
-        <v>9.216666666666665</v>
-      </c>
-      <c r="I151" t="n">
-        <v>8.183333333333334</v>
-      </c>
-      <c r="J151" t="n">
-        <v>9.216666666666665</v>
-      </c>
-      <c r="K151" t="n">
-        <v>8.183333333333334</v>
-      </c>
-      <c r="L151" t="n">
-        <v>9.216666666666665</v>
-      </c>
-      <c r="M151" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="N151" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="n">
-        <v>150</v>
-      </c>
-      <c r="B152" t="n">
-        <v>90</v>
-      </c>
-      <c r="C152" t="n">
-        <v>-33.6060651581938</v>
-      </c>
-      <c r="D152" t="n">
-        <v>2.20467172657312</v>
-      </c>
-      <c r="E152" t="n">
-        <v>100.6088</v>
-      </c>
-      <c r="F152" t="n">
-        <v>0.22653</v>
-      </c>
-      <c r="G152" t="n">
-        <v>5.833333333333334</v>
-      </c>
-      <c r="H152" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="I152" t="n">
-        <v>5.833333333333334</v>
-      </c>
-      <c r="J152" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="K152" t="n">
-        <v>5.833333333333334</v>
-      </c>
-      <c r="L152" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="M152" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="N152" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="n">
-        <v>151</v>
-      </c>
-      <c r="B153" t="n">
-        <v>91</v>
-      </c>
-      <c r="C153" t="n">
-        <v>-5.63196878175453</v>
-      </c>
-      <c r="D153" t="n">
-        <v>-30.3321609421464</v>
-      </c>
-      <c r="E153" t="n">
-        <v>70.435</v>
-      </c>
-      <c r="F153" t="n">
-        <v>0.39102</v>
-      </c>
-      <c r="G153" t="n">
-        <v>8.666666666666668</v>
-      </c>
-      <c r="H153" t="n">
-        <v>9.983333333333334</v>
-      </c>
-      <c r="I153" t="n">
-        <v>8.666666666666668</v>
-      </c>
-      <c r="J153" t="n">
-        <v>9.983333333333334</v>
-      </c>
-      <c r="K153" t="n">
-        <v>8.666666666666668</v>
-      </c>
-      <c r="L153" t="n">
-        <v>9.983333333333334</v>
-      </c>
-      <c r="M153" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="N153" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="n">
-        <v>152</v>
-      </c>
-      <c r="B154" t="n">
-        <v>92</v>
-      </c>
-      <c r="C154" t="n">
-        <v>8.28368192850442</v>
-      </c>
-      <c r="D154" t="n">
-        <v>17.7735226449337</v>
-      </c>
-      <c r="E154" t="n">
-        <v>1524.5125</v>
-      </c>
-      <c r="F154" t="n">
-        <v>3.82045</v>
-      </c>
-      <c r="G154" t="n">
-        <v>6.783333333333333</v>
-      </c>
-      <c r="H154" t="n">
-        <v>8.116666666666667</v>
-      </c>
-      <c r="I154" t="n">
-        <v>6.783333333333333</v>
-      </c>
-      <c r="J154" t="n">
-        <v>8.116666666666667</v>
-      </c>
-      <c r="K154" t="n">
-        <v>6.783333333333333</v>
-      </c>
-      <c r="L154" t="n">
-        <v>8.116666666666667</v>
-      </c>
-      <c r="M154" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="N154" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="n">
-        <v>153</v>
-      </c>
-      <c r="B155" t="n">
-        <v>93</v>
-      </c>
-      <c r="C155" t="n">
-        <v>0.746941949932783</v>
-      </c>
-      <c r="D155" t="n">
-        <v>-28.7424167151396</v>
-      </c>
-      <c r="E155" t="n">
-        <v>97.6961</v>
-      </c>
-      <c r="F155" t="n">
-        <v>0.33417</v>
-      </c>
-      <c r="G155" t="n">
-        <v>4.866666666666667</v>
-      </c>
-      <c r="H155" t="n">
-        <v>6.233333333333333</v>
-      </c>
-      <c r="I155" t="n">
-        <v>4.866666666666667</v>
-      </c>
-      <c r="J155" t="n">
-        <v>6.233333333333333</v>
-      </c>
-      <c r="K155" t="n">
-        <v>4.866666666666667</v>
-      </c>
-      <c r="L155" t="n">
-        <v>6.233333333333333</v>
-      </c>
-      <c r="M155" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="N155" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="n">
-        <v>154</v>
-      </c>
-      <c r="B156" t="n">
-        <v>94</v>
-      </c>
-      <c r="C156" t="n">
-        <v>21.835155243347</v>
-      </c>
-      <c r="D156" t="n">
-        <v>-28.7650388212301</v>
-      </c>
-      <c r="E156" t="n">
-        <v>9.186</v>
-      </c>
-      <c r="F156" t="n">
-        <v>0.01795</v>
-      </c>
-      <c r="G156" t="n">
-        <v>4.716666666666667</v>
-      </c>
-      <c r="H156" t="n">
-        <v>5.949999999999999</v>
-      </c>
-      <c r="I156" t="n">
-        <v>4.716666666666667</v>
-      </c>
-      <c r="J156" t="n">
-        <v>5.949999999999999</v>
-      </c>
-      <c r="K156" t="n">
-        <v>4.716666666666667</v>
-      </c>
-      <c r="L156" t="n">
-        <v>5.949999999999999</v>
-      </c>
-      <c r="M156" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="N156" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="n">
-        <v>155</v>
-      </c>
-      <c r="B157" t="n">
-        <v>95</v>
-      </c>
-      <c r="C157" t="n">
-        <v>-6.22843376493341</v>
-      </c>
-      <c r="D157" t="n">
-        <v>-26.8257702440231</v>
-      </c>
-      <c r="E157" t="n">
-        <v>109.35</v>
-      </c>
-      <c r="F157" t="n">
-        <v>0.29746</v>
-      </c>
-      <c r="G157" t="n">
-        <v>6.416666666666666</v>
-      </c>
-      <c r="H157" t="n">
-        <v>7.566666666666666</v>
-      </c>
-      <c r="I157" t="n">
-        <v>6.416666666666666</v>
-      </c>
-      <c r="J157" t="n">
-        <v>7.566666666666666</v>
-      </c>
-      <c r="K157" t="n">
-        <v>6.416666666666666</v>
-      </c>
-      <c r="L157" t="n">
-        <v>7.566666666666666</v>
-      </c>
-      <c r="M157" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="N157" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="n">
-        <v>156</v>
-      </c>
-      <c r="B158" t="n">
-        <v>96</v>
-      </c>
-      <c r="C158" t="n">
-        <v>-12.3209577741134</v>
-      </c>
-      <c r="D158" t="n">
-        <v>10.3641991683692</v>
-      </c>
-      <c r="E158" t="n">
-        <v>0</v>
-      </c>
-      <c r="F158" t="n">
-        <v>0</v>
-      </c>
-      <c r="G158" t="n">
-        <v>8.383333333333333</v>
-      </c>
-      <c r="H158" t="n">
-        <v>9.866666666666667</v>
-      </c>
-      <c r="I158" t="n">
-        <v>8.383333333333333</v>
-      </c>
-      <c r="J158" t="n">
-        <v>9.866666666666667</v>
-      </c>
-      <c r="K158" t="n">
-        <v>8.383333333333333</v>
-      </c>
-      <c r="L158" t="n">
-        <v>9.866666666666667</v>
-      </c>
-      <c r="M158" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="N158" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="n">
-        <v>157</v>
-      </c>
-      <c r="B159" t="n">
-        <v>97</v>
-      </c>
-      <c r="C159" t="n">
-        <v>7.2247850453069</v>
-      </c>
-      <c r="D159" t="n">
-        <v>-12.1653024302337</v>
-      </c>
-      <c r="E159" t="n">
-        <v>17.48</v>
-      </c>
-      <c r="F159" t="n">
-        <v>0.04201</v>
-      </c>
-      <c r="G159" t="n">
-        <v>5.699999999999999</v>
-      </c>
-      <c r="H159" t="n">
-        <v>7.183333333333334</v>
-      </c>
-      <c r="I159" t="n">
-        <v>5.699999999999999</v>
-      </c>
-      <c r="J159" t="n">
-        <v>7.183333333333334</v>
-      </c>
-      <c r="K159" t="n">
-        <v>5.699999999999999</v>
-      </c>
-      <c r="L159" t="n">
-        <v>7.183333333333334</v>
-      </c>
-      <c r="M159" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="N159" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="n">
-        <v>158</v>
-      </c>
-      <c r="B160" t="n">
-        <v>98</v>
-      </c>
-      <c r="C160" t="n">
-        <v>-19.3415293006296</v>
-      </c>
-      <c r="D160" t="n">
-        <v>-35.0080570685232</v>
-      </c>
-      <c r="E160" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="F160" t="n">
-        <v>0.0646</v>
-      </c>
-      <c r="G160" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="H160" t="n">
-        <v>12.68333333333333</v>
-      </c>
-      <c r="I160" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J160" t="n">
-        <v>12.68333333333333</v>
-      </c>
-      <c r="K160" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="L160" t="n">
-        <v>12.68333333333333</v>
-      </c>
-      <c r="M160" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="N160" t="b">
         <v>0</v>
       </c>
     </row>
